--- a/usd_krw_1y.xlsx
+++ b/usd_krw_1y.xlsx
@@ -25,9 +25,6 @@
     <t>02:00 종가</t>
   </si>
   <si>
-    <t>2025-05-20</t>
-  </si>
-  <si>
     <t>2025-05-21</t>
   </si>
   <si>
@@ -758,6 +755,9 @@
   </si>
   <si>
     <t>2026-05-20</t>
+  </si>
+  <si>
+    <t>2026-05-21</t>
   </si>
 </sst>
 </file>
@@ -935,739 +935,739 @@
               <c:strCache>
                 <c:ptCount val="245"/>
                 <c:pt idx="0">
-                  <c:v>2025-05-20</c:v>
+                  <c:v>2025-05-21</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2025-05-21</c:v>
+                  <c:v>2025-05-22</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>2025-05-22</c:v>
+                  <c:v>2025-05-23</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>2025-05-23</c:v>
+                  <c:v>2025-05-26</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>2025-05-26</c:v>
+                  <c:v>2025-05-27</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>2025-05-27</c:v>
+                  <c:v>2025-05-28</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>2025-05-28</c:v>
+                  <c:v>2025-05-29</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>2025-05-29</c:v>
+                  <c:v>2025-05-30</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>2025-05-30</c:v>
+                  <c:v>2025-06-02</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>2025-06-02</c:v>
+                  <c:v>2025-06-04</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>2025-06-04</c:v>
+                  <c:v>2025-06-05</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>2025-06-05</c:v>
+                  <c:v>2025-06-09</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>2025-06-09</c:v>
+                  <c:v>2025-06-10</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>2025-06-10</c:v>
+                  <c:v>2025-06-11</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>2025-06-11</c:v>
+                  <c:v>2025-06-12</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>2025-06-12</c:v>
+                  <c:v>2025-06-13</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>2025-06-13</c:v>
+                  <c:v>2025-06-16</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>2025-06-16</c:v>
+                  <c:v>2025-06-17</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>2025-06-17</c:v>
+                  <c:v>2025-06-18</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>2025-06-18</c:v>
+                  <c:v>2025-06-19</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>2025-06-19</c:v>
+                  <c:v>2025-06-20</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>2025-06-20</c:v>
+                  <c:v>2025-06-23</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>2025-06-23</c:v>
+                  <c:v>2025-06-24</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>2025-06-24</c:v>
+                  <c:v>2025-06-25</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>2025-06-25</c:v>
+                  <c:v>2025-06-26</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>2025-06-26</c:v>
+                  <c:v>2025-06-27</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>2025-06-27</c:v>
+                  <c:v>2025-06-30</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>2025-06-30</c:v>
+                  <c:v>2025-07-01</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>2025-07-01</c:v>
+                  <c:v>2025-07-02</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>2025-07-02</c:v>
+                  <c:v>2025-07-03</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>2025-07-03</c:v>
+                  <c:v>2025-07-04</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>2025-07-04</c:v>
+                  <c:v>2025-07-07</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>2025-07-07</c:v>
+                  <c:v>2025-07-08</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>2025-07-08</c:v>
+                  <c:v>2025-07-09</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>2025-07-09</c:v>
+                  <c:v>2025-07-10</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>2025-07-10</c:v>
+                  <c:v>2025-07-11</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>2025-07-11</c:v>
+                  <c:v>2025-07-14</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>2025-07-14</c:v>
+                  <c:v>2025-07-15</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>2025-07-15</c:v>
+                  <c:v>2025-07-16</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>2025-07-16</c:v>
+                  <c:v>2025-07-17</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>2025-07-17</c:v>
+                  <c:v>2025-07-18</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>2025-07-18</c:v>
+                  <c:v>2025-07-21</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>2025-07-21</c:v>
+                  <c:v>2025-07-22</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>2025-07-22</c:v>
+                  <c:v>2025-07-23</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>2025-07-23</c:v>
+                  <c:v>2025-07-24</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>2025-07-24</c:v>
+                  <c:v>2025-07-25</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>2025-07-25</c:v>
+                  <c:v>2025-07-28</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>2025-07-28</c:v>
+                  <c:v>2025-07-29</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>2025-07-29</c:v>
+                  <c:v>2025-07-30</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>2025-07-30</c:v>
+                  <c:v>2025-07-31</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>2025-07-31</c:v>
+                  <c:v>2025-08-01</c:v>
                 </c:pt>
                 <c:pt idx="51">
-                  <c:v>2025-08-01</c:v>
+                  <c:v>2025-08-04</c:v>
                 </c:pt>
                 <c:pt idx="52">
-                  <c:v>2025-08-04</c:v>
+                  <c:v>2025-08-05</c:v>
                 </c:pt>
                 <c:pt idx="53">
-                  <c:v>2025-08-05</c:v>
+                  <c:v>2025-08-06</c:v>
                 </c:pt>
                 <c:pt idx="54">
-                  <c:v>2025-08-06</c:v>
+                  <c:v>2025-08-07</c:v>
                 </c:pt>
                 <c:pt idx="55">
-                  <c:v>2025-08-07</c:v>
+                  <c:v>2025-08-08</c:v>
                 </c:pt>
                 <c:pt idx="56">
-                  <c:v>2025-08-08</c:v>
+                  <c:v>2025-08-11</c:v>
                 </c:pt>
                 <c:pt idx="57">
-                  <c:v>2025-08-11</c:v>
+                  <c:v>2025-08-12</c:v>
                 </c:pt>
                 <c:pt idx="58">
-                  <c:v>2025-08-12</c:v>
+                  <c:v>2025-08-13</c:v>
                 </c:pt>
                 <c:pt idx="59">
-                  <c:v>2025-08-13</c:v>
+                  <c:v>2025-08-14</c:v>
                 </c:pt>
                 <c:pt idx="60">
-                  <c:v>2025-08-14</c:v>
+                  <c:v>2025-08-18</c:v>
                 </c:pt>
                 <c:pt idx="61">
-                  <c:v>2025-08-18</c:v>
+                  <c:v>2025-08-19</c:v>
                 </c:pt>
                 <c:pt idx="62">
-                  <c:v>2025-08-19</c:v>
+                  <c:v>2025-08-20</c:v>
                 </c:pt>
                 <c:pt idx="63">
-                  <c:v>2025-08-20</c:v>
+                  <c:v>2025-08-21</c:v>
                 </c:pt>
                 <c:pt idx="64">
-                  <c:v>2025-08-21</c:v>
+                  <c:v>2025-08-22</c:v>
                 </c:pt>
                 <c:pt idx="65">
-                  <c:v>2025-08-22</c:v>
+                  <c:v>2025-08-25</c:v>
                 </c:pt>
                 <c:pt idx="66">
-                  <c:v>2025-08-25</c:v>
+                  <c:v>2025-08-26</c:v>
                 </c:pt>
                 <c:pt idx="67">
-                  <c:v>2025-08-26</c:v>
+                  <c:v>2025-08-27</c:v>
                 </c:pt>
                 <c:pt idx="68">
-                  <c:v>2025-08-27</c:v>
+                  <c:v>2025-08-28</c:v>
                 </c:pt>
                 <c:pt idx="69">
-                  <c:v>2025-08-28</c:v>
+                  <c:v>2025-08-29</c:v>
                 </c:pt>
                 <c:pt idx="70">
-                  <c:v>2025-08-29</c:v>
+                  <c:v>2025-09-01</c:v>
                 </c:pt>
                 <c:pt idx="71">
-                  <c:v>2025-09-01</c:v>
+                  <c:v>2025-09-02</c:v>
                 </c:pt>
                 <c:pt idx="72">
-                  <c:v>2025-09-02</c:v>
+                  <c:v>2025-09-03</c:v>
                 </c:pt>
                 <c:pt idx="73">
-                  <c:v>2025-09-03</c:v>
+                  <c:v>2025-09-04</c:v>
                 </c:pt>
                 <c:pt idx="74">
-                  <c:v>2025-09-04</c:v>
+                  <c:v>2025-09-05</c:v>
                 </c:pt>
                 <c:pt idx="75">
-                  <c:v>2025-09-05</c:v>
+                  <c:v>2025-09-08</c:v>
                 </c:pt>
                 <c:pt idx="76">
-                  <c:v>2025-09-08</c:v>
+                  <c:v>2025-09-09</c:v>
                 </c:pt>
                 <c:pt idx="77">
-                  <c:v>2025-09-09</c:v>
+                  <c:v>2025-09-10</c:v>
                 </c:pt>
                 <c:pt idx="78">
-                  <c:v>2025-09-10</c:v>
+                  <c:v>2025-09-11</c:v>
                 </c:pt>
                 <c:pt idx="79">
-                  <c:v>2025-09-11</c:v>
+                  <c:v>2025-09-12</c:v>
                 </c:pt>
                 <c:pt idx="80">
-                  <c:v>2025-09-12</c:v>
+                  <c:v>2025-09-15</c:v>
                 </c:pt>
                 <c:pt idx="81">
-                  <c:v>2025-09-15</c:v>
+                  <c:v>2025-09-16</c:v>
                 </c:pt>
                 <c:pt idx="82">
-                  <c:v>2025-09-16</c:v>
+                  <c:v>2025-09-17</c:v>
                 </c:pt>
                 <c:pt idx="83">
-                  <c:v>2025-09-17</c:v>
+                  <c:v>2025-09-18</c:v>
                 </c:pt>
                 <c:pt idx="84">
-                  <c:v>2025-09-18</c:v>
+                  <c:v>2025-09-19</c:v>
                 </c:pt>
                 <c:pt idx="85">
-                  <c:v>2025-09-19</c:v>
+                  <c:v>2025-09-22</c:v>
                 </c:pt>
                 <c:pt idx="86">
-                  <c:v>2025-09-22</c:v>
+                  <c:v>2025-09-23</c:v>
                 </c:pt>
                 <c:pt idx="87">
-                  <c:v>2025-09-23</c:v>
+                  <c:v>2025-09-24</c:v>
                 </c:pt>
                 <c:pt idx="88">
-                  <c:v>2025-09-24</c:v>
+                  <c:v>2025-09-25</c:v>
                 </c:pt>
                 <c:pt idx="89">
-                  <c:v>2025-09-25</c:v>
+                  <c:v>2025-09-26</c:v>
                 </c:pt>
                 <c:pt idx="90">
-                  <c:v>2025-09-26</c:v>
+                  <c:v>2025-09-29</c:v>
                 </c:pt>
                 <c:pt idx="91">
-                  <c:v>2025-09-29</c:v>
+                  <c:v>2025-09-30</c:v>
                 </c:pt>
                 <c:pt idx="92">
-                  <c:v>2025-09-30</c:v>
+                  <c:v>2025-10-01</c:v>
                 </c:pt>
                 <c:pt idx="93">
-                  <c:v>2025-10-01</c:v>
+                  <c:v>2025-10-02</c:v>
                 </c:pt>
                 <c:pt idx="94">
-                  <c:v>2025-10-02</c:v>
+                  <c:v>2025-10-10</c:v>
                 </c:pt>
                 <c:pt idx="95">
-                  <c:v>2025-10-10</c:v>
+                  <c:v>2025-10-13</c:v>
                 </c:pt>
                 <c:pt idx="96">
-                  <c:v>2025-10-13</c:v>
+                  <c:v>2025-10-14</c:v>
                 </c:pt>
                 <c:pt idx="97">
-                  <c:v>2025-10-14</c:v>
+                  <c:v>2025-10-15</c:v>
                 </c:pt>
                 <c:pt idx="98">
-                  <c:v>2025-10-15</c:v>
+                  <c:v>2025-10-16</c:v>
                 </c:pt>
                 <c:pt idx="99">
-                  <c:v>2025-10-16</c:v>
+                  <c:v>2025-10-17</c:v>
                 </c:pt>
                 <c:pt idx="100">
-                  <c:v>2025-10-17</c:v>
+                  <c:v>2025-10-20</c:v>
                 </c:pt>
                 <c:pt idx="101">
-                  <c:v>2025-10-20</c:v>
+                  <c:v>2025-10-21</c:v>
                 </c:pt>
                 <c:pt idx="102">
-                  <c:v>2025-10-21</c:v>
+                  <c:v>2025-10-22</c:v>
                 </c:pt>
                 <c:pt idx="103">
-                  <c:v>2025-10-22</c:v>
+                  <c:v>2025-10-23</c:v>
                 </c:pt>
                 <c:pt idx="104">
-                  <c:v>2025-10-23</c:v>
+                  <c:v>2025-10-24</c:v>
                 </c:pt>
                 <c:pt idx="105">
-                  <c:v>2025-10-24</c:v>
+                  <c:v>2025-10-27</c:v>
                 </c:pt>
                 <c:pt idx="106">
-                  <c:v>2025-10-27</c:v>
+                  <c:v>2025-10-28</c:v>
                 </c:pt>
                 <c:pt idx="107">
-                  <c:v>2025-10-28</c:v>
+                  <c:v>2025-10-29</c:v>
                 </c:pt>
                 <c:pt idx="108">
-                  <c:v>2025-10-29</c:v>
+                  <c:v>2025-10-30</c:v>
                 </c:pt>
                 <c:pt idx="109">
-                  <c:v>2025-10-30</c:v>
+                  <c:v>2025-10-31</c:v>
                 </c:pt>
                 <c:pt idx="110">
-                  <c:v>2025-10-31</c:v>
+                  <c:v>2025-11-03</c:v>
                 </c:pt>
                 <c:pt idx="111">
-                  <c:v>2025-11-03</c:v>
+                  <c:v>2025-11-04</c:v>
                 </c:pt>
                 <c:pt idx="112">
-                  <c:v>2025-11-04</c:v>
+                  <c:v>2025-11-05</c:v>
                 </c:pt>
                 <c:pt idx="113">
-                  <c:v>2025-11-05</c:v>
+                  <c:v>2025-11-06</c:v>
                 </c:pt>
                 <c:pt idx="114">
-                  <c:v>2025-11-06</c:v>
+                  <c:v>2025-11-07</c:v>
                 </c:pt>
                 <c:pt idx="115">
-                  <c:v>2025-11-07</c:v>
+                  <c:v>2025-11-10</c:v>
                 </c:pt>
                 <c:pt idx="116">
-                  <c:v>2025-11-10</c:v>
+                  <c:v>2025-11-11</c:v>
                 </c:pt>
                 <c:pt idx="117">
-                  <c:v>2025-11-11</c:v>
+                  <c:v>2025-11-12</c:v>
                 </c:pt>
                 <c:pt idx="118">
-                  <c:v>2025-11-12</c:v>
+                  <c:v>2025-11-13</c:v>
                 </c:pt>
                 <c:pt idx="119">
-                  <c:v>2025-11-13</c:v>
+                  <c:v>2025-11-14</c:v>
                 </c:pt>
                 <c:pt idx="120">
-                  <c:v>2025-11-14</c:v>
+                  <c:v>2025-11-17</c:v>
                 </c:pt>
                 <c:pt idx="121">
-                  <c:v>2025-11-17</c:v>
+                  <c:v>2025-11-18</c:v>
                 </c:pt>
                 <c:pt idx="122">
-                  <c:v>2025-11-18</c:v>
+                  <c:v>2025-11-19</c:v>
                 </c:pt>
                 <c:pt idx="123">
-                  <c:v>2025-11-19</c:v>
+                  <c:v>2025-11-20</c:v>
                 </c:pt>
                 <c:pt idx="124">
-                  <c:v>2025-11-20</c:v>
+                  <c:v>2025-11-21</c:v>
                 </c:pt>
                 <c:pt idx="125">
-                  <c:v>2025-11-21</c:v>
+                  <c:v>2025-11-24</c:v>
                 </c:pt>
                 <c:pt idx="126">
-                  <c:v>2025-11-24</c:v>
+                  <c:v>2025-11-25</c:v>
                 </c:pt>
                 <c:pt idx="127">
-                  <c:v>2025-11-25</c:v>
+                  <c:v>2025-11-26</c:v>
                 </c:pt>
                 <c:pt idx="128">
-                  <c:v>2025-11-26</c:v>
+                  <c:v>2025-11-27</c:v>
                 </c:pt>
                 <c:pt idx="129">
-                  <c:v>2025-11-27</c:v>
+                  <c:v>2025-11-28</c:v>
                 </c:pt>
                 <c:pt idx="130">
-                  <c:v>2025-11-28</c:v>
+                  <c:v>2025-12-01</c:v>
                 </c:pt>
                 <c:pt idx="131">
-                  <c:v>2025-12-01</c:v>
+                  <c:v>2025-12-02</c:v>
                 </c:pt>
                 <c:pt idx="132">
-                  <c:v>2025-12-02</c:v>
+                  <c:v>2025-12-03</c:v>
                 </c:pt>
                 <c:pt idx="133">
-                  <c:v>2025-12-03</c:v>
+                  <c:v>2025-12-04</c:v>
                 </c:pt>
                 <c:pt idx="134">
-                  <c:v>2025-12-04</c:v>
+                  <c:v>2025-12-05</c:v>
                 </c:pt>
                 <c:pt idx="135">
-                  <c:v>2025-12-05</c:v>
+                  <c:v>2025-12-08</c:v>
                 </c:pt>
                 <c:pt idx="136">
-                  <c:v>2025-12-08</c:v>
+                  <c:v>2025-12-09</c:v>
                 </c:pt>
                 <c:pt idx="137">
-                  <c:v>2025-12-09</c:v>
+                  <c:v>2025-12-10</c:v>
                 </c:pt>
                 <c:pt idx="138">
-                  <c:v>2025-12-10</c:v>
+                  <c:v>2025-12-11</c:v>
                 </c:pt>
                 <c:pt idx="139">
-                  <c:v>2025-12-11</c:v>
+                  <c:v>2025-12-12</c:v>
                 </c:pt>
                 <c:pt idx="140">
-                  <c:v>2025-12-12</c:v>
+                  <c:v>2025-12-15</c:v>
                 </c:pt>
                 <c:pt idx="141">
-                  <c:v>2025-12-15</c:v>
+                  <c:v>2025-12-16</c:v>
                 </c:pt>
                 <c:pt idx="142">
-                  <c:v>2025-12-16</c:v>
+                  <c:v>2025-12-17</c:v>
                 </c:pt>
                 <c:pt idx="143">
-                  <c:v>2025-12-17</c:v>
+                  <c:v>2025-12-18</c:v>
                 </c:pt>
                 <c:pt idx="144">
-                  <c:v>2025-12-18</c:v>
+                  <c:v>2025-12-19</c:v>
                 </c:pt>
                 <c:pt idx="145">
-                  <c:v>2025-12-19</c:v>
+                  <c:v>2025-12-22</c:v>
                 </c:pt>
                 <c:pt idx="146">
-                  <c:v>2025-12-22</c:v>
+                  <c:v>2025-12-23</c:v>
                 </c:pt>
                 <c:pt idx="147">
-                  <c:v>2025-12-23</c:v>
+                  <c:v>2025-12-24</c:v>
                 </c:pt>
                 <c:pt idx="148">
-                  <c:v>2025-12-24</c:v>
+                  <c:v>2025-12-26</c:v>
                 </c:pt>
                 <c:pt idx="149">
-                  <c:v>2025-12-26</c:v>
+                  <c:v>2025-12-29</c:v>
                 </c:pt>
                 <c:pt idx="150">
-                  <c:v>2025-12-29</c:v>
+                  <c:v>2025-12-30</c:v>
                 </c:pt>
                 <c:pt idx="151">
-                  <c:v>2025-12-30</c:v>
+                  <c:v>2026-01-02</c:v>
                 </c:pt>
                 <c:pt idx="152">
-                  <c:v>2026-01-02</c:v>
+                  <c:v>2026-01-05</c:v>
                 </c:pt>
                 <c:pt idx="153">
-                  <c:v>2026-01-05</c:v>
+                  <c:v>2026-01-06</c:v>
                 </c:pt>
                 <c:pt idx="154">
-                  <c:v>2026-01-06</c:v>
+                  <c:v>2026-01-07</c:v>
                 </c:pt>
                 <c:pt idx="155">
-                  <c:v>2026-01-07</c:v>
+                  <c:v>2026-01-08</c:v>
                 </c:pt>
                 <c:pt idx="156">
-                  <c:v>2026-01-08</c:v>
+                  <c:v>2026-01-09</c:v>
                 </c:pt>
                 <c:pt idx="157">
-                  <c:v>2026-01-09</c:v>
+                  <c:v>2026-01-12</c:v>
                 </c:pt>
                 <c:pt idx="158">
-                  <c:v>2026-01-12</c:v>
+                  <c:v>2026-01-13</c:v>
                 </c:pt>
                 <c:pt idx="159">
-                  <c:v>2026-01-13</c:v>
+                  <c:v>2026-01-14</c:v>
                 </c:pt>
                 <c:pt idx="160">
-                  <c:v>2026-01-14</c:v>
+                  <c:v>2026-01-15</c:v>
                 </c:pt>
                 <c:pt idx="161">
-                  <c:v>2026-01-15</c:v>
+                  <c:v>2026-01-16</c:v>
                 </c:pt>
                 <c:pt idx="162">
-                  <c:v>2026-01-16</c:v>
+                  <c:v>2026-01-19</c:v>
                 </c:pt>
                 <c:pt idx="163">
-                  <c:v>2026-01-19</c:v>
+                  <c:v>2026-01-20</c:v>
                 </c:pt>
                 <c:pt idx="164">
-                  <c:v>2026-01-20</c:v>
+                  <c:v>2026-01-21</c:v>
                 </c:pt>
                 <c:pt idx="165">
-                  <c:v>2026-01-21</c:v>
+                  <c:v>2026-01-22</c:v>
                 </c:pt>
                 <c:pt idx="166">
-                  <c:v>2026-01-22</c:v>
+                  <c:v>2026-01-23</c:v>
                 </c:pt>
                 <c:pt idx="167">
-                  <c:v>2026-01-23</c:v>
+                  <c:v>2026-01-26</c:v>
                 </c:pt>
                 <c:pt idx="168">
-                  <c:v>2026-01-26</c:v>
+                  <c:v>2026-01-27</c:v>
                 </c:pt>
                 <c:pt idx="169">
-                  <c:v>2026-01-27</c:v>
+                  <c:v>2026-01-28</c:v>
                 </c:pt>
                 <c:pt idx="170">
-                  <c:v>2026-01-28</c:v>
+                  <c:v>2026-01-29</c:v>
                 </c:pt>
                 <c:pt idx="171">
-                  <c:v>2026-01-29</c:v>
+                  <c:v>2026-01-30</c:v>
                 </c:pt>
                 <c:pt idx="172">
-                  <c:v>2026-01-30</c:v>
+                  <c:v>2026-02-02</c:v>
                 </c:pt>
                 <c:pt idx="173">
-                  <c:v>2026-02-02</c:v>
+                  <c:v>2026-02-03</c:v>
                 </c:pt>
                 <c:pt idx="174">
-                  <c:v>2026-02-03</c:v>
+                  <c:v>2026-02-04</c:v>
                 </c:pt>
                 <c:pt idx="175">
-                  <c:v>2026-02-04</c:v>
+                  <c:v>2026-02-05</c:v>
                 </c:pt>
                 <c:pt idx="176">
-                  <c:v>2026-02-05</c:v>
+                  <c:v>2026-02-06</c:v>
                 </c:pt>
                 <c:pt idx="177">
-                  <c:v>2026-02-06</c:v>
+                  <c:v>2026-02-09</c:v>
                 </c:pt>
                 <c:pt idx="178">
-                  <c:v>2026-02-09</c:v>
+                  <c:v>2026-02-10</c:v>
                 </c:pt>
                 <c:pt idx="179">
-                  <c:v>2026-02-10</c:v>
+                  <c:v>2026-02-11</c:v>
                 </c:pt>
                 <c:pt idx="180">
-                  <c:v>2026-02-11</c:v>
+                  <c:v>2026-02-12</c:v>
                 </c:pt>
                 <c:pt idx="181">
-                  <c:v>2026-02-12</c:v>
+                  <c:v>2026-02-13</c:v>
                 </c:pt>
                 <c:pt idx="182">
-                  <c:v>2026-02-13</c:v>
+                  <c:v>2026-02-19</c:v>
                 </c:pt>
                 <c:pt idx="183">
-                  <c:v>2026-02-19</c:v>
+                  <c:v>2026-02-20</c:v>
                 </c:pt>
                 <c:pt idx="184">
-                  <c:v>2026-02-20</c:v>
+                  <c:v>2026-02-23</c:v>
                 </c:pt>
                 <c:pt idx="185">
-                  <c:v>2026-02-23</c:v>
+                  <c:v>2026-02-24</c:v>
                 </c:pt>
                 <c:pt idx="186">
-                  <c:v>2026-02-24</c:v>
+                  <c:v>2026-02-25</c:v>
                 </c:pt>
                 <c:pt idx="187">
-                  <c:v>2026-02-25</c:v>
+                  <c:v>2026-02-26</c:v>
                 </c:pt>
                 <c:pt idx="188">
-                  <c:v>2026-02-26</c:v>
+                  <c:v>2026-02-27</c:v>
                 </c:pt>
                 <c:pt idx="189">
-                  <c:v>2026-02-27</c:v>
+                  <c:v>2026-03-03</c:v>
                 </c:pt>
                 <c:pt idx="190">
-                  <c:v>2026-03-03</c:v>
+                  <c:v>2026-03-04</c:v>
                 </c:pt>
                 <c:pt idx="191">
-                  <c:v>2026-03-04</c:v>
+                  <c:v>2026-03-05</c:v>
                 </c:pt>
                 <c:pt idx="192">
-                  <c:v>2026-03-05</c:v>
+                  <c:v>2026-03-06</c:v>
                 </c:pt>
                 <c:pt idx="193">
-                  <c:v>2026-03-06</c:v>
+                  <c:v>2026-03-09</c:v>
                 </c:pt>
                 <c:pt idx="194">
-                  <c:v>2026-03-09</c:v>
+                  <c:v>2026-03-10</c:v>
                 </c:pt>
                 <c:pt idx="195">
-                  <c:v>2026-03-10</c:v>
+                  <c:v>2026-03-11</c:v>
                 </c:pt>
                 <c:pt idx="196">
-                  <c:v>2026-03-11</c:v>
+                  <c:v>2026-03-12</c:v>
                 </c:pt>
                 <c:pt idx="197">
-                  <c:v>2026-03-12</c:v>
+                  <c:v>2026-03-13</c:v>
                 </c:pt>
                 <c:pt idx="198">
-                  <c:v>2026-03-13</c:v>
+                  <c:v>2026-03-16</c:v>
                 </c:pt>
                 <c:pt idx="199">
-                  <c:v>2026-03-16</c:v>
+                  <c:v>2026-03-17</c:v>
                 </c:pt>
                 <c:pt idx="200">
-                  <c:v>2026-03-17</c:v>
+                  <c:v>2026-03-18</c:v>
                 </c:pt>
                 <c:pt idx="201">
-                  <c:v>2026-03-18</c:v>
+                  <c:v>2026-03-19</c:v>
                 </c:pt>
                 <c:pt idx="202">
-                  <c:v>2026-03-19</c:v>
+                  <c:v>2026-03-20</c:v>
                 </c:pt>
                 <c:pt idx="203">
-                  <c:v>2026-03-20</c:v>
+                  <c:v>2026-03-23</c:v>
                 </c:pt>
                 <c:pt idx="204">
-                  <c:v>2026-03-23</c:v>
+                  <c:v>2026-03-24</c:v>
                 </c:pt>
                 <c:pt idx="205">
-                  <c:v>2026-03-24</c:v>
+                  <c:v>2026-03-25</c:v>
                 </c:pt>
                 <c:pt idx="206">
-                  <c:v>2026-03-25</c:v>
+                  <c:v>2026-03-26</c:v>
                 </c:pt>
                 <c:pt idx="207">
-                  <c:v>2026-03-26</c:v>
+                  <c:v>2026-03-27</c:v>
                 </c:pt>
                 <c:pt idx="208">
-                  <c:v>2026-03-27</c:v>
+                  <c:v>2026-03-30</c:v>
                 </c:pt>
                 <c:pt idx="209">
-                  <c:v>2026-03-30</c:v>
+                  <c:v>2026-03-31</c:v>
                 </c:pt>
                 <c:pt idx="210">
-                  <c:v>2026-03-31</c:v>
+                  <c:v>2026-04-01</c:v>
                 </c:pt>
                 <c:pt idx="211">
-                  <c:v>2026-04-01</c:v>
+                  <c:v>2026-04-02</c:v>
                 </c:pt>
                 <c:pt idx="212">
-                  <c:v>2026-04-02</c:v>
+                  <c:v>2026-04-03</c:v>
                 </c:pt>
                 <c:pt idx="213">
-                  <c:v>2026-04-03</c:v>
+                  <c:v>2026-04-06</c:v>
                 </c:pt>
                 <c:pt idx="214">
-                  <c:v>2026-04-06</c:v>
+                  <c:v>2026-04-07</c:v>
                 </c:pt>
                 <c:pt idx="215">
-                  <c:v>2026-04-07</c:v>
+                  <c:v>2026-04-08</c:v>
                 </c:pt>
                 <c:pt idx="216">
-                  <c:v>2026-04-08</c:v>
+                  <c:v>2026-04-09</c:v>
                 </c:pt>
                 <c:pt idx="217">
-                  <c:v>2026-04-09</c:v>
+                  <c:v>2026-04-10</c:v>
                 </c:pt>
                 <c:pt idx="218">
-                  <c:v>2026-04-10</c:v>
+                  <c:v>2026-04-13</c:v>
                 </c:pt>
                 <c:pt idx="219">
-                  <c:v>2026-04-13</c:v>
+                  <c:v>2026-04-14</c:v>
                 </c:pt>
                 <c:pt idx="220">
-                  <c:v>2026-04-14</c:v>
+                  <c:v>2026-04-15</c:v>
                 </c:pt>
                 <c:pt idx="221">
-                  <c:v>2026-04-15</c:v>
+                  <c:v>2026-04-16</c:v>
                 </c:pt>
                 <c:pt idx="222">
-                  <c:v>2026-04-16</c:v>
+                  <c:v>2026-04-17</c:v>
                 </c:pt>
                 <c:pt idx="223">
-                  <c:v>2026-04-17</c:v>
+                  <c:v>2026-04-20</c:v>
                 </c:pt>
                 <c:pt idx="224">
-                  <c:v>2026-04-20</c:v>
+                  <c:v>2026-04-21</c:v>
                 </c:pt>
                 <c:pt idx="225">
-                  <c:v>2026-04-21</c:v>
+                  <c:v>2026-04-22</c:v>
                 </c:pt>
                 <c:pt idx="226">
-                  <c:v>2026-04-22</c:v>
+                  <c:v>2026-04-23</c:v>
                 </c:pt>
                 <c:pt idx="227">
-                  <c:v>2026-04-23</c:v>
+                  <c:v>2026-04-24</c:v>
                 </c:pt>
                 <c:pt idx="228">
-                  <c:v>2026-04-24</c:v>
+                  <c:v>2026-04-27</c:v>
                 </c:pt>
                 <c:pt idx="229">
-                  <c:v>2026-04-27</c:v>
+                  <c:v>2026-04-28</c:v>
                 </c:pt>
                 <c:pt idx="230">
-                  <c:v>2026-04-28</c:v>
+                  <c:v>2026-04-29</c:v>
                 </c:pt>
                 <c:pt idx="231">
-                  <c:v>2026-04-29</c:v>
+                  <c:v>2026-04-30</c:v>
                 </c:pt>
                 <c:pt idx="232">
-                  <c:v>2026-04-30</c:v>
+                  <c:v>2026-05-04</c:v>
                 </c:pt>
                 <c:pt idx="233">
-                  <c:v>2026-05-04</c:v>
+                  <c:v>2026-05-06</c:v>
                 </c:pt>
                 <c:pt idx="234">
-                  <c:v>2026-05-06</c:v>
+                  <c:v>2026-05-07</c:v>
                 </c:pt>
                 <c:pt idx="235">
-                  <c:v>2026-05-07</c:v>
+                  <c:v>2026-05-08</c:v>
                 </c:pt>
                 <c:pt idx="236">
-                  <c:v>2026-05-08</c:v>
+                  <c:v>2026-05-11</c:v>
                 </c:pt>
                 <c:pt idx="237">
-                  <c:v>2026-05-11</c:v>
+                  <c:v>2026-05-12</c:v>
                 </c:pt>
                 <c:pt idx="238">
-                  <c:v>2026-05-12</c:v>
+                  <c:v>2026-05-13</c:v>
                 </c:pt>
                 <c:pt idx="239">
-                  <c:v>2026-05-13</c:v>
+                  <c:v>2026-05-14</c:v>
                 </c:pt>
                 <c:pt idx="240">
-                  <c:v>2026-05-14</c:v>
+                  <c:v>2026-05-15</c:v>
                 </c:pt>
                 <c:pt idx="241">
-                  <c:v>2026-05-15</c:v>
+                  <c:v>2026-05-18</c:v>
                 </c:pt>
                 <c:pt idx="242">
-                  <c:v>2026-05-18</c:v>
+                  <c:v>2026-05-19</c:v>
                 </c:pt>
                 <c:pt idx="243">
-                  <c:v>2026-05-19</c:v>
+                  <c:v>2026-05-20</c:v>
                 </c:pt>
                 <c:pt idx="244">
-                  <c:v>2026-05-20</c:v>
+                  <c:v>2026-05-21</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -1679,739 +1679,739 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="245"/>
                 <c:pt idx="0">
-                  <c:v>1392.4</c:v>
+                  <c:v>1387.2</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1387.2</c:v>
+                  <c:v>1381.3</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1381.3</c:v>
+                  <c:v>1375.6</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1375.6</c:v>
+                  <c:v>1364.4</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1364.4</c:v>
+                  <c:v>1369.5</c:v>
                 </c:pt>
                 <c:pt idx="5">
+                  <c:v>1376.5</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1375.9</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1380.1</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1373.1</c:v>
+                </c:pt>
+                <c:pt idx="9">
                   <c:v>1369.5</c:v>
                 </c:pt>
-                <c:pt idx="6">
-                  <c:v>1376.5</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>1375.9</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>1380.1</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>1373.1</c:v>
-                </c:pt>
                 <c:pt idx="10">
-                  <c:v>1369.5</c:v>
+                  <c:v>1358.4</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1358.4</c:v>
+                  <c:v>1356.4</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1356.4</c:v>
+                  <c:v>1364.3</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>1364.3</c:v>
+                  <c:v>1375</c:v>
                 </c:pt>
                 <c:pt idx="14">
+                  <c:v>1358.7</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>1369.6</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>1363.8</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>1362.7</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>1369.4</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>1380.2</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>1365.6</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>1384.3</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>1360.2</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>1362.4</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>1356.9</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>1357.4</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>1350</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>1355.9</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>1358.7</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>1359.4</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>1362.3</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>1367.8</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>1367.9</c:v>
+                </c:pt>
+                <c:pt idx="33">
                   <c:v>1375</c:v>
                 </c:pt>
-                <c:pt idx="15">
-                  <c:v>1358.7</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>1369.6</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>1363.8</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>1362.7</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>1369.4</c:v>
-                </c:pt>
-                <c:pt idx="20">
+                <c:pt idx="34">
+                  <c:v>1370</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>1375.4</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>1381.2</c:v>
+                </c:pt>
+                <c:pt idx="37">
                   <c:v>1380.2</c:v>
                 </c:pt>
-                <c:pt idx="21">
-                  <c:v>1365.6</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>1384.3</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>1360.2</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>1362.4</c:v>
-                </c:pt>
-                <c:pt idx="25">
-                  <c:v>1356.9</c:v>
-                </c:pt>
-                <c:pt idx="26">
-                  <c:v>1357.4</c:v>
-                </c:pt>
-                <c:pt idx="27">
-                  <c:v>1350</c:v>
-                </c:pt>
-                <c:pt idx="28">
-                  <c:v>1355.9</c:v>
-                </c:pt>
-                <c:pt idx="29">
-                  <c:v>1358.7</c:v>
-                </c:pt>
-                <c:pt idx="30">
-                  <c:v>1359.4</c:v>
-                </c:pt>
-                <c:pt idx="31">
-                  <c:v>1362.3</c:v>
-                </c:pt>
-                <c:pt idx="32">
-                  <c:v>1367.8</c:v>
-                </c:pt>
-                <c:pt idx="33">
-                  <c:v>1367.9</c:v>
-                </c:pt>
-                <c:pt idx="34">
-                  <c:v>1375</c:v>
-                </c:pt>
-                <c:pt idx="35">
-                  <c:v>1370</c:v>
-                </c:pt>
-                <c:pt idx="36">
-                  <c:v>1375.4</c:v>
-                </c:pt>
-                <c:pt idx="37">
+                <c:pt idx="38">
+                  <c:v>1385.7</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>1392.6</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>1393</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>1388.2</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>1387.8</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>1379.8</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>1367.2</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>1377.9</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>1382</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>1391</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>1383.1</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>1387</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>1401.4</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>1385.2</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>1388.3</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>1389.5</c:v>
+                </c:pt>
+                <c:pt idx="54">
                   <c:v>1381.2</c:v>
                 </c:pt>
-                <c:pt idx="38">
-                  <c:v>1380.2</c:v>
-                </c:pt>
-                <c:pt idx="39">
-                  <c:v>1385.7</c:v>
-                </c:pt>
-                <c:pt idx="40">
-                  <c:v>1392.6</c:v>
-                </c:pt>
-                <c:pt idx="41">
-                  <c:v>1393</c:v>
-                </c:pt>
-                <c:pt idx="42">
-                  <c:v>1388.2</c:v>
-                </c:pt>
-                <c:pt idx="43">
-                  <c:v>1387.8</c:v>
-                </c:pt>
-                <c:pt idx="44">
-                  <c:v>1379.8</c:v>
-                </c:pt>
-                <c:pt idx="45">
-                  <c:v>1367.2</c:v>
-                </c:pt>
-                <c:pt idx="46">
-                  <c:v>1377.9</c:v>
-                </c:pt>
-                <c:pt idx="47">
+                <c:pt idx="55">
+                  <c:v>1389.6</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>1388</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>1389.9</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>1381.7</c:v>
+                </c:pt>
+                <c:pt idx="59">
                   <c:v>1382</c:v>
                 </c:pt>
-                <c:pt idx="48">
-                  <c:v>1391</c:v>
-                </c:pt>
-                <c:pt idx="49">
-                  <c:v>1383.1</c:v>
-                </c:pt>
-                <c:pt idx="50">
-                  <c:v>1387</c:v>
-                </c:pt>
-                <c:pt idx="51">
-                  <c:v>1401.4</c:v>
-                </c:pt>
-                <c:pt idx="52">
-                  <c:v>1385.2</c:v>
-                </c:pt>
-                <c:pt idx="53">
-                  <c:v>1388.3</c:v>
-                </c:pt>
-                <c:pt idx="54">
-                  <c:v>1389.5</c:v>
-                </c:pt>
-                <c:pt idx="55">
-                  <c:v>1381.2</c:v>
-                </c:pt>
-                <c:pt idx="56">
-                  <c:v>1389.6</c:v>
-                </c:pt>
-                <c:pt idx="57">
-                  <c:v>1388</c:v>
-                </c:pt>
-                <c:pt idx="58">
-                  <c:v>1389.9</c:v>
-                </c:pt>
-                <c:pt idx="59">
-                  <c:v>1381.7</c:v>
-                </c:pt>
                 <c:pt idx="60">
-                  <c:v>1382</c:v>
+                  <c:v>1385</c:v>
                 </c:pt>
                 <c:pt idx="61">
-                  <c:v>1385</c:v>
+                  <c:v>1390.9</c:v>
                 </c:pt>
                 <c:pt idx="62">
-                  <c:v>1390.9</c:v>
+                  <c:v>1398.4</c:v>
                 </c:pt>
                 <c:pt idx="63">
                   <c:v>1398.4</c:v>
                 </c:pt>
                 <c:pt idx="64">
-                  <c:v>1398.4</c:v>
+                  <c:v>1393.2</c:v>
                 </c:pt>
                 <c:pt idx="65">
-                  <c:v>1393.2</c:v>
+                  <c:v>1384.7</c:v>
                 </c:pt>
                 <c:pt idx="66">
-                  <c:v>1384.7</c:v>
+                  <c:v>1395.8</c:v>
                 </c:pt>
                 <c:pt idx="67">
-                  <c:v>1395.8</c:v>
+                  <c:v>1396.3</c:v>
                 </c:pt>
                 <c:pt idx="68">
-                  <c:v>1396.3</c:v>
+                  <c:v>1387.6</c:v>
                 </c:pt>
                 <c:pt idx="69">
-                  <c:v>1387.6</c:v>
+                  <c:v>1390.1</c:v>
                 </c:pt>
                 <c:pt idx="70">
-                  <c:v>1390.1</c:v>
+                  <c:v>1393.7</c:v>
                 </c:pt>
                 <c:pt idx="71">
-                  <c:v>1393.7</c:v>
+                  <c:v>1391</c:v>
                 </c:pt>
                 <c:pt idx="72">
+                  <c:v>1392.3</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>1392.5</c:v>
+                </c:pt>
+                <c:pt idx="74">
                   <c:v>1391</c:v>
                 </c:pt>
-                <c:pt idx="73">
-                  <c:v>1392.3</c:v>
-                </c:pt>
-                <c:pt idx="74">
-                  <c:v>1392.5</c:v>
-                </c:pt>
                 <c:pt idx="75">
-                  <c:v>1391</c:v>
+                  <c:v>1390.6</c:v>
                 </c:pt>
                 <c:pt idx="76">
-                  <c:v>1390.6</c:v>
+                  <c:v>1387.9</c:v>
                 </c:pt>
                 <c:pt idx="77">
-                  <c:v>1387.9</c:v>
+                  <c:v>1386.6</c:v>
                 </c:pt>
                 <c:pt idx="78">
-                  <c:v>1386.6</c:v>
+                  <c:v>1391.8</c:v>
                 </c:pt>
                 <c:pt idx="79">
-                  <c:v>1391.8</c:v>
+                  <c:v>1388.2</c:v>
                 </c:pt>
                 <c:pt idx="80">
-                  <c:v>1388.2</c:v>
+                  <c:v>1389</c:v>
                 </c:pt>
                 <c:pt idx="81">
-                  <c:v>1389</c:v>
+                  <c:v>1378.9</c:v>
                 </c:pt>
                 <c:pt idx="82">
-                  <c:v>1378.9</c:v>
+                  <c:v>1380.1</c:v>
                 </c:pt>
                 <c:pt idx="83">
-                  <c:v>1380.1</c:v>
+                  <c:v>1387.8</c:v>
                 </c:pt>
                 <c:pt idx="84">
-                  <c:v>1387.8</c:v>
+                  <c:v>1393.6</c:v>
                 </c:pt>
                 <c:pt idx="85">
-                  <c:v>1393.6</c:v>
+                  <c:v>1392.6</c:v>
                 </c:pt>
                 <c:pt idx="86">
                   <c:v>1392.6</c:v>
                 </c:pt>
                 <c:pt idx="87">
-                  <c:v>1392.6</c:v>
+                  <c:v>1397.5</c:v>
                 </c:pt>
                 <c:pt idx="88">
-                  <c:v>1397.5</c:v>
+                  <c:v>1400.6</c:v>
                 </c:pt>
                 <c:pt idx="89">
-                  <c:v>1400.6</c:v>
+                  <c:v>1412.4</c:v>
                 </c:pt>
                 <c:pt idx="90">
-                  <c:v>1412.4</c:v>
+                  <c:v>1398.7</c:v>
                 </c:pt>
                 <c:pt idx="91">
-                  <c:v>1398.7</c:v>
+                  <c:v>1402.9</c:v>
                 </c:pt>
                 <c:pt idx="92">
-                  <c:v>1402.9</c:v>
+                  <c:v>1403.2</c:v>
                 </c:pt>
                 <c:pt idx="93">
-                  <c:v>1403.2</c:v>
+                  <c:v>1400</c:v>
                 </c:pt>
                 <c:pt idx="94">
-                  <c:v>1400</c:v>
+                  <c:v>1421</c:v>
                 </c:pt>
                 <c:pt idx="95">
-                  <c:v>1421</c:v>
+                  <c:v>1425.8</c:v>
                 </c:pt>
                 <c:pt idx="96">
+                  <c:v>1431</c:v>
+                </c:pt>
+                <c:pt idx="97">
+                  <c:v>1421.3</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>1417.9</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>1421.2</c:v>
+                </c:pt>
+                <c:pt idx="100">
+                  <c:v>1419.2</c:v>
+                </c:pt>
+                <c:pt idx="101">
+                  <c:v>1427.8</c:v>
+                </c:pt>
+                <c:pt idx="102">
+                  <c:v>1429.8</c:v>
+                </c:pt>
+                <c:pt idx="103">
+                  <c:v>1439.6</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>1437.1</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>1431.7</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>1437.7</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>1431.7</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>1426.5</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>1424.4</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>1428.8</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>1437.9</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>1449.4</c:v>
+                </c:pt>
+                <c:pt idx="113">
+                  <c:v>1447.7</c:v>
+                </c:pt>
+                <c:pt idx="114">
+                  <c:v>1456.9</c:v>
+                </c:pt>
+                <c:pt idx="115">
+                  <c:v>1451.4</c:v>
+                </c:pt>
+                <c:pt idx="116">
+                  <c:v>1463.3</c:v>
+                </c:pt>
+                <c:pt idx="117">
+                  <c:v>1465.7</c:v>
+                </c:pt>
+                <c:pt idx="118">
+                  <c:v>1467.7</c:v>
+                </c:pt>
+                <c:pt idx="119">
+                  <c:v>1457</c:v>
+                </c:pt>
+                <c:pt idx="120">
+                  <c:v>1458</c:v>
+                </c:pt>
+                <c:pt idx="121">
+                  <c:v>1465.3</c:v>
+                </c:pt>
+                <c:pt idx="122">
+                  <c:v>1465.6</c:v>
+                </c:pt>
+                <c:pt idx="123">
+                  <c:v>1467.9</c:v>
+                </c:pt>
+                <c:pt idx="124">
+                  <c:v>1475.6</c:v>
+                </c:pt>
+                <c:pt idx="125">
+                  <c:v>1477.1</c:v>
+                </c:pt>
+                <c:pt idx="126">
+                  <c:v>1472.4</c:v>
+                </c:pt>
+                <c:pt idx="127">
+                  <c:v>1465.6</c:v>
+                </c:pt>
+                <c:pt idx="128">
+                  <c:v>1464.9</c:v>
+                </c:pt>
+                <c:pt idx="129">
+                  <c:v>1470.6</c:v>
+                </c:pt>
+                <c:pt idx="130">
+                  <c:v>1469.9</c:v>
+                </c:pt>
+                <c:pt idx="131">
+                  <c:v>1468.4</c:v>
+                </c:pt>
+                <c:pt idx="132">
+                  <c:v>1468</c:v>
+                </c:pt>
+                <c:pt idx="133">
+                  <c:v>1473.5</c:v>
+                </c:pt>
+                <c:pt idx="134">
+                  <c:v>1468.8</c:v>
+                </c:pt>
+                <c:pt idx="135">
+                  <c:v>1466.9</c:v>
+                </c:pt>
+                <c:pt idx="136">
+                  <c:v>1472.3</c:v>
+                </c:pt>
+                <c:pt idx="137">
+                  <c:v>1470.4</c:v>
+                </c:pt>
+                <c:pt idx="138">
+                  <c:v>1473</c:v>
+                </c:pt>
+                <c:pt idx="139">
+                  <c:v>1473.7</c:v>
+                </c:pt>
+                <c:pt idx="140">
+                  <c:v>1471</c:v>
+                </c:pt>
+                <c:pt idx="141">
+                  <c:v>1477</c:v>
+                </c:pt>
+                <c:pt idx="142">
+                  <c:v>1479.8</c:v>
+                </c:pt>
+                <c:pt idx="143">
+                  <c:v>1478.3</c:v>
+                </c:pt>
+                <c:pt idx="144">
+                  <c:v>1476.3</c:v>
+                </c:pt>
+                <c:pt idx="145">
+                  <c:v>1480.1</c:v>
+                </c:pt>
+                <c:pt idx="146">
+                  <c:v>1483.6</c:v>
+                </c:pt>
+                <c:pt idx="147">
+                  <c:v>1449.8</c:v>
+                </c:pt>
+                <c:pt idx="148">
+                  <c:v>1440.3</c:v>
+                </c:pt>
+                <c:pt idx="149">
+                  <c:v>1429.8</c:v>
+                </c:pt>
+                <c:pt idx="150">
+                  <c:v>1439</c:v>
+                </c:pt>
+                <c:pt idx="151">
+                  <c:v>1441.8</c:v>
+                </c:pt>
+                <c:pt idx="152">
+                  <c:v>1443.8</c:v>
+                </c:pt>
+                <c:pt idx="153">
+                  <c:v>1445.4</c:v>
+                </c:pt>
+                <c:pt idx="154">
+                  <c:v>1445.8</c:v>
+                </c:pt>
+                <c:pt idx="155">
+                  <c:v>1450.6</c:v>
+                </c:pt>
+                <c:pt idx="156">
+                  <c:v>1457.6</c:v>
+                </c:pt>
+                <c:pt idx="157">
+                  <c:v>1468.4</c:v>
+                </c:pt>
+                <c:pt idx="158">
+                  <c:v>1473.7</c:v>
+                </c:pt>
+                <c:pt idx="159">
+                  <c:v>1477.5</c:v>
+                </c:pt>
+                <c:pt idx="160">
+                  <c:v>1469.7</c:v>
+                </c:pt>
+                <c:pt idx="161">
+                  <c:v>1473.6</c:v>
+                </c:pt>
+                <c:pt idx="162">
+                  <c:v>1473.7</c:v>
+                </c:pt>
+                <c:pt idx="163">
+                  <c:v>1478.1</c:v>
+                </c:pt>
+                <c:pt idx="164">
+                  <c:v>1471.3</c:v>
+                </c:pt>
+                <c:pt idx="165">
+                  <c:v>1469.9</c:v>
+                </c:pt>
+                <c:pt idx="166">
+                  <c:v>1465.8</c:v>
+                </c:pt>
+                <c:pt idx="167">
+                  <c:v>1440.6</c:v>
+                </c:pt>
+                <c:pt idx="168">
+                  <c:v>1446.2</c:v>
+                </c:pt>
+                <c:pt idx="169">
+                  <c:v>1422.5</c:v>
+                </c:pt>
+                <c:pt idx="170">
+                  <c:v>1426.3</c:v>
+                </c:pt>
+                <c:pt idx="171">
+                  <c:v>1439.5</c:v>
+                </c:pt>
+                <c:pt idx="172">
+                  <c:v>1464.3</c:v>
+                </c:pt>
+                <c:pt idx="173">
+                  <c:v>1445.4</c:v>
+                </c:pt>
+                <c:pt idx="174">
+                  <c:v>1450.2</c:v>
+                </c:pt>
+                <c:pt idx="175">
+                  <c:v>1469</c:v>
+                </c:pt>
+                <c:pt idx="176">
+                  <c:v>1469.5</c:v>
+                </c:pt>
+                <c:pt idx="177">
+                  <c:v>1460.3</c:v>
+                </c:pt>
+                <c:pt idx="178">
+                  <c:v>1459.1</c:v>
+                </c:pt>
+                <c:pt idx="179">
+                  <c:v>1450.1</c:v>
+                </c:pt>
+                <c:pt idx="180">
+                  <c:v>1440.2</c:v>
+                </c:pt>
+                <c:pt idx="181">
+                  <c:v>1444.9</c:v>
+                </c:pt>
+                <c:pt idx="182">
+                  <c:v>1445.5</c:v>
+                </c:pt>
+                <c:pt idx="183">
+                  <c:v>1446.6</c:v>
+                </c:pt>
+                <c:pt idx="184">
+                  <c:v>1440</c:v>
+                </c:pt>
+                <c:pt idx="185">
+                  <c:v>1442.5</c:v>
+                </c:pt>
+                <c:pt idx="186">
+                  <c:v>1429.4</c:v>
+                </c:pt>
+                <c:pt idx="187">
                   <c:v>1425.8</c:v>
                 </c:pt>
-                <c:pt idx="97">
-                  <c:v>1431</c:v>
-                </c:pt>
-                <c:pt idx="98">
-                  <c:v>1421.3</c:v>
-                </c:pt>
-                <c:pt idx="99">
-                  <c:v>1417.9</c:v>
-                </c:pt>
-                <c:pt idx="100">
-                  <c:v>1421.2</c:v>
-                </c:pt>
-                <c:pt idx="101">
-                  <c:v>1419.2</c:v>
-                </c:pt>
-                <c:pt idx="102">
-                  <c:v>1427.8</c:v>
-                </c:pt>
-                <c:pt idx="103">
-                  <c:v>1429.8</c:v>
-                </c:pt>
-                <c:pt idx="104">
-                  <c:v>1439.6</c:v>
-                </c:pt>
-                <c:pt idx="105">
-                  <c:v>1437.1</c:v>
-                </c:pt>
-                <c:pt idx="106">
-                  <c:v>1431.7</c:v>
-                </c:pt>
-                <c:pt idx="107">
-                  <c:v>1437.7</c:v>
-                </c:pt>
-                <c:pt idx="108">
-                  <c:v>1431.7</c:v>
-                </c:pt>
-                <c:pt idx="109">
-                  <c:v>1426.5</c:v>
-                </c:pt>
-                <c:pt idx="110">
-                  <c:v>1424.4</c:v>
-                </c:pt>
-                <c:pt idx="111">
-                  <c:v>1428.8</c:v>
-                </c:pt>
-                <c:pt idx="112">
-                  <c:v>1437.9</c:v>
-                </c:pt>
-                <c:pt idx="113">
-                  <c:v>1449.4</c:v>
-                </c:pt>
-                <c:pt idx="114">
-                  <c:v>1447.7</c:v>
-                </c:pt>
-                <c:pt idx="115">
-                  <c:v>1456.9</c:v>
-                </c:pt>
-                <c:pt idx="116">
-                  <c:v>1451.4</c:v>
-                </c:pt>
-                <c:pt idx="117">
-                  <c:v>1463.3</c:v>
-                </c:pt>
-                <c:pt idx="118">
-                  <c:v>1465.7</c:v>
-                </c:pt>
-                <c:pt idx="119">
-                  <c:v>1467.7</c:v>
-                </c:pt>
-                <c:pt idx="120">
-                  <c:v>1457</c:v>
-                </c:pt>
-                <c:pt idx="121">
-                  <c:v>1458</c:v>
-                </c:pt>
-                <c:pt idx="122">
-                  <c:v>1465.3</c:v>
-                </c:pt>
-                <c:pt idx="123">
-                  <c:v>1465.6</c:v>
-                </c:pt>
-                <c:pt idx="124">
-                  <c:v>1467.9</c:v>
-                </c:pt>
-                <c:pt idx="125">
-                  <c:v>1475.6</c:v>
-                </c:pt>
-                <c:pt idx="126">
-                  <c:v>1477.1</c:v>
-                </c:pt>
-                <c:pt idx="127">
-                  <c:v>1472.4</c:v>
-                </c:pt>
-                <c:pt idx="128">
-                  <c:v>1465.6</c:v>
-                </c:pt>
-                <c:pt idx="129">
-                  <c:v>1464.9</c:v>
-                </c:pt>
-                <c:pt idx="130">
+                <c:pt idx="188">
+                  <c:v>1439.7</c:v>
+                </c:pt>
+                <c:pt idx="189">
+                  <c:v>1466.1</c:v>
+                </c:pt>
+                <c:pt idx="190">
+                  <c:v>1476.2</c:v>
+                </c:pt>
+                <c:pt idx="191">
+                  <c:v>1468.1</c:v>
+                </c:pt>
+                <c:pt idx="192">
+                  <c:v>1476.4</c:v>
+                </c:pt>
+                <c:pt idx="193">
+                  <c:v>1495.5</c:v>
+                </c:pt>
+                <c:pt idx="194">
+                  <c:v>1469.2</c:v>
+                </c:pt>
+                <c:pt idx="195">
+                  <c:v>1466.5</c:v>
+                </c:pt>
+                <c:pt idx="196">
+                  <c:v>1481.2</c:v>
+                </c:pt>
+                <c:pt idx="197">
+                  <c:v>1493.7</c:v>
+                </c:pt>
+                <c:pt idx="198">
+                  <c:v>1497.5</c:v>
+                </c:pt>
+                <c:pt idx="199">
+                  <c:v>1493.6</c:v>
+                </c:pt>
+                <c:pt idx="200">
+                  <c:v>1483.1</c:v>
+                </c:pt>
+                <c:pt idx="201">
+                  <c:v>1501</c:v>
+                </c:pt>
+                <c:pt idx="202">
+                  <c:v>1500.6</c:v>
+                </c:pt>
+                <c:pt idx="203">
+                  <c:v>1517.3</c:v>
+                </c:pt>
+                <c:pt idx="204">
+                  <c:v>1495.2</c:v>
+                </c:pt>
+                <c:pt idx="205">
+                  <c:v>1499.7</c:v>
+                </c:pt>
+                <c:pt idx="206">
+                  <c:v>1507</c:v>
+                </c:pt>
+                <c:pt idx="207">
+                  <c:v>1508.9</c:v>
+                </c:pt>
+                <c:pt idx="208">
+                  <c:v>1515.7</c:v>
+                </c:pt>
+                <c:pt idx="209">
+                  <c:v>1530.1</c:v>
+                </c:pt>
+                <c:pt idx="210">
+                  <c:v>1501.3</c:v>
+                </c:pt>
+                <c:pt idx="211">
+                  <c:v>1519.7</c:v>
+                </c:pt>
+                <c:pt idx="212">
+                  <c:v>1505.2</c:v>
+                </c:pt>
+                <c:pt idx="213">
+                  <c:v>1506.3</c:v>
+                </c:pt>
+                <c:pt idx="214">
+                  <c:v>1504.2</c:v>
+                </c:pt>
+                <c:pt idx="215">
                   <c:v>1470.6</c:v>
                 </c:pt>
-                <c:pt idx="131">
-                  <c:v>1469.9</c:v>
-                </c:pt>
-                <c:pt idx="132">
-                  <c:v>1468.4</c:v>
-                </c:pt>
-                <c:pt idx="133">
-                  <c:v>1468</c:v>
-                </c:pt>
-                <c:pt idx="134">
-                  <c:v>1473.5</c:v>
-                </c:pt>
-                <c:pt idx="135">
-                  <c:v>1468.8</c:v>
-                </c:pt>
-                <c:pt idx="136">
-                  <c:v>1466.9</c:v>
-                </c:pt>
-                <c:pt idx="137">
-                  <c:v>1472.3</c:v>
-                </c:pt>
-                <c:pt idx="138">
-                  <c:v>1470.4</c:v>
-                </c:pt>
-                <c:pt idx="139">
-                  <c:v>1473</c:v>
-                </c:pt>
-                <c:pt idx="140">
-                  <c:v>1473.7</c:v>
-                </c:pt>
-                <c:pt idx="141">
-                  <c:v>1471</c:v>
-                </c:pt>
-                <c:pt idx="142">
-                  <c:v>1477</c:v>
-                </c:pt>
-                <c:pt idx="143">
-                  <c:v>1479.8</c:v>
-                </c:pt>
-                <c:pt idx="144">
-                  <c:v>1478.3</c:v>
-                </c:pt>
-                <c:pt idx="145">
-                  <c:v>1476.3</c:v>
-                </c:pt>
-                <c:pt idx="146">
-                  <c:v>1480.1</c:v>
-                </c:pt>
-                <c:pt idx="147">
-                  <c:v>1483.6</c:v>
-                </c:pt>
-                <c:pt idx="148">
-                  <c:v>1449.8</c:v>
-                </c:pt>
-                <c:pt idx="149">
-                  <c:v>1440.3</c:v>
-                </c:pt>
-                <c:pt idx="150">
-                  <c:v>1429.8</c:v>
-                </c:pt>
-                <c:pt idx="151">
-                  <c:v>1439</c:v>
-                </c:pt>
-                <c:pt idx="152">
-                  <c:v>1441.8</c:v>
-                </c:pt>
-                <c:pt idx="153">
-                  <c:v>1443.8</c:v>
-                </c:pt>
-                <c:pt idx="154">
-                  <c:v>1445.4</c:v>
-                </c:pt>
-                <c:pt idx="155">
-                  <c:v>1445.8</c:v>
-                </c:pt>
-                <c:pt idx="156">
-                  <c:v>1450.6</c:v>
-                </c:pt>
-                <c:pt idx="157">
-                  <c:v>1457.6</c:v>
-                </c:pt>
-                <c:pt idx="158">
-                  <c:v>1468.4</c:v>
-                </c:pt>
-                <c:pt idx="159">
-                  <c:v>1473.7</c:v>
-                </c:pt>
-                <c:pt idx="160">
-                  <c:v>1477.5</c:v>
-                </c:pt>
-                <c:pt idx="161">
-                  <c:v>1469.7</c:v>
-                </c:pt>
-                <c:pt idx="162">
-                  <c:v>1473.6</c:v>
-                </c:pt>
-                <c:pt idx="163">
-                  <c:v>1473.7</c:v>
-                </c:pt>
-                <c:pt idx="164">
-                  <c:v>1478.1</c:v>
-                </c:pt>
-                <c:pt idx="165">
-                  <c:v>1471.3</c:v>
-                </c:pt>
-                <c:pt idx="166">
-                  <c:v>1469.9</c:v>
-                </c:pt>
-                <c:pt idx="167">
-                  <c:v>1465.8</c:v>
-                </c:pt>
-                <c:pt idx="168">
-                  <c:v>1440.6</c:v>
-                </c:pt>
-                <c:pt idx="169">
-                  <c:v>1446.2</c:v>
-                </c:pt>
-                <c:pt idx="170">
-                  <c:v>1422.5</c:v>
-                </c:pt>
-                <c:pt idx="171">
-                  <c:v>1426.3</c:v>
-                </c:pt>
-                <c:pt idx="172">
-                  <c:v>1439.5</c:v>
-                </c:pt>
-                <c:pt idx="173">
-                  <c:v>1464.3</c:v>
-                </c:pt>
-                <c:pt idx="174">
-                  <c:v>1445.4</c:v>
-                </c:pt>
-                <c:pt idx="175">
-                  <c:v>1450.2</c:v>
-                </c:pt>
-                <c:pt idx="176">
-                  <c:v>1469</c:v>
-                </c:pt>
-                <c:pt idx="177">
-                  <c:v>1469.5</c:v>
-                </c:pt>
-                <c:pt idx="178">
-                  <c:v>1460.3</c:v>
-                </c:pt>
-                <c:pt idx="179">
-                  <c:v>1459.1</c:v>
-                </c:pt>
-                <c:pt idx="180">
-                  <c:v>1450.1</c:v>
-                </c:pt>
-                <c:pt idx="181">
-                  <c:v>1440.2</c:v>
-                </c:pt>
-                <c:pt idx="182">
-                  <c:v>1444.9</c:v>
-                </c:pt>
-                <c:pt idx="183">
-                  <c:v>1445.5</c:v>
-                </c:pt>
-                <c:pt idx="184">
-                  <c:v>1446.6</c:v>
-                </c:pt>
-                <c:pt idx="185">
-                  <c:v>1440</c:v>
-                </c:pt>
-                <c:pt idx="186">
-                  <c:v>1442.5</c:v>
-                </c:pt>
-                <c:pt idx="187">
-                  <c:v>1429.4</c:v>
-                </c:pt>
-                <c:pt idx="188">
-                  <c:v>1425.8</c:v>
-                </c:pt>
-                <c:pt idx="189">
-                  <c:v>1439.7</c:v>
-                </c:pt>
-                <c:pt idx="190">
-                  <c:v>1466.1</c:v>
-                </c:pt>
-                <c:pt idx="191">
-                  <c:v>1476.2</c:v>
-                </c:pt>
-                <c:pt idx="192">
-                  <c:v>1468.1</c:v>
-                </c:pt>
-                <c:pt idx="193">
-                  <c:v>1476.4</c:v>
-                </c:pt>
-                <c:pt idx="194">
-                  <c:v>1495.5</c:v>
-                </c:pt>
-                <c:pt idx="195">
-                  <c:v>1469.2</c:v>
-                </c:pt>
-                <c:pt idx="196">
-                  <c:v>1466.5</c:v>
-                </c:pt>
-                <c:pt idx="197">
-                  <c:v>1481.2</c:v>
-                </c:pt>
-                <c:pt idx="198">
-                  <c:v>1493.7</c:v>
-                </c:pt>
-                <c:pt idx="199">
-                  <c:v>1497.5</c:v>
-                </c:pt>
-                <c:pt idx="200">
-                  <c:v>1493.6</c:v>
-                </c:pt>
-                <c:pt idx="201">
-                  <c:v>1483.1</c:v>
-                </c:pt>
-                <c:pt idx="202">
-                  <c:v>1501</c:v>
-                </c:pt>
-                <c:pt idx="203">
-                  <c:v>1500.6</c:v>
-                </c:pt>
-                <c:pt idx="204">
-                  <c:v>1517.3</c:v>
-                </c:pt>
-                <c:pt idx="205">
-                  <c:v>1495.2</c:v>
-                </c:pt>
-                <c:pt idx="206">
-                  <c:v>1499.7</c:v>
-                </c:pt>
-                <c:pt idx="207">
-                  <c:v>1507</c:v>
-                </c:pt>
-                <c:pt idx="208">
-                  <c:v>1508.9</c:v>
-                </c:pt>
-                <c:pt idx="209">
-                  <c:v>1515.7</c:v>
-                </c:pt>
-                <c:pt idx="210">
-                  <c:v>1530.1</c:v>
-                </c:pt>
-                <c:pt idx="211">
-                  <c:v>1501.3</c:v>
-                </c:pt>
-                <c:pt idx="212">
-                  <c:v>1519.7</c:v>
-                </c:pt>
-                <c:pt idx="213">
-                  <c:v>1505.2</c:v>
-                </c:pt>
-                <c:pt idx="214">
-                  <c:v>1506.3</c:v>
-                </c:pt>
-                <c:pt idx="215">
-                  <c:v>1504.2</c:v>
-                </c:pt>
                 <c:pt idx="216">
-                  <c:v>1470.6</c:v>
+                  <c:v>1482.5</c:v>
                 </c:pt>
                 <c:pt idx="217">
                   <c:v>1482.5</c:v>
                 </c:pt>
                 <c:pt idx="218">
-                  <c:v>1482.5</c:v>
+                  <c:v>1489.3</c:v>
                 </c:pt>
                 <c:pt idx="219">
-                  <c:v>1489.3</c:v>
+                  <c:v>1481.2</c:v>
                 </c:pt>
                 <c:pt idx="220">
-                  <c:v>1481.2</c:v>
+                  <c:v>1474.2</c:v>
                 </c:pt>
                 <c:pt idx="221">
-                  <c:v>1474.2</c:v>
+                  <c:v>1474.6</c:v>
                 </c:pt>
                 <c:pt idx="222">
-                  <c:v>1474.6</c:v>
+                  <c:v>1483.5</c:v>
                 </c:pt>
                 <c:pt idx="223">
-                  <c:v>1483.5</c:v>
+                  <c:v>1477.2</c:v>
                 </c:pt>
                 <c:pt idx="224">
-                  <c:v>1477.2</c:v>
+                  <c:v>1468.5</c:v>
                 </c:pt>
                 <c:pt idx="225">
-                  <c:v>1468.5</c:v>
+                  <c:v>1476</c:v>
                 </c:pt>
                 <c:pt idx="226">
-                  <c:v>1476</c:v>
+                  <c:v>1481</c:v>
                 </c:pt>
                 <c:pt idx="227">
-                  <c:v>1481</c:v>
+                  <c:v>1484.5</c:v>
                 </c:pt>
                 <c:pt idx="228">
-                  <c:v>1484.5</c:v>
+                  <c:v>1472.5</c:v>
                 </c:pt>
                 <c:pt idx="229">
-                  <c:v>1472.5</c:v>
+                  <c:v>1473.6</c:v>
                 </c:pt>
                 <c:pt idx="230">
-                  <c:v>1473.6</c:v>
+                  <c:v>1479</c:v>
                 </c:pt>
                 <c:pt idx="231">
-                  <c:v>1479</c:v>
+                  <c:v>1483.3</c:v>
                 </c:pt>
                 <c:pt idx="232">
-                  <c:v>1483.3</c:v>
+                  <c:v>1462.8</c:v>
                 </c:pt>
                 <c:pt idx="233">
-                  <c:v>1462.8</c:v>
+                  <c:v>1455.1</c:v>
                 </c:pt>
                 <c:pt idx="234">
-                  <c:v>1455.1</c:v>
+                  <c:v>1454</c:v>
                 </c:pt>
                 <c:pt idx="235">
-                  <c:v>1454</c:v>
+                  <c:v>1471.7</c:v>
                 </c:pt>
                 <c:pt idx="236">
-                  <c:v>1471.7</c:v>
+                  <c:v>1472.4</c:v>
                 </c:pt>
                 <c:pt idx="237">
-                  <c:v>1472.4</c:v>
+                  <c:v>1489.9</c:v>
                 </c:pt>
                 <c:pt idx="238">
-                  <c:v>1489.9</c:v>
+                  <c:v>1490.6</c:v>
                 </c:pt>
                 <c:pt idx="239">
-                  <c:v>1490.6</c:v>
+                  <c:v>1491</c:v>
                 </c:pt>
                 <c:pt idx="240">
-                  <c:v>1491</c:v>
+                  <c:v>1500.8</c:v>
                 </c:pt>
                 <c:pt idx="241">
-                  <c:v>1500.8</c:v>
+                  <c:v>1500.3</c:v>
                 </c:pt>
                 <c:pt idx="242">
-                  <c:v>1500.3</c:v>
+                  <c:v>1507.8</c:v>
                 </c:pt>
                 <c:pt idx="243">
-                  <c:v>1507.8</c:v>
+                  <c:v>1506.8</c:v>
                 </c:pt>
                 <c:pt idx="244">
-                  <c:v>1506.8</c:v>
+                  <c:v>1506.1</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2556,739 +2556,739 @@
               <c:strCache>
                 <c:ptCount val="245"/>
                 <c:pt idx="0">
-                  <c:v>2025-05-20</c:v>
+                  <c:v>2025-05-21</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2025-05-21</c:v>
+                  <c:v>2025-05-22</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>2025-05-22</c:v>
+                  <c:v>2025-05-23</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>2025-05-23</c:v>
+                  <c:v>2025-05-26</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>2025-05-26</c:v>
+                  <c:v>2025-05-27</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>2025-05-27</c:v>
+                  <c:v>2025-05-28</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>2025-05-28</c:v>
+                  <c:v>2025-05-29</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>2025-05-29</c:v>
+                  <c:v>2025-05-30</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>2025-05-30</c:v>
+                  <c:v>2025-06-02</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>2025-06-02</c:v>
+                  <c:v>2025-06-04</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>2025-06-04</c:v>
+                  <c:v>2025-06-05</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>2025-06-05</c:v>
+                  <c:v>2025-06-09</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>2025-06-09</c:v>
+                  <c:v>2025-06-10</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>2025-06-10</c:v>
+                  <c:v>2025-06-11</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>2025-06-11</c:v>
+                  <c:v>2025-06-12</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>2025-06-12</c:v>
+                  <c:v>2025-06-13</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>2025-06-13</c:v>
+                  <c:v>2025-06-16</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>2025-06-16</c:v>
+                  <c:v>2025-06-17</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>2025-06-17</c:v>
+                  <c:v>2025-06-18</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>2025-06-18</c:v>
+                  <c:v>2025-06-19</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>2025-06-19</c:v>
+                  <c:v>2025-06-20</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>2025-06-20</c:v>
+                  <c:v>2025-06-23</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>2025-06-23</c:v>
+                  <c:v>2025-06-24</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>2025-06-24</c:v>
+                  <c:v>2025-06-25</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>2025-06-25</c:v>
+                  <c:v>2025-06-26</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>2025-06-26</c:v>
+                  <c:v>2025-06-27</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>2025-06-27</c:v>
+                  <c:v>2025-06-30</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>2025-06-30</c:v>
+                  <c:v>2025-07-01</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>2025-07-01</c:v>
+                  <c:v>2025-07-02</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>2025-07-02</c:v>
+                  <c:v>2025-07-03</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>2025-07-03</c:v>
+                  <c:v>2025-07-04</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>2025-07-04</c:v>
+                  <c:v>2025-07-07</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>2025-07-07</c:v>
+                  <c:v>2025-07-08</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>2025-07-08</c:v>
+                  <c:v>2025-07-09</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>2025-07-09</c:v>
+                  <c:v>2025-07-10</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>2025-07-10</c:v>
+                  <c:v>2025-07-11</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>2025-07-11</c:v>
+                  <c:v>2025-07-14</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>2025-07-14</c:v>
+                  <c:v>2025-07-15</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>2025-07-15</c:v>
+                  <c:v>2025-07-16</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>2025-07-16</c:v>
+                  <c:v>2025-07-17</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>2025-07-17</c:v>
+                  <c:v>2025-07-18</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>2025-07-18</c:v>
+                  <c:v>2025-07-21</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>2025-07-21</c:v>
+                  <c:v>2025-07-22</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>2025-07-22</c:v>
+                  <c:v>2025-07-23</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>2025-07-23</c:v>
+                  <c:v>2025-07-24</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>2025-07-24</c:v>
+                  <c:v>2025-07-25</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>2025-07-25</c:v>
+                  <c:v>2025-07-28</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>2025-07-28</c:v>
+                  <c:v>2025-07-29</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>2025-07-29</c:v>
+                  <c:v>2025-07-30</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>2025-07-30</c:v>
+                  <c:v>2025-07-31</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>2025-07-31</c:v>
+                  <c:v>2025-08-01</c:v>
                 </c:pt>
                 <c:pt idx="51">
-                  <c:v>2025-08-01</c:v>
+                  <c:v>2025-08-04</c:v>
                 </c:pt>
                 <c:pt idx="52">
-                  <c:v>2025-08-04</c:v>
+                  <c:v>2025-08-05</c:v>
                 </c:pt>
                 <c:pt idx="53">
-                  <c:v>2025-08-05</c:v>
+                  <c:v>2025-08-06</c:v>
                 </c:pt>
                 <c:pt idx="54">
-                  <c:v>2025-08-06</c:v>
+                  <c:v>2025-08-07</c:v>
                 </c:pt>
                 <c:pt idx="55">
-                  <c:v>2025-08-07</c:v>
+                  <c:v>2025-08-08</c:v>
                 </c:pt>
                 <c:pt idx="56">
-                  <c:v>2025-08-08</c:v>
+                  <c:v>2025-08-11</c:v>
                 </c:pt>
                 <c:pt idx="57">
-                  <c:v>2025-08-11</c:v>
+                  <c:v>2025-08-12</c:v>
                 </c:pt>
                 <c:pt idx="58">
-                  <c:v>2025-08-12</c:v>
+                  <c:v>2025-08-13</c:v>
                 </c:pt>
                 <c:pt idx="59">
-                  <c:v>2025-08-13</c:v>
+                  <c:v>2025-08-14</c:v>
                 </c:pt>
                 <c:pt idx="60">
-                  <c:v>2025-08-14</c:v>
+                  <c:v>2025-08-18</c:v>
                 </c:pt>
                 <c:pt idx="61">
-                  <c:v>2025-08-18</c:v>
+                  <c:v>2025-08-19</c:v>
                 </c:pt>
                 <c:pt idx="62">
-                  <c:v>2025-08-19</c:v>
+                  <c:v>2025-08-20</c:v>
                 </c:pt>
                 <c:pt idx="63">
-                  <c:v>2025-08-20</c:v>
+                  <c:v>2025-08-21</c:v>
                 </c:pt>
                 <c:pt idx="64">
-                  <c:v>2025-08-21</c:v>
+                  <c:v>2025-08-22</c:v>
                 </c:pt>
                 <c:pt idx="65">
-                  <c:v>2025-08-22</c:v>
+                  <c:v>2025-08-25</c:v>
                 </c:pt>
                 <c:pt idx="66">
-                  <c:v>2025-08-25</c:v>
+                  <c:v>2025-08-26</c:v>
                 </c:pt>
                 <c:pt idx="67">
-                  <c:v>2025-08-26</c:v>
+                  <c:v>2025-08-27</c:v>
                 </c:pt>
                 <c:pt idx="68">
-                  <c:v>2025-08-27</c:v>
+                  <c:v>2025-08-28</c:v>
                 </c:pt>
                 <c:pt idx="69">
-                  <c:v>2025-08-28</c:v>
+                  <c:v>2025-08-29</c:v>
                 </c:pt>
                 <c:pt idx="70">
-                  <c:v>2025-08-29</c:v>
+                  <c:v>2025-09-01</c:v>
                 </c:pt>
                 <c:pt idx="71">
-                  <c:v>2025-09-01</c:v>
+                  <c:v>2025-09-02</c:v>
                 </c:pt>
                 <c:pt idx="72">
-                  <c:v>2025-09-02</c:v>
+                  <c:v>2025-09-03</c:v>
                 </c:pt>
                 <c:pt idx="73">
-                  <c:v>2025-09-03</c:v>
+                  <c:v>2025-09-04</c:v>
                 </c:pt>
                 <c:pt idx="74">
-                  <c:v>2025-09-04</c:v>
+                  <c:v>2025-09-05</c:v>
                 </c:pt>
                 <c:pt idx="75">
-                  <c:v>2025-09-05</c:v>
+                  <c:v>2025-09-08</c:v>
                 </c:pt>
                 <c:pt idx="76">
-                  <c:v>2025-09-08</c:v>
+                  <c:v>2025-09-09</c:v>
                 </c:pt>
                 <c:pt idx="77">
-                  <c:v>2025-09-09</c:v>
+                  <c:v>2025-09-10</c:v>
                 </c:pt>
                 <c:pt idx="78">
-                  <c:v>2025-09-10</c:v>
+                  <c:v>2025-09-11</c:v>
                 </c:pt>
                 <c:pt idx="79">
-                  <c:v>2025-09-11</c:v>
+                  <c:v>2025-09-12</c:v>
                 </c:pt>
                 <c:pt idx="80">
-                  <c:v>2025-09-12</c:v>
+                  <c:v>2025-09-15</c:v>
                 </c:pt>
                 <c:pt idx="81">
-                  <c:v>2025-09-15</c:v>
+                  <c:v>2025-09-16</c:v>
                 </c:pt>
                 <c:pt idx="82">
-                  <c:v>2025-09-16</c:v>
+                  <c:v>2025-09-17</c:v>
                 </c:pt>
                 <c:pt idx="83">
-                  <c:v>2025-09-17</c:v>
+                  <c:v>2025-09-18</c:v>
                 </c:pt>
                 <c:pt idx="84">
-                  <c:v>2025-09-18</c:v>
+                  <c:v>2025-09-19</c:v>
                 </c:pt>
                 <c:pt idx="85">
-                  <c:v>2025-09-19</c:v>
+                  <c:v>2025-09-22</c:v>
                 </c:pt>
                 <c:pt idx="86">
-                  <c:v>2025-09-22</c:v>
+                  <c:v>2025-09-23</c:v>
                 </c:pt>
                 <c:pt idx="87">
-                  <c:v>2025-09-23</c:v>
+                  <c:v>2025-09-24</c:v>
                 </c:pt>
                 <c:pt idx="88">
-                  <c:v>2025-09-24</c:v>
+                  <c:v>2025-09-25</c:v>
                 </c:pt>
                 <c:pt idx="89">
-                  <c:v>2025-09-25</c:v>
+                  <c:v>2025-09-26</c:v>
                 </c:pt>
                 <c:pt idx="90">
-                  <c:v>2025-09-26</c:v>
+                  <c:v>2025-09-29</c:v>
                 </c:pt>
                 <c:pt idx="91">
-                  <c:v>2025-09-29</c:v>
+                  <c:v>2025-09-30</c:v>
                 </c:pt>
                 <c:pt idx="92">
-                  <c:v>2025-09-30</c:v>
+                  <c:v>2025-10-01</c:v>
                 </c:pt>
                 <c:pt idx="93">
-                  <c:v>2025-10-01</c:v>
+                  <c:v>2025-10-02</c:v>
                 </c:pt>
                 <c:pt idx="94">
-                  <c:v>2025-10-02</c:v>
+                  <c:v>2025-10-10</c:v>
                 </c:pt>
                 <c:pt idx="95">
-                  <c:v>2025-10-10</c:v>
+                  <c:v>2025-10-13</c:v>
                 </c:pt>
                 <c:pt idx="96">
-                  <c:v>2025-10-13</c:v>
+                  <c:v>2025-10-14</c:v>
                 </c:pt>
                 <c:pt idx="97">
-                  <c:v>2025-10-14</c:v>
+                  <c:v>2025-10-15</c:v>
                 </c:pt>
                 <c:pt idx="98">
-                  <c:v>2025-10-15</c:v>
+                  <c:v>2025-10-16</c:v>
                 </c:pt>
                 <c:pt idx="99">
-                  <c:v>2025-10-16</c:v>
+                  <c:v>2025-10-17</c:v>
                 </c:pt>
                 <c:pt idx="100">
-                  <c:v>2025-10-17</c:v>
+                  <c:v>2025-10-20</c:v>
                 </c:pt>
                 <c:pt idx="101">
-                  <c:v>2025-10-20</c:v>
+                  <c:v>2025-10-21</c:v>
                 </c:pt>
                 <c:pt idx="102">
-                  <c:v>2025-10-21</c:v>
+                  <c:v>2025-10-22</c:v>
                 </c:pt>
                 <c:pt idx="103">
-                  <c:v>2025-10-22</c:v>
+                  <c:v>2025-10-23</c:v>
                 </c:pt>
                 <c:pt idx="104">
-                  <c:v>2025-10-23</c:v>
+                  <c:v>2025-10-24</c:v>
                 </c:pt>
                 <c:pt idx="105">
-                  <c:v>2025-10-24</c:v>
+                  <c:v>2025-10-27</c:v>
                 </c:pt>
                 <c:pt idx="106">
-                  <c:v>2025-10-27</c:v>
+                  <c:v>2025-10-28</c:v>
                 </c:pt>
                 <c:pt idx="107">
-                  <c:v>2025-10-28</c:v>
+                  <c:v>2025-10-29</c:v>
                 </c:pt>
                 <c:pt idx="108">
-                  <c:v>2025-10-29</c:v>
+                  <c:v>2025-10-30</c:v>
                 </c:pt>
                 <c:pt idx="109">
-                  <c:v>2025-10-30</c:v>
+                  <c:v>2025-10-31</c:v>
                 </c:pt>
                 <c:pt idx="110">
-                  <c:v>2025-10-31</c:v>
+                  <c:v>2025-11-03</c:v>
                 </c:pt>
                 <c:pt idx="111">
-                  <c:v>2025-11-03</c:v>
+                  <c:v>2025-11-04</c:v>
                 </c:pt>
                 <c:pt idx="112">
-                  <c:v>2025-11-04</c:v>
+                  <c:v>2025-11-05</c:v>
                 </c:pt>
                 <c:pt idx="113">
-                  <c:v>2025-11-05</c:v>
+                  <c:v>2025-11-06</c:v>
                 </c:pt>
                 <c:pt idx="114">
-                  <c:v>2025-11-06</c:v>
+                  <c:v>2025-11-07</c:v>
                 </c:pt>
                 <c:pt idx="115">
-                  <c:v>2025-11-07</c:v>
+                  <c:v>2025-11-10</c:v>
                 </c:pt>
                 <c:pt idx="116">
-                  <c:v>2025-11-10</c:v>
+                  <c:v>2025-11-11</c:v>
                 </c:pt>
                 <c:pt idx="117">
-                  <c:v>2025-11-11</c:v>
+                  <c:v>2025-11-12</c:v>
                 </c:pt>
                 <c:pt idx="118">
-                  <c:v>2025-11-12</c:v>
+                  <c:v>2025-11-13</c:v>
                 </c:pt>
                 <c:pt idx="119">
-                  <c:v>2025-11-13</c:v>
+                  <c:v>2025-11-14</c:v>
                 </c:pt>
                 <c:pt idx="120">
-                  <c:v>2025-11-14</c:v>
+                  <c:v>2025-11-17</c:v>
                 </c:pt>
                 <c:pt idx="121">
-                  <c:v>2025-11-17</c:v>
+                  <c:v>2025-11-18</c:v>
                 </c:pt>
                 <c:pt idx="122">
-                  <c:v>2025-11-18</c:v>
+                  <c:v>2025-11-19</c:v>
                 </c:pt>
                 <c:pt idx="123">
-                  <c:v>2025-11-19</c:v>
+                  <c:v>2025-11-20</c:v>
                 </c:pt>
                 <c:pt idx="124">
-                  <c:v>2025-11-20</c:v>
+                  <c:v>2025-11-21</c:v>
                 </c:pt>
                 <c:pt idx="125">
-                  <c:v>2025-11-21</c:v>
+                  <c:v>2025-11-24</c:v>
                 </c:pt>
                 <c:pt idx="126">
-                  <c:v>2025-11-24</c:v>
+                  <c:v>2025-11-25</c:v>
                 </c:pt>
                 <c:pt idx="127">
-                  <c:v>2025-11-25</c:v>
+                  <c:v>2025-11-26</c:v>
                 </c:pt>
                 <c:pt idx="128">
-                  <c:v>2025-11-26</c:v>
+                  <c:v>2025-11-27</c:v>
                 </c:pt>
                 <c:pt idx="129">
-                  <c:v>2025-11-27</c:v>
+                  <c:v>2025-11-28</c:v>
                 </c:pt>
                 <c:pt idx="130">
-                  <c:v>2025-11-28</c:v>
+                  <c:v>2025-12-01</c:v>
                 </c:pt>
                 <c:pt idx="131">
-                  <c:v>2025-12-01</c:v>
+                  <c:v>2025-12-02</c:v>
                 </c:pt>
                 <c:pt idx="132">
-                  <c:v>2025-12-02</c:v>
+                  <c:v>2025-12-03</c:v>
                 </c:pt>
                 <c:pt idx="133">
-                  <c:v>2025-12-03</c:v>
+                  <c:v>2025-12-04</c:v>
                 </c:pt>
                 <c:pt idx="134">
-                  <c:v>2025-12-04</c:v>
+                  <c:v>2025-12-05</c:v>
                 </c:pt>
                 <c:pt idx="135">
-                  <c:v>2025-12-05</c:v>
+                  <c:v>2025-12-08</c:v>
                 </c:pt>
                 <c:pt idx="136">
-                  <c:v>2025-12-08</c:v>
+                  <c:v>2025-12-09</c:v>
                 </c:pt>
                 <c:pt idx="137">
-                  <c:v>2025-12-09</c:v>
+                  <c:v>2025-12-10</c:v>
                 </c:pt>
                 <c:pt idx="138">
-                  <c:v>2025-12-10</c:v>
+                  <c:v>2025-12-11</c:v>
                 </c:pt>
                 <c:pt idx="139">
-                  <c:v>2025-12-11</c:v>
+                  <c:v>2025-12-12</c:v>
                 </c:pt>
                 <c:pt idx="140">
-                  <c:v>2025-12-12</c:v>
+                  <c:v>2025-12-15</c:v>
                 </c:pt>
                 <c:pt idx="141">
-                  <c:v>2025-12-15</c:v>
+                  <c:v>2025-12-16</c:v>
                 </c:pt>
                 <c:pt idx="142">
-                  <c:v>2025-12-16</c:v>
+                  <c:v>2025-12-17</c:v>
                 </c:pt>
                 <c:pt idx="143">
-                  <c:v>2025-12-17</c:v>
+                  <c:v>2025-12-18</c:v>
                 </c:pt>
                 <c:pt idx="144">
-                  <c:v>2025-12-18</c:v>
+                  <c:v>2025-12-19</c:v>
                 </c:pt>
                 <c:pt idx="145">
-                  <c:v>2025-12-19</c:v>
+                  <c:v>2025-12-22</c:v>
                 </c:pt>
                 <c:pt idx="146">
-                  <c:v>2025-12-22</c:v>
+                  <c:v>2025-12-23</c:v>
                 </c:pt>
                 <c:pt idx="147">
-                  <c:v>2025-12-23</c:v>
+                  <c:v>2025-12-24</c:v>
                 </c:pt>
                 <c:pt idx="148">
-                  <c:v>2025-12-24</c:v>
+                  <c:v>2025-12-26</c:v>
                 </c:pt>
                 <c:pt idx="149">
-                  <c:v>2025-12-26</c:v>
+                  <c:v>2025-12-29</c:v>
                 </c:pt>
                 <c:pt idx="150">
-                  <c:v>2025-12-29</c:v>
+                  <c:v>2025-12-30</c:v>
                 </c:pt>
                 <c:pt idx="151">
-                  <c:v>2025-12-30</c:v>
+                  <c:v>2026-01-02</c:v>
                 </c:pt>
                 <c:pt idx="152">
-                  <c:v>2026-01-02</c:v>
+                  <c:v>2026-01-05</c:v>
                 </c:pt>
                 <c:pt idx="153">
-                  <c:v>2026-01-05</c:v>
+                  <c:v>2026-01-06</c:v>
                 </c:pt>
                 <c:pt idx="154">
-                  <c:v>2026-01-06</c:v>
+                  <c:v>2026-01-07</c:v>
                 </c:pt>
                 <c:pt idx="155">
-                  <c:v>2026-01-07</c:v>
+                  <c:v>2026-01-08</c:v>
                 </c:pt>
                 <c:pt idx="156">
-                  <c:v>2026-01-08</c:v>
+                  <c:v>2026-01-09</c:v>
                 </c:pt>
                 <c:pt idx="157">
-                  <c:v>2026-01-09</c:v>
+                  <c:v>2026-01-12</c:v>
                 </c:pt>
                 <c:pt idx="158">
-                  <c:v>2026-01-12</c:v>
+                  <c:v>2026-01-13</c:v>
                 </c:pt>
                 <c:pt idx="159">
-                  <c:v>2026-01-13</c:v>
+                  <c:v>2026-01-14</c:v>
                 </c:pt>
                 <c:pt idx="160">
-                  <c:v>2026-01-14</c:v>
+                  <c:v>2026-01-15</c:v>
                 </c:pt>
                 <c:pt idx="161">
-                  <c:v>2026-01-15</c:v>
+                  <c:v>2026-01-16</c:v>
                 </c:pt>
                 <c:pt idx="162">
-                  <c:v>2026-01-16</c:v>
+                  <c:v>2026-01-19</c:v>
                 </c:pt>
                 <c:pt idx="163">
-                  <c:v>2026-01-19</c:v>
+                  <c:v>2026-01-20</c:v>
                 </c:pt>
                 <c:pt idx="164">
-                  <c:v>2026-01-20</c:v>
+                  <c:v>2026-01-21</c:v>
                 </c:pt>
                 <c:pt idx="165">
-                  <c:v>2026-01-21</c:v>
+                  <c:v>2026-01-22</c:v>
                 </c:pt>
                 <c:pt idx="166">
-                  <c:v>2026-01-22</c:v>
+                  <c:v>2026-01-23</c:v>
                 </c:pt>
                 <c:pt idx="167">
-                  <c:v>2026-01-23</c:v>
+                  <c:v>2026-01-26</c:v>
                 </c:pt>
                 <c:pt idx="168">
-                  <c:v>2026-01-26</c:v>
+                  <c:v>2026-01-27</c:v>
                 </c:pt>
                 <c:pt idx="169">
-                  <c:v>2026-01-27</c:v>
+                  <c:v>2026-01-28</c:v>
                 </c:pt>
                 <c:pt idx="170">
-                  <c:v>2026-01-28</c:v>
+                  <c:v>2026-01-29</c:v>
                 </c:pt>
                 <c:pt idx="171">
-                  <c:v>2026-01-29</c:v>
+                  <c:v>2026-01-30</c:v>
                 </c:pt>
                 <c:pt idx="172">
-                  <c:v>2026-01-30</c:v>
+                  <c:v>2026-02-02</c:v>
                 </c:pt>
                 <c:pt idx="173">
-                  <c:v>2026-02-02</c:v>
+                  <c:v>2026-02-03</c:v>
                 </c:pt>
                 <c:pt idx="174">
-                  <c:v>2026-02-03</c:v>
+                  <c:v>2026-02-04</c:v>
                 </c:pt>
                 <c:pt idx="175">
-                  <c:v>2026-02-04</c:v>
+                  <c:v>2026-02-05</c:v>
                 </c:pt>
                 <c:pt idx="176">
-                  <c:v>2026-02-05</c:v>
+                  <c:v>2026-02-06</c:v>
                 </c:pt>
                 <c:pt idx="177">
-                  <c:v>2026-02-06</c:v>
+                  <c:v>2026-02-09</c:v>
                 </c:pt>
                 <c:pt idx="178">
-                  <c:v>2026-02-09</c:v>
+                  <c:v>2026-02-10</c:v>
                 </c:pt>
                 <c:pt idx="179">
-                  <c:v>2026-02-10</c:v>
+                  <c:v>2026-02-11</c:v>
                 </c:pt>
                 <c:pt idx="180">
-                  <c:v>2026-02-11</c:v>
+                  <c:v>2026-02-12</c:v>
                 </c:pt>
                 <c:pt idx="181">
-                  <c:v>2026-02-12</c:v>
+                  <c:v>2026-02-13</c:v>
                 </c:pt>
                 <c:pt idx="182">
-                  <c:v>2026-02-13</c:v>
+                  <c:v>2026-02-19</c:v>
                 </c:pt>
                 <c:pt idx="183">
-                  <c:v>2026-02-19</c:v>
+                  <c:v>2026-02-20</c:v>
                 </c:pt>
                 <c:pt idx="184">
-                  <c:v>2026-02-20</c:v>
+                  <c:v>2026-02-23</c:v>
                 </c:pt>
                 <c:pt idx="185">
-                  <c:v>2026-02-23</c:v>
+                  <c:v>2026-02-24</c:v>
                 </c:pt>
                 <c:pt idx="186">
-                  <c:v>2026-02-24</c:v>
+                  <c:v>2026-02-25</c:v>
                 </c:pt>
                 <c:pt idx="187">
-                  <c:v>2026-02-25</c:v>
+                  <c:v>2026-02-26</c:v>
                 </c:pt>
                 <c:pt idx="188">
-                  <c:v>2026-02-26</c:v>
+                  <c:v>2026-02-27</c:v>
                 </c:pt>
                 <c:pt idx="189">
-                  <c:v>2026-02-27</c:v>
+                  <c:v>2026-03-03</c:v>
                 </c:pt>
                 <c:pt idx="190">
-                  <c:v>2026-03-03</c:v>
+                  <c:v>2026-03-04</c:v>
                 </c:pt>
                 <c:pt idx="191">
-                  <c:v>2026-03-04</c:v>
+                  <c:v>2026-03-05</c:v>
                 </c:pt>
                 <c:pt idx="192">
-                  <c:v>2026-03-05</c:v>
+                  <c:v>2026-03-06</c:v>
                 </c:pt>
                 <c:pt idx="193">
-                  <c:v>2026-03-06</c:v>
+                  <c:v>2026-03-09</c:v>
                 </c:pt>
                 <c:pt idx="194">
-                  <c:v>2026-03-09</c:v>
+                  <c:v>2026-03-10</c:v>
                 </c:pt>
                 <c:pt idx="195">
-                  <c:v>2026-03-10</c:v>
+                  <c:v>2026-03-11</c:v>
                 </c:pt>
                 <c:pt idx="196">
-                  <c:v>2026-03-11</c:v>
+                  <c:v>2026-03-12</c:v>
                 </c:pt>
                 <c:pt idx="197">
-                  <c:v>2026-03-12</c:v>
+                  <c:v>2026-03-13</c:v>
                 </c:pt>
                 <c:pt idx="198">
-                  <c:v>2026-03-13</c:v>
+                  <c:v>2026-03-16</c:v>
                 </c:pt>
                 <c:pt idx="199">
-                  <c:v>2026-03-16</c:v>
+                  <c:v>2026-03-17</c:v>
                 </c:pt>
                 <c:pt idx="200">
-                  <c:v>2026-03-17</c:v>
+                  <c:v>2026-03-18</c:v>
                 </c:pt>
                 <c:pt idx="201">
-                  <c:v>2026-03-18</c:v>
+                  <c:v>2026-03-19</c:v>
                 </c:pt>
                 <c:pt idx="202">
-                  <c:v>2026-03-19</c:v>
+                  <c:v>2026-03-20</c:v>
                 </c:pt>
                 <c:pt idx="203">
-                  <c:v>2026-03-20</c:v>
+                  <c:v>2026-03-23</c:v>
                 </c:pt>
                 <c:pt idx="204">
-                  <c:v>2026-03-23</c:v>
+                  <c:v>2026-03-24</c:v>
                 </c:pt>
                 <c:pt idx="205">
-                  <c:v>2026-03-24</c:v>
+                  <c:v>2026-03-25</c:v>
                 </c:pt>
                 <c:pt idx="206">
-                  <c:v>2026-03-25</c:v>
+                  <c:v>2026-03-26</c:v>
                 </c:pt>
                 <c:pt idx="207">
-                  <c:v>2026-03-26</c:v>
+                  <c:v>2026-03-27</c:v>
                 </c:pt>
                 <c:pt idx="208">
-                  <c:v>2026-03-27</c:v>
+                  <c:v>2026-03-30</c:v>
                 </c:pt>
                 <c:pt idx="209">
-                  <c:v>2026-03-30</c:v>
+                  <c:v>2026-03-31</c:v>
                 </c:pt>
                 <c:pt idx="210">
-                  <c:v>2026-03-31</c:v>
+                  <c:v>2026-04-01</c:v>
                 </c:pt>
                 <c:pt idx="211">
-                  <c:v>2026-04-01</c:v>
+                  <c:v>2026-04-02</c:v>
                 </c:pt>
                 <c:pt idx="212">
-                  <c:v>2026-04-02</c:v>
+                  <c:v>2026-04-03</c:v>
                 </c:pt>
                 <c:pt idx="213">
-                  <c:v>2026-04-03</c:v>
+                  <c:v>2026-04-06</c:v>
                 </c:pt>
                 <c:pt idx="214">
-                  <c:v>2026-04-06</c:v>
+                  <c:v>2026-04-07</c:v>
                 </c:pt>
                 <c:pt idx="215">
-                  <c:v>2026-04-07</c:v>
+                  <c:v>2026-04-08</c:v>
                 </c:pt>
                 <c:pt idx="216">
-                  <c:v>2026-04-08</c:v>
+                  <c:v>2026-04-09</c:v>
                 </c:pt>
                 <c:pt idx="217">
-                  <c:v>2026-04-09</c:v>
+                  <c:v>2026-04-10</c:v>
                 </c:pt>
                 <c:pt idx="218">
-                  <c:v>2026-04-10</c:v>
+                  <c:v>2026-04-13</c:v>
                 </c:pt>
                 <c:pt idx="219">
-                  <c:v>2026-04-13</c:v>
+                  <c:v>2026-04-14</c:v>
                 </c:pt>
                 <c:pt idx="220">
-                  <c:v>2026-04-14</c:v>
+                  <c:v>2026-04-15</c:v>
                 </c:pt>
                 <c:pt idx="221">
-                  <c:v>2026-04-15</c:v>
+                  <c:v>2026-04-16</c:v>
                 </c:pt>
                 <c:pt idx="222">
-                  <c:v>2026-04-16</c:v>
+                  <c:v>2026-04-17</c:v>
                 </c:pt>
                 <c:pt idx="223">
-                  <c:v>2026-04-17</c:v>
+                  <c:v>2026-04-20</c:v>
                 </c:pt>
                 <c:pt idx="224">
-                  <c:v>2026-04-20</c:v>
+                  <c:v>2026-04-21</c:v>
                 </c:pt>
                 <c:pt idx="225">
-                  <c:v>2026-04-21</c:v>
+                  <c:v>2026-04-22</c:v>
                 </c:pt>
                 <c:pt idx="226">
-                  <c:v>2026-04-22</c:v>
+                  <c:v>2026-04-23</c:v>
                 </c:pt>
                 <c:pt idx="227">
-                  <c:v>2026-04-23</c:v>
+                  <c:v>2026-04-24</c:v>
                 </c:pt>
                 <c:pt idx="228">
-                  <c:v>2026-04-24</c:v>
+                  <c:v>2026-04-27</c:v>
                 </c:pt>
                 <c:pt idx="229">
-                  <c:v>2026-04-27</c:v>
+                  <c:v>2026-04-28</c:v>
                 </c:pt>
                 <c:pt idx="230">
-                  <c:v>2026-04-28</c:v>
+                  <c:v>2026-04-29</c:v>
                 </c:pt>
                 <c:pt idx="231">
-                  <c:v>2026-04-29</c:v>
+                  <c:v>2026-04-30</c:v>
                 </c:pt>
                 <c:pt idx="232">
-                  <c:v>2026-04-30</c:v>
+                  <c:v>2026-05-04</c:v>
                 </c:pt>
                 <c:pt idx="233">
-                  <c:v>2026-05-04</c:v>
+                  <c:v>2026-05-06</c:v>
                 </c:pt>
                 <c:pt idx="234">
-                  <c:v>2026-05-06</c:v>
+                  <c:v>2026-05-07</c:v>
                 </c:pt>
                 <c:pt idx="235">
-                  <c:v>2026-05-07</c:v>
+                  <c:v>2026-05-08</c:v>
                 </c:pt>
                 <c:pt idx="236">
-                  <c:v>2026-05-08</c:v>
+                  <c:v>2026-05-11</c:v>
                 </c:pt>
                 <c:pt idx="237">
-                  <c:v>2026-05-11</c:v>
+                  <c:v>2026-05-12</c:v>
                 </c:pt>
                 <c:pt idx="238">
-                  <c:v>2026-05-12</c:v>
+                  <c:v>2026-05-13</c:v>
                 </c:pt>
                 <c:pt idx="239">
-                  <c:v>2026-05-13</c:v>
+                  <c:v>2026-05-14</c:v>
                 </c:pt>
                 <c:pt idx="240">
-                  <c:v>2026-05-14</c:v>
+                  <c:v>2026-05-15</c:v>
                 </c:pt>
                 <c:pt idx="241">
-                  <c:v>2026-05-15</c:v>
+                  <c:v>2026-05-18</c:v>
                 </c:pt>
                 <c:pt idx="242">
-                  <c:v>2026-05-18</c:v>
+                  <c:v>2026-05-19</c:v>
                 </c:pt>
                 <c:pt idx="243">
-                  <c:v>2026-05-19</c:v>
+                  <c:v>2026-05-20</c:v>
                 </c:pt>
                 <c:pt idx="244">
-                  <c:v>2026-05-20</c:v>
+                  <c:v>2026-05-21</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -3300,739 +3300,739 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="245"/>
                 <c:pt idx="0">
-                  <c:v>1394.4</c:v>
+                  <c:v>1371.8</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1371.8</c:v>
+                  <c:v>1382.7</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1382.7</c:v>
+                  <c:v>1366.5</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1366.5</c:v>
+                  <c:v>1370.5</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1370.5</c:v>
+                  <c:v>1376.5</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1376.5</c:v>
+                  <c:v>1376</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1376</c:v>
+                  <c:v>1371.1</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1371.1</c:v>
+                  <c:v>1383.1</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1383.1</c:v>
+                  <c:v>1377.1</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1377.1</c:v>
+                  <c:v>1364.1</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1364.1</c:v>
+                  <c:v>1356.5</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1356.5</c:v>
+                  <c:v>1354.2</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1354.2</c:v>
+                  <c:v>1368</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>1368</c:v>
+                  <c:v>1370.9</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>1370.9</c:v>
+                  <c:v>1357.1</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>1357.1</c:v>
+                  <c:v>1363.5</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>1363.5</c:v>
+                  <c:v>1358.1</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>1358.1</c:v>
+                  <c:v>1374</c:v>
                 </c:pt>
                 <c:pt idx="18">
+                  <c:v>1372.3</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>1379.8</c:v>
+                </c:pt>
+                <c:pt idx="20">
                   <c:v>1374</c:v>
                 </c:pt>
-                <c:pt idx="19">
-                  <c:v>1372.3</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>1379.8</c:v>
-                </c:pt>
                 <c:pt idx="21">
-                  <c:v>1374</c:v>
+                  <c:v>1382</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>1382</c:v>
+                  <c:v>1361.4</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>1361.4</c:v>
+                  <c:v>1361.2</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>1361.2</c:v>
+                  <c:v>1352.9</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>1352.9</c:v>
+                  <c:v>1361.3</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>1361.3</c:v>
+                  <c:v>1355.3</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>1355.3</c:v>
+                  <c:v>1359</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>1359</c:v>
+                  <c:v>1355.5</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>1355.5</c:v>
+                  <c:v>1365.5</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>1365.5</c:v>
+                  <c:v>1362.5</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>1362.5</c:v>
+                  <c:v>1377</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>1377</c:v>
+                  <c:v>1373.2</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>1373.2</c:v>
+                  <c:v>1375.2</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>1375.2</c:v>
+                  <c:v>1373.9</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>1373.9</c:v>
+                  <c:v>1375.8</c:v>
                 </c:pt>
                 <c:pt idx="36">
+                  <c:v>1383</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>1388.2</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>1387</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>1392.2</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>1391.6</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>1382.2</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>1381</c:v>
+                </c:pt>
+                <c:pt idx="43">
                   <c:v>1375.8</c:v>
                 </c:pt>
-                <c:pt idx="37">
-                  <c:v>1383</c:v>
-                </c:pt>
-                <c:pt idx="38">
-                  <c:v>1388.2</c:v>
-                </c:pt>
-                <c:pt idx="39">
+                <c:pt idx="44">
+                  <c:v>1371.3</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>1383.7</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>1389.1</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>1389.7</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>1391.8</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>1392</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>1388.3</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>1386.5</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>1386.3</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>1386.4</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>1386</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>1387.5</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>1390.5</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>1384.4</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>1379.4</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>1389.5</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>1388.1</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>1392</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>1397</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>1398.8</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>1383.5</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>1390.3</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>1393.2</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>1394.2</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>1384.8</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>1389.8</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>1394</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>1395.9</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>1389.7</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>1395.3</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>1388.4</c:v>
+                </c:pt>
+                <c:pt idx="75">
                   <c:v>1387</c:v>
                 </c:pt>
-                <c:pt idx="40">
-                  <c:v>1392.2</c:v>
-                </c:pt>
-                <c:pt idx="41">
-                  <c:v>1391.6</c:v>
-                </c:pt>
-                <c:pt idx="42">
-                  <c:v>1382.2</c:v>
-                </c:pt>
-                <c:pt idx="43">
-                  <c:v>1381</c:v>
-                </c:pt>
-                <c:pt idx="44">
-                  <c:v>1375.8</c:v>
-                </c:pt>
-                <c:pt idx="45">
-                  <c:v>1371.3</c:v>
-                </c:pt>
-                <c:pt idx="46">
-                  <c:v>1383.7</c:v>
-                </c:pt>
-                <c:pt idx="47">
-                  <c:v>1389.1</c:v>
-                </c:pt>
-                <c:pt idx="48">
-                  <c:v>1389.7</c:v>
-                </c:pt>
-                <c:pt idx="49">
-                  <c:v>1391.8</c:v>
-                </c:pt>
-                <c:pt idx="50">
-                  <c:v>1392</c:v>
-                </c:pt>
-                <c:pt idx="51">
-                  <c:v>1388.3</c:v>
-                </c:pt>
-                <c:pt idx="52">
-                  <c:v>1386.5</c:v>
-                </c:pt>
-                <c:pt idx="53">
-                  <c:v>1386.3</c:v>
-                </c:pt>
-                <c:pt idx="54">
-                  <c:v>1386.4</c:v>
-                </c:pt>
-                <c:pt idx="55">
-                  <c:v>1386</c:v>
-                </c:pt>
-                <c:pt idx="56">
-                  <c:v>1387.5</c:v>
-                </c:pt>
-                <c:pt idx="57">
-                  <c:v>1390.5</c:v>
-                </c:pt>
-                <c:pt idx="58">
-                  <c:v>1384.4</c:v>
-                </c:pt>
-                <c:pt idx="59">
-                  <c:v>1379.4</c:v>
-                </c:pt>
-                <c:pt idx="60">
-                  <c:v>1389.5</c:v>
-                </c:pt>
-                <c:pt idx="61">
-                  <c:v>1388.1</c:v>
-                </c:pt>
-                <c:pt idx="62">
-                  <c:v>1392</c:v>
-                </c:pt>
-                <c:pt idx="63">
+                <c:pt idx="76">
+                  <c:v>1387.8</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>1388.5</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>1390.7</c:v>
+                </c:pt>
+                <c:pt idx="79">
+                  <c:v>1395.4</c:v>
+                </c:pt>
+                <c:pt idx="80">
+                  <c:v>1386.6</c:v>
+                </c:pt>
+                <c:pt idx="81">
+                  <c:v>1379.5</c:v>
+                </c:pt>
+                <c:pt idx="82">
+                  <c:v>1376.3</c:v>
+                </c:pt>
+                <c:pt idx="83">
+                  <c:v>1389</c:v>
+                </c:pt>
+                <c:pt idx="84">
                   <c:v>1397</c:v>
                 </c:pt>
-                <c:pt idx="64">
-                  <c:v>1398.8</c:v>
-                </c:pt>
-                <c:pt idx="65">
-                  <c:v>1383.5</c:v>
-                </c:pt>
-                <c:pt idx="66">
-                  <c:v>1390.3</c:v>
-                </c:pt>
-                <c:pt idx="67">
-                  <c:v>1393.2</c:v>
-                </c:pt>
-                <c:pt idx="68">
-                  <c:v>1394.2</c:v>
-                </c:pt>
-                <c:pt idx="69">
-                  <c:v>1384.8</c:v>
-                </c:pt>
-                <c:pt idx="70">
-                  <c:v>1389.8</c:v>
-                </c:pt>
-                <c:pt idx="71">
+                <c:pt idx="85">
+                  <c:v>1391.5</c:v>
+                </c:pt>
+                <c:pt idx="86">
                   <c:v>1394</c:v>
                 </c:pt>
-                <c:pt idx="72">
-                  <c:v>1395.9</c:v>
-                </c:pt>
-                <c:pt idx="73">
-                  <c:v>1389.7</c:v>
-                </c:pt>
-                <c:pt idx="74">
-                  <c:v>1395.3</c:v>
-                </c:pt>
-                <c:pt idx="75">
-                  <c:v>1388.4</c:v>
-                </c:pt>
-                <c:pt idx="76">
-                  <c:v>1387</c:v>
-                </c:pt>
-                <c:pt idx="77">
-                  <c:v>1387.8</c:v>
-                </c:pt>
-                <c:pt idx="78">
-                  <c:v>1388.5</c:v>
-                </c:pt>
-                <c:pt idx="79">
-                  <c:v>1390.7</c:v>
-                </c:pt>
-                <c:pt idx="80">
-                  <c:v>1395.4</c:v>
-                </c:pt>
-                <c:pt idx="81">
-                  <c:v>1386.6</c:v>
-                </c:pt>
-                <c:pt idx="82">
-                  <c:v>1379.5</c:v>
-                </c:pt>
-                <c:pt idx="83">
-                  <c:v>1376.3</c:v>
-                </c:pt>
-                <c:pt idx="84">
-                  <c:v>1389</c:v>
-                </c:pt>
-                <c:pt idx="85">
-                  <c:v>1397</c:v>
-                </c:pt>
-                <c:pt idx="86">
-                  <c:v>1391.5</c:v>
-                </c:pt>
                 <c:pt idx="87">
-                  <c:v>1394</c:v>
+                  <c:v>1403.8</c:v>
                 </c:pt>
                 <c:pt idx="88">
-                  <c:v>1403.8</c:v>
+                  <c:v>1409.3</c:v>
                 </c:pt>
                 <c:pt idx="89">
-                  <c:v>1409.3</c:v>
+                  <c:v>1409.7</c:v>
                 </c:pt>
                 <c:pt idx="90">
-                  <c:v>1409.7</c:v>
+                  <c:v>1400.4</c:v>
                 </c:pt>
                 <c:pt idx="91">
-                  <c:v>1400.4</c:v>
+                  <c:v>1405</c:v>
                 </c:pt>
                 <c:pt idx="92">
-                  <c:v>1405</c:v>
+                  <c:v>1403</c:v>
                 </c:pt>
                 <c:pt idx="93">
-                  <c:v>1403</c:v>
+                  <c:v>1407</c:v>
                 </c:pt>
                 <c:pt idx="94">
-                  <c:v>1407</c:v>
+                  <c:v>1427</c:v>
                 </c:pt>
                 <c:pt idx="95">
-                  <c:v>1427</c:v>
+                  <c:v>1424.5</c:v>
                 </c:pt>
                 <c:pt idx="96">
-                  <c:v>1424.5</c:v>
+                  <c:v>1428.1</c:v>
                 </c:pt>
                 <c:pt idx="97">
-                  <c:v>1428.1</c:v>
+                  <c:v>1422.6</c:v>
                 </c:pt>
                 <c:pt idx="98">
-                  <c:v>1422.6</c:v>
+                  <c:v>1417.9</c:v>
                 </c:pt>
                 <c:pt idx="99">
-                  <c:v>1417.9</c:v>
+                  <c:v>1422.2</c:v>
                 </c:pt>
                 <c:pt idx="100">
-                  <c:v>1422.2</c:v>
+                  <c:v>1420.8</c:v>
                 </c:pt>
                 <c:pt idx="101">
-                  <c:v>1420.8</c:v>
+                  <c:v>1432</c:v>
                 </c:pt>
                 <c:pt idx="102">
-                  <c:v>1432</c:v>
+                  <c:v>1431</c:v>
                 </c:pt>
                 <c:pt idx="103">
-                  <c:v>1431</c:v>
+                  <c:v>1437.4</c:v>
                 </c:pt>
                 <c:pt idx="104">
-                  <c:v>1437.4</c:v>
+                  <c:v>1439.4</c:v>
                 </c:pt>
                 <c:pt idx="105">
-                  <c:v>1439.4</c:v>
+                  <c:v>1433.4</c:v>
                 </c:pt>
                 <c:pt idx="106">
-                  <c:v>1433.4</c:v>
+                  <c:v>1432.7</c:v>
                 </c:pt>
                 <c:pt idx="107">
-                  <c:v>1432.7</c:v>
+                  <c:v>1421</c:v>
                 </c:pt>
                 <c:pt idx="108">
-                  <c:v>1421</c:v>
+                  <c:v>1435</c:v>
                 </c:pt>
                 <c:pt idx="109">
-                  <c:v>1435</c:v>
+                  <c:v>1433</c:v>
                 </c:pt>
                 <c:pt idx="110">
-                  <c:v>1433</c:v>
+                  <c:v>1431.3</c:v>
                 </c:pt>
                 <c:pt idx="111">
-                  <c:v>1431.3</c:v>
+                  <c:v>1440.6</c:v>
                 </c:pt>
                 <c:pt idx="112">
-                  <c:v>1440.6</c:v>
+                  <c:v>1441.8</c:v>
                 </c:pt>
                 <c:pt idx="113">
-                  <c:v>1441.8</c:v>
+                  <c:v>1449.3</c:v>
                 </c:pt>
                 <c:pt idx="114">
-                  <c:v>1449.3</c:v>
+                  <c:v>1461.5</c:v>
                 </c:pt>
                 <c:pt idx="115">
-                  <c:v>1461.5</c:v>
+                  <c:v>1456.8</c:v>
                 </c:pt>
                 <c:pt idx="116">
-                  <c:v>1456.8</c:v>
+                  <c:v>1463.4</c:v>
                 </c:pt>
                 <c:pt idx="117">
-                  <c:v>1463.4</c:v>
+                  <c:v>1468.9</c:v>
                 </c:pt>
                 <c:pt idx="118">
-                  <c:v>1468.9</c:v>
+                  <c:v>1466</c:v>
                 </c:pt>
                 <c:pt idx="119">
-                  <c:v>1466</c:v>
+                  <c:v>1453.1</c:v>
                 </c:pt>
                 <c:pt idx="120">
-                  <c:v>1453.1</c:v>
+                  <c:v>1460.4</c:v>
                 </c:pt>
                 <c:pt idx="121">
-                  <c:v>1460.4</c:v>
+                  <c:v>1461.9</c:v>
                 </c:pt>
                 <c:pt idx="122">
-                  <c:v>1461.9</c:v>
+                  <c:v>1468.5</c:v>
                 </c:pt>
                 <c:pt idx="123">
-                  <c:v>1468.5</c:v>
+                  <c:v>1472.2</c:v>
                 </c:pt>
                 <c:pt idx="124">
-                  <c:v>1472.2</c:v>
+                  <c:v>1471.5</c:v>
                 </c:pt>
                 <c:pt idx="125">
-                  <c:v>1471.5</c:v>
+                  <c:v>1476.5</c:v>
                 </c:pt>
                 <c:pt idx="126">
-                  <c:v>1476.5</c:v>
+                  <c:v>1469.3</c:v>
                 </c:pt>
                 <c:pt idx="127">
-                  <c:v>1469.3</c:v>
+                  <c:v>1468.3</c:v>
                 </c:pt>
                 <c:pt idx="128">
-                  <c:v>1468.3</c:v>
+                  <c:v>1462.7</c:v>
                 </c:pt>
                 <c:pt idx="129">
-                  <c:v>1462.7</c:v>
+                  <c:v>1466.8</c:v>
                 </c:pt>
                 <c:pt idx="130">
-                  <c:v>1466.8</c:v>
+                  <c:v>1468</c:v>
                 </c:pt>
                 <c:pt idx="131">
-                  <c:v>1468</c:v>
+                  <c:v>1469.4</c:v>
                 </c:pt>
                 <c:pt idx="132">
-                  <c:v>1469.4</c:v>
+                  <c:v>1466.9</c:v>
                 </c:pt>
                 <c:pt idx="133">
-                  <c:v>1466.9</c:v>
+                  <c:v>1473.6</c:v>
                 </c:pt>
                 <c:pt idx="134">
-                  <c:v>1473.6</c:v>
+                  <c:v>1473.3</c:v>
                 </c:pt>
                 <c:pt idx="135">
-                  <c:v>1473.3</c:v>
+                  <c:v>1469.8</c:v>
                 </c:pt>
                 <c:pt idx="136">
-                  <c:v>1469.8</c:v>
+                  <c:v>1469.9</c:v>
                 </c:pt>
                 <c:pt idx="137">
-                  <c:v>1469.9</c:v>
+                  <c:v>1470.8</c:v>
                 </c:pt>
                 <c:pt idx="138">
-                  <c:v>1470.8</c:v>
+                  <c:v>1471.9</c:v>
                 </c:pt>
                 <c:pt idx="139">
-                  <c:v>1471.9</c:v>
+                  <c:v>1477</c:v>
                 </c:pt>
                 <c:pt idx="140">
-                  <c:v>1477</c:v>
+                  <c:v>1468.6</c:v>
                 </c:pt>
                 <c:pt idx="141">
-                  <c:v>1468.6</c:v>
+                  <c:v>1473</c:v>
                 </c:pt>
                 <c:pt idx="142">
-                  <c:v>1473</c:v>
+                  <c:v>1474.5</c:v>
                 </c:pt>
                 <c:pt idx="143">
-                  <c:v>1474.5</c:v>
+                  <c:v>1473.1</c:v>
                 </c:pt>
                 <c:pt idx="144">
-                  <c:v>1473.1</c:v>
+                  <c:v>1478</c:v>
                 </c:pt>
                 <c:pt idx="145">
-                  <c:v>1478</c:v>
+                  <c:v>1481</c:v>
                 </c:pt>
                 <c:pt idx="146">
                   <c:v>1481</c:v>
                 </c:pt>
                 <c:pt idx="147">
-                  <c:v>1481</c:v>
+                  <c:v>1445.7</c:v>
                 </c:pt>
                 <c:pt idx="148">
-                  <c:v>1445.7</c:v>
+                  <c:v>1442.2</c:v>
                 </c:pt>
                 <c:pt idx="149">
-                  <c:v>1442.2</c:v>
+                  <c:v>1434.1</c:v>
                 </c:pt>
                 <c:pt idx="150">
-                  <c:v>1434.1</c:v>
+                  <c:v>1439.5</c:v>
                 </c:pt>
                 <c:pt idx="151">
-                  <c:v>1439.5</c:v>
+                  <c:v>1444.7</c:v>
                 </c:pt>
                 <c:pt idx="152">
-                  <c:v>1444.7</c:v>
+                  <c:v>1445.6</c:v>
                 </c:pt>
                 <c:pt idx="153">
-                  <c:v>1445.6</c:v>
+                  <c:v>1447.1</c:v>
                 </c:pt>
                 <c:pt idx="154">
-                  <c:v>1447.1</c:v>
+                  <c:v>1447.6</c:v>
                 </c:pt>
                 <c:pt idx="155">
-                  <c:v>1447.6</c:v>
+                  <c:v>1451.8</c:v>
                 </c:pt>
                 <c:pt idx="156">
-                  <c:v>1451.8</c:v>
+                  <c:v>1459</c:v>
                 </c:pt>
                 <c:pt idx="157">
-                  <c:v>1459</c:v>
+                  <c:v>1468.8</c:v>
                 </c:pt>
                 <c:pt idx="158">
-                  <c:v>1468.8</c:v>
+                  <c:v>1478.8</c:v>
                 </c:pt>
                 <c:pt idx="159">
-                  <c:v>1478.8</c:v>
+                  <c:v>1464</c:v>
                 </c:pt>
                 <c:pt idx="160">
-                  <c:v>1464</c:v>
+                  <c:v>1469.2</c:v>
                 </c:pt>
                 <c:pt idx="161">
-                  <c:v>1469.2</c:v>
+                  <c:v>1474.5</c:v>
                 </c:pt>
                 <c:pt idx="162">
-                  <c:v>1474.5</c:v>
+                  <c:v>1473.1</c:v>
                 </c:pt>
                 <c:pt idx="163">
-                  <c:v>1473.1</c:v>
+                  <c:v>1476.7</c:v>
                 </c:pt>
                 <c:pt idx="164">
-                  <c:v>1476.7</c:v>
+                  <c:v>1465.9</c:v>
                 </c:pt>
                 <c:pt idx="165">
-                  <c:v>1465.9</c:v>
+                  <c:v>1464.5</c:v>
                 </c:pt>
                 <c:pt idx="166">
-                  <c:v>1464.5</c:v>
+                  <c:v>1462.5</c:v>
                 </c:pt>
                 <c:pt idx="167">
-                  <c:v>1462.5</c:v>
+                  <c:v>1443.9</c:v>
                 </c:pt>
                 <c:pt idx="168">
-                  <c:v>1443.9</c:v>
+                  <c:v>1437.5</c:v>
                 </c:pt>
                 <c:pt idx="169">
-                  <c:v>1437.5</c:v>
+                  <c:v>1436.1</c:v>
                 </c:pt>
                 <c:pt idx="170">
-                  <c:v>1436.1</c:v>
+                  <c:v>1434</c:v>
                 </c:pt>
                 <c:pt idx="171">
-                  <c:v>1434</c:v>
+                  <c:v>1443.5</c:v>
                 </c:pt>
                 <c:pt idx="172">
-                  <c:v>1443.5</c:v>
+                  <c:v>1451.5</c:v>
                 </c:pt>
                 <c:pt idx="173">
-                  <c:v>1451.5</c:v>
+                  <c:v>1446.6</c:v>
                 </c:pt>
                 <c:pt idx="174">
+                  <c:v>1459.5</c:v>
+                </c:pt>
+                <c:pt idx="175">
+                  <c:v>1463.7</c:v>
+                </c:pt>
+                <c:pt idx="176">
+                  <c:v>1463</c:v>
+                </c:pt>
+                <c:pt idx="177">
+                  <c:v>1457.7</c:v>
+                </c:pt>
+                <c:pt idx="178">
+                  <c:v>1457.2</c:v>
+                </c:pt>
+                <c:pt idx="179">
+                  <c:v>1447</c:v>
+                </c:pt>
+                <c:pt idx="180">
+                  <c:v>1438.6</c:v>
+                </c:pt>
+                <c:pt idx="181">
+                  <c:v>1444.6</c:v>
+                </c:pt>
+                <c:pt idx="182">
+                  <c:v>1448.9</c:v>
+                </c:pt>
+                <c:pt idx="183">
                   <c:v>1446.6</c:v>
                 </c:pt>
-                <c:pt idx="175">
-                  <c:v>1459.5</c:v>
-                </c:pt>
-                <c:pt idx="176">
-                  <c:v>1463.7</c:v>
-                </c:pt>
-                <c:pt idx="177">
-                  <c:v>1463</c:v>
-                </c:pt>
-                <c:pt idx="178">
-                  <c:v>1457.7</c:v>
-                </c:pt>
-                <c:pt idx="179">
-                  <c:v>1457.2</c:v>
-                </c:pt>
-                <c:pt idx="180">
-                  <c:v>1447</c:v>
-                </c:pt>
-                <c:pt idx="181">
-                  <c:v>1438.6</c:v>
-                </c:pt>
-                <c:pt idx="182">
-                  <c:v>1444.6</c:v>
-                </c:pt>
-                <c:pt idx="183">
-                  <c:v>1448.9</c:v>
-                </c:pt>
                 <c:pt idx="184">
-                  <c:v>1446.6</c:v>
+                  <c:v>1442.9</c:v>
                 </c:pt>
                 <c:pt idx="185">
-                  <c:v>1442.9</c:v>
+                  <c:v>1441</c:v>
                 </c:pt>
                 <c:pt idx="186">
-                  <c:v>1441</c:v>
+                  <c:v>1427.8</c:v>
                 </c:pt>
                 <c:pt idx="187">
-                  <c:v>1427.8</c:v>
+                  <c:v>1433.5</c:v>
                 </c:pt>
                 <c:pt idx="188">
-                  <c:v>1433.5</c:v>
+                  <c:v>1440</c:v>
                 </c:pt>
                 <c:pt idx="189">
-                  <c:v>1440</c:v>
+                  <c:v>1485.7</c:v>
                 </c:pt>
                 <c:pt idx="190">
-                  <c:v>1485.7</c:v>
+                  <c:v>1462.9</c:v>
                 </c:pt>
                 <c:pt idx="191">
-                  <c:v>1462.9</c:v>
+                  <c:v>1482.2</c:v>
                 </c:pt>
                 <c:pt idx="192">
-                  <c:v>1482.2</c:v>
+                  <c:v>1481.6</c:v>
                 </c:pt>
                 <c:pt idx="193">
-                  <c:v>1481.6</c:v>
+                  <c:v>1473.7</c:v>
                 </c:pt>
                 <c:pt idx="194">
-                  <c:v>1473.7</c:v>
+                  <c:v>1465.7</c:v>
                 </c:pt>
                 <c:pt idx="195">
-                  <c:v>1465.7</c:v>
+                  <c:v>1477</c:v>
                 </c:pt>
                 <c:pt idx="196">
-                  <c:v>1477</c:v>
+                  <c:v>1488.5</c:v>
                 </c:pt>
                 <c:pt idx="197">
+                  <c:v>1497.5</c:v>
+                </c:pt>
+                <c:pt idx="198">
+                  <c:v>1491.9</c:v>
+                </c:pt>
+                <c:pt idx="199">
+                  <c:v>1488.4</c:v>
+                </c:pt>
+                <c:pt idx="200">
+                  <c:v>1500.7</c:v>
+                </c:pt>
+                <c:pt idx="201">
+                  <c:v>1495</c:v>
+                </c:pt>
+                <c:pt idx="202">
+                  <c:v>1504.7</c:v>
+                </c:pt>
+                <c:pt idx="203">
+                  <c:v>1486.7</c:v>
+                </c:pt>
+                <c:pt idx="204">
+                  <c:v>1499.9</c:v>
+                </c:pt>
+                <c:pt idx="205">
+                  <c:v>1501.7</c:v>
+                </c:pt>
+                <c:pt idx="206">
+                  <c:v>1508</c:v>
+                </c:pt>
+                <c:pt idx="207">
+                  <c:v>1511.4</c:v>
+                </c:pt>
+                <c:pt idx="208">
+                  <c:v>1518.2</c:v>
+                </c:pt>
+                <c:pt idx="209">
+                  <c:v>1517</c:v>
+                </c:pt>
+                <c:pt idx="210">
+                  <c:v>1513.3</c:v>
+                </c:pt>
+                <c:pt idx="211">
+                  <c:v>1510.6</c:v>
+                </c:pt>
+                <c:pt idx="212">
+                  <c:v>1511.4</c:v>
+                </c:pt>
+                <c:pt idx="213">
+                  <c:v>1509.8</c:v>
+                </c:pt>
+                <c:pt idx="214">
+                  <c:v>1501</c:v>
+                </c:pt>
+                <c:pt idx="215">
+                  <c:v>1479.2</c:v>
+                </c:pt>
+                <c:pt idx="216">
+                  <c:v>1474.7</c:v>
+                </c:pt>
+                <c:pt idx="217">
+                  <c:v>1483.5</c:v>
+                </c:pt>
+                <c:pt idx="218">
+                  <c:v>1482.7</c:v>
+                </c:pt>
+                <c:pt idx="219">
+                  <c:v>1472.7</c:v>
+                </c:pt>
+                <c:pt idx="220">
+                  <c:v>1475.5</c:v>
+                </c:pt>
+                <c:pt idx="221">
+                  <c:v>1479.2</c:v>
+                </c:pt>
+                <c:pt idx="222">
+                  <c:v>1460</c:v>
+                </c:pt>
+                <c:pt idx="223">
+                  <c:v>1472.8</c:v>
+                </c:pt>
+                <c:pt idx="224">
+                  <c:v>1480.8</c:v>
+                </c:pt>
+                <c:pt idx="225">
+                  <c:v>1480.3</c:v>
+                </c:pt>
+                <c:pt idx="226">
+                  <c:v>1479.2</c:v>
+                </c:pt>
+                <c:pt idx="227">
+                  <c:v>1476.8</c:v>
+                </c:pt>
+                <c:pt idx="228">
+                  <c:v>1473.6</c:v>
+                </c:pt>
+                <c:pt idx="229">
+                  <c:v>1473.2</c:v>
+                </c:pt>
+                <c:pt idx="230">
                   <c:v>1488.5</c:v>
                 </c:pt>
-                <c:pt idx="198">
+                <c:pt idx="231">
+                  <c:v>1477.5</c:v>
+                </c:pt>
+                <c:pt idx="232">
+                  <c:v>1478.4</c:v>
+                </c:pt>
+                <c:pt idx="233">
+                  <c:v>1449.4</c:v>
+                </c:pt>
+                <c:pt idx="234">
+                  <c:v>1456</c:v>
+                </c:pt>
+                <c:pt idx="235">
+                  <c:v>1462.3</c:v>
+                </c:pt>
+                <c:pt idx="236">
+                  <c:v>1472.7</c:v>
+                </c:pt>
+                <c:pt idx="237">
+                  <c:v>1490.9</c:v>
+                </c:pt>
+                <c:pt idx="238">
+                  <c:v>1489.3</c:v>
+                </c:pt>
+                <c:pt idx="239">
+                  <c:v>1493.4</c:v>
+                </c:pt>
+                <c:pt idx="240">
                   <c:v>1497.5</c:v>
                 </c:pt>
-                <c:pt idx="199">
-                  <c:v>1491.9</c:v>
-                </c:pt>
-                <c:pt idx="200">
-                  <c:v>1488.4</c:v>
-                </c:pt>
-                <c:pt idx="201">
-                  <c:v>1500.7</c:v>
-                </c:pt>
-                <c:pt idx="202">
-                  <c:v>1495</c:v>
-                </c:pt>
-                <c:pt idx="203">
-                  <c:v>1504.7</c:v>
-                </c:pt>
-                <c:pt idx="204">
-                  <c:v>1486.7</c:v>
-                </c:pt>
-                <c:pt idx="205">
-                  <c:v>1499.9</c:v>
-                </c:pt>
-                <c:pt idx="206">
-                  <c:v>1501.7</c:v>
-                </c:pt>
-                <c:pt idx="207">
-                  <c:v>1508</c:v>
-                </c:pt>
-                <c:pt idx="208">
-                  <c:v>1511.4</c:v>
-                </c:pt>
-                <c:pt idx="209">
-                  <c:v>1518.2</c:v>
-                </c:pt>
-                <c:pt idx="210">
-                  <c:v>1517</c:v>
-                </c:pt>
-                <c:pt idx="211">
-                  <c:v>1513.3</c:v>
-                </c:pt>
-                <c:pt idx="212">
-                  <c:v>1510.6</c:v>
-                </c:pt>
-                <c:pt idx="213">
-                  <c:v>1511.4</c:v>
-                </c:pt>
-                <c:pt idx="214">
-                  <c:v>1509.8</c:v>
-                </c:pt>
-                <c:pt idx="215">
-                  <c:v>1501</c:v>
-                </c:pt>
-                <c:pt idx="216">
-                  <c:v>1479.2</c:v>
-                </c:pt>
-                <c:pt idx="217">
-                  <c:v>1474.7</c:v>
-                </c:pt>
-                <c:pt idx="218">
-                  <c:v>1483.5</c:v>
-                </c:pt>
-                <c:pt idx="219">
-                  <c:v>1482.7</c:v>
-                </c:pt>
-                <c:pt idx="220">
-                  <c:v>1472.7</c:v>
-                </c:pt>
-                <c:pt idx="221">
-                  <c:v>1475.5</c:v>
-                </c:pt>
-                <c:pt idx="222">
-                  <c:v>1479.2</c:v>
-                </c:pt>
-                <c:pt idx="223">
-                  <c:v>1460</c:v>
-                </c:pt>
-                <c:pt idx="224">
-                  <c:v>1472.8</c:v>
-                </c:pt>
-                <c:pt idx="225">
-                  <c:v>1480.8</c:v>
-                </c:pt>
-                <c:pt idx="226">
-                  <c:v>1480.3</c:v>
-                </c:pt>
-                <c:pt idx="227">
-                  <c:v>1479.2</c:v>
-                </c:pt>
-                <c:pt idx="228">
-                  <c:v>1476.8</c:v>
-                </c:pt>
-                <c:pt idx="229">
-                  <c:v>1473.6</c:v>
-                </c:pt>
-                <c:pt idx="230">
-                  <c:v>1473.2</c:v>
-                </c:pt>
-                <c:pt idx="231">
-                  <c:v>1488.5</c:v>
-                </c:pt>
-                <c:pt idx="232">
-                  <c:v>1477.5</c:v>
-                </c:pt>
-                <c:pt idx="233">
-                  <c:v>1478.4</c:v>
-                </c:pt>
-                <c:pt idx="234">
-                  <c:v>1449.4</c:v>
-                </c:pt>
-                <c:pt idx="235">
-                  <c:v>1456</c:v>
-                </c:pt>
-                <c:pt idx="236">
-                  <c:v>1462.3</c:v>
-                </c:pt>
-                <c:pt idx="237">
-                  <c:v>1472.7</c:v>
-                </c:pt>
-                <c:pt idx="238">
-                  <c:v>1490.9</c:v>
-                </c:pt>
-                <c:pt idx="239">
-                  <c:v>1489.3</c:v>
-                </c:pt>
-                <c:pt idx="240">
-                  <c:v>1493.4</c:v>
-                </c:pt>
                 <c:pt idx="241">
-                  <c:v>1497.5</c:v>
+                  <c:v>1492.9</c:v>
                 </c:pt>
                 <c:pt idx="242">
-                  <c:v>1492.9</c:v>
+                  <c:v>1508.7</c:v>
                 </c:pt>
                 <c:pt idx="243">
-                  <c:v>1508.7</c:v>
+                  <c:v>1496.7</c:v>
                 </c:pt>
                 <c:pt idx="244">
-                  <c:v>1508.7</c:v>
+                  <c:v>1496.7</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4491,10 +4491,10 @@
         <v>3</v>
       </c>
       <c r="B2" s="3">
-        <v>1392.4</v>
+        <v>1387.2</v>
       </c>
       <c r="C2" s="3">
-        <v>1394.4</v>
+        <v>1371.8</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -4502,10 +4502,10 @@
         <v>4</v>
       </c>
       <c r="B3" s="3">
-        <v>1387.2</v>
+        <v>1381.3</v>
       </c>
       <c r="C3" s="3">
-        <v>1371.8</v>
+        <v>1382.7</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -4513,10 +4513,10 @@
         <v>5</v>
       </c>
       <c r="B4" s="3">
-        <v>1381.3</v>
+        <v>1375.6</v>
       </c>
       <c r="C4" s="3">
-        <v>1382.7</v>
+        <v>1366.5</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -4524,10 +4524,10 @@
         <v>6</v>
       </c>
       <c r="B5" s="3">
-        <v>1375.6</v>
+        <v>1364.4</v>
       </c>
       <c r="C5" s="3">
-        <v>1366.5</v>
+        <v>1370.5</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -4535,10 +4535,10 @@
         <v>7</v>
       </c>
       <c r="B6" s="3">
-        <v>1364.4</v>
+        <v>1369.5</v>
       </c>
       <c r="C6" s="3">
-        <v>1370.5</v>
+        <v>1376.5</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -4546,10 +4546,10 @@
         <v>8</v>
       </c>
       <c r="B7" s="3">
-        <v>1369.5</v>
+        <v>1376.5</v>
       </c>
       <c r="C7" s="3">
-        <v>1376.5</v>
+        <v>1376</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -4557,10 +4557,10 @@
         <v>9</v>
       </c>
       <c r="B8" s="3">
-        <v>1376.5</v>
+        <v>1375.9</v>
       </c>
       <c r="C8" s="3">
-        <v>1376</v>
+        <v>1371.1</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -4568,10 +4568,10 @@
         <v>10</v>
       </c>
       <c r="B9" s="3">
-        <v>1375.9</v>
+        <v>1380.1</v>
       </c>
       <c r="C9" s="3">
-        <v>1371.1</v>
+        <v>1383.1</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -4579,10 +4579,10 @@
         <v>11</v>
       </c>
       <c r="B10" s="3">
-        <v>1380.1</v>
+        <v>1373.1</v>
       </c>
       <c r="C10" s="3">
-        <v>1383.1</v>
+        <v>1377.1</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -4590,10 +4590,10 @@
         <v>12</v>
       </c>
       <c r="B11" s="3">
-        <v>1373.1</v>
+        <v>1369.5</v>
       </c>
       <c r="C11" s="3">
-        <v>1377.1</v>
+        <v>1364.1</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -4601,10 +4601,10 @@
         <v>13</v>
       </c>
       <c r="B12" s="3">
-        <v>1369.5</v>
+        <v>1358.4</v>
       </c>
       <c r="C12" s="3">
-        <v>1364.1</v>
+        <v>1356.5</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -4612,10 +4612,10 @@
         <v>14</v>
       </c>
       <c r="B13" s="3">
-        <v>1358.4</v>
+        <v>1356.4</v>
       </c>
       <c r="C13" s="3">
-        <v>1356.5</v>
+        <v>1354.2</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -4623,10 +4623,10 @@
         <v>15</v>
       </c>
       <c r="B14" s="3">
-        <v>1356.4</v>
+        <v>1364.3</v>
       </c>
       <c r="C14" s="3">
-        <v>1354.2</v>
+        <v>1368</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -4634,10 +4634,10 @@
         <v>16</v>
       </c>
       <c r="B15" s="3">
-        <v>1364.3</v>
+        <v>1375</v>
       </c>
       <c r="C15" s="3">
-        <v>1368</v>
+        <v>1370.9</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -4645,10 +4645,10 @@
         <v>17</v>
       </c>
       <c r="B16" s="3">
-        <v>1375</v>
+        <v>1358.7</v>
       </c>
       <c r="C16" s="3">
-        <v>1370.9</v>
+        <v>1357.1</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -4656,10 +4656,10 @@
         <v>18</v>
       </c>
       <c r="B17" s="3">
-        <v>1358.7</v>
+        <v>1369.6</v>
       </c>
       <c r="C17" s="3">
-        <v>1357.1</v>
+        <v>1363.5</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -4667,10 +4667,10 @@
         <v>19</v>
       </c>
       <c r="B18" s="3">
-        <v>1369.6</v>
+        <v>1363.8</v>
       </c>
       <c r="C18" s="3">
-        <v>1363.5</v>
+        <v>1358.1</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -4678,10 +4678,10 @@
         <v>20</v>
       </c>
       <c r="B19" s="3">
-        <v>1363.8</v>
+        <v>1362.7</v>
       </c>
       <c r="C19" s="3">
-        <v>1358.1</v>
+        <v>1374</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -4689,10 +4689,10 @@
         <v>21</v>
       </c>
       <c r="B20" s="3">
-        <v>1362.7</v>
+        <v>1369.4</v>
       </c>
       <c r="C20" s="3">
-        <v>1374</v>
+        <v>1372.3</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -4700,10 +4700,10 @@
         <v>22</v>
       </c>
       <c r="B21" s="3">
-        <v>1369.4</v>
+        <v>1380.2</v>
       </c>
       <c r="C21" s="3">
-        <v>1372.3</v>
+        <v>1379.8</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -4711,10 +4711,10 @@
         <v>23</v>
       </c>
       <c r="B22" s="3">
-        <v>1380.2</v>
+        <v>1365.6</v>
       </c>
       <c r="C22" s="3">
-        <v>1379.8</v>
+        <v>1374</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -4722,10 +4722,10 @@
         <v>24</v>
       </c>
       <c r="B23" s="3">
-        <v>1365.6</v>
+        <v>1384.3</v>
       </c>
       <c r="C23" s="3">
-        <v>1374</v>
+        <v>1382</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -4733,10 +4733,10 @@
         <v>25</v>
       </c>
       <c r="B24" s="3">
-        <v>1384.3</v>
+        <v>1360.2</v>
       </c>
       <c r="C24" s="3">
-        <v>1382</v>
+        <v>1361.4</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -4744,10 +4744,10 @@
         <v>26</v>
       </c>
       <c r="B25" s="3">
-        <v>1360.2</v>
+        <v>1362.4</v>
       </c>
       <c r="C25" s="3">
-        <v>1361.4</v>
+        <v>1361.2</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -4755,10 +4755,10 @@
         <v>27</v>
       </c>
       <c r="B26" s="3">
-        <v>1362.4</v>
+        <v>1356.9</v>
       </c>
       <c r="C26" s="3">
-        <v>1361.2</v>
+        <v>1352.9</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -4766,10 +4766,10 @@
         <v>28</v>
       </c>
       <c r="B27" s="3">
-        <v>1356.9</v>
+        <v>1357.4</v>
       </c>
       <c r="C27" s="3">
-        <v>1352.9</v>
+        <v>1361.3</v>
       </c>
     </row>
     <row r="28" spans="1:3">
@@ -4777,10 +4777,10 @@
         <v>29</v>
       </c>
       <c r="B28" s="3">
-        <v>1357.4</v>
+        <v>1350</v>
       </c>
       <c r="C28" s="3">
-        <v>1361.3</v>
+        <v>1355.3</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -4788,10 +4788,10 @@
         <v>30</v>
       </c>
       <c r="B29" s="3">
-        <v>1350</v>
+        <v>1355.9</v>
       </c>
       <c r="C29" s="3">
-        <v>1355.3</v>
+        <v>1359</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -4799,10 +4799,10 @@
         <v>31</v>
       </c>
       <c r="B30" s="3">
-        <v>1355.9</v>
+        <v>1358.7</v>
       </c>
       <c r="C30" s="3">
-        <v>1359</v>
+        <v>1355.5</v>
       </c>
     </row>
     <row r="31" spans="1:3">
@@ -4810,10 +4810,10 @@
         <v>32</v>
       </c>
       <c r="B31" s="3">
-        <v>1358.7</v>
+        <v>1359.4</v>
       </c>
       <c r="C31" s="3">
-        <v>1355.5</v>
+        <v>1365.5</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -4821,10 +4821,10 @@
         <v>33</v>
       </c>
       <c r="B32" s="3">
-        <v>1359.4</v>
+        <v>1362.3</v>
       </c>
       <c r="C32" s="3">
-        <v>1365.5</v>
+        <v>1362.5</v>
       </c>
     </row>
     <row r="33" spans="1:3">
@@ -4832,10 +4832,10 @@
         <v>34</v>
       </c>
       <c r="B33" s="3">
-        <v>1362.3</v>
+        <v>1367.8</v>
       </c>
       <c r="C33" s="3">
-        <v>1362.5</v>
+        <v>1377</v>
       </c>
     </row>
     <row r="34" spans="1:3">
@@ -4843,10 +4843,10 @@
         <v>35</v>
       </c>
       <c r="B34" s="3">
-        <v>1367.8</v>
+        <v>1367.9</v>
       </c>
       <c r="C34" s="3">
-        <v>1377</v>
+        <v>1373.2</v>
       </c>
     </row>
     <row r="35" spans="1:3">
@@ -4854,10 +4854,10 @@
         <v>36</v>
       </c>
       <c r="B35" s="3">
-        <v>1367.9</v>
+        <v>1375</v>
       </c>
       <c r="C35" s="3">
-        <v>1373.2</v>
+        <v>1375.2</v>
       </c>
     </row>
     <row r="36" spans="1:3">
@@ -4865,10 +4865,10 @@
         <v>37</v>
       </c>
       <c r="B36" s="3">
-        <v>1375</v>
+        <v>1370</v>
       </c>
       <c r="C36" s="3">
-        <v>1375.2</v>
+        <v>1373.9</v>
       </c>
     </row>
     <row r="37" spans="1:3">
@@ -4876,10 +4876,10 @@
         <v>38</v>
       </c>
       <c r="B37" s="3">
-        <v>1370</v>
+        <v>1375.4</v>
       </c>
       <c r="C37" s="3">
-        <v>1373.9</v>
+        <v>1375.8</v>
       </c>
     </row>
     <row r="38" spans="1:3">
@@ -4887,10 +4887,10 @@
         <v>39</v>
       </c>
       <c r="B38" s="3">
-        <v>1375.4</v>
+        <v>1381.2</v>
       </c>
       <c r="C38" s="3">
-        <v>1375.8</v>
+        <v>1383</v>
       </c>
     </row>
     <row r="39" spans="1:3">
@@ -4898,10 +4898,10 @@
         <v>40</v>
       </c>
       <c r="B39" s="3">
-        <v>1381.2</v>
+        <v>1380.2</v>
       </c>
       <c r="C39" s="3">
-        <v>1383</v>
+        <v>1388.2</v>
       </c>
     </row>
     <row r="40" spans="1:3">
@@ -4909,10 +4909,10 @@
         <v>41</v>
       </c>
       <c r="B40" s="3">
-        <v>1380.2</v>
+        <v>1385.7</v>
       </c>
       <c r="C40" s="3">
-        <v>1388.2</v>
+        <v>1387</v>
       </c>
     </row>
     <row r="41" spans="1:3">
@@ -4920,10 +4920,10 @@
         <v>42</v>
       </c>
       <c r="B41" s="3">
-        <v>1385.7</v>
+        <v>1392.6</v>
       </c>
       <c r="C41" s="3">
-        <v>1387</v>
+        <v>1392.2</v>
       </c>
     </row>
     <row r="42" spans="1:3">
@@ -4931,10 +4931,10 @@
         <v>43</v>
       </c>
       <c r="B42" s="3">
-        <v>1392.6</v>
+        <v>1393</v>
       </c>
       <c r="C42" s="3">
-        <v>1392.2</v>
+        <v>1391.6</v>
       </c>
     </row>
     <row r="43" spans="1:3">
@@ -4942,10 +4942,10 @@
         <v>44</v>
       </c>
       <c r="B43" s="3">
-        <v>1393</v>
+        <v>1388.2</v>
       </c>
       <c r="C43" s="3">
-        <v>1391.6</v>
+        <v>1382.2</v>
       </c>
     </row>
     <row r="44" spans="1:3">
@@ -4953,10 +4953,10 @@
         <v>45</v>
       </c>
       <c r="B44" s="3">
-        <v>1388.2</v>
+        <v>1387.8</v>
       </c>
       <c r="C44" s="3">
-        <v>1382.2</v>
+        <v>1381</v>
       </c>
     </row>
     <row r="45" spans="1:3">
@@ -4964,10 +4964,10 @@
         <v>46</v>
       </c>
       <c r="B45" s="3">
-        <v>1387.8</v>
+        <v>1379.8</v>
       </c>
       <c r="C45" s="3">
-        <v>1381</v>
+        <v>1375.8</v>
       </c>
     </row>
     <row r="46" spans="1:3">
@@ -4975,10 +4975,10 @@
         <v>47</v>
       </c>
       <c r="B46" s="3">
-        <v>1379.8</v>
+        <v>1367.2</v>
       </c>
       <c r="C46" s="3">
-        <v>1375.8</v>
+        <v>1371.3</v>
       </c>
     </row>
     <row r="47" spans="1:3">
@@ -4986,10 +4986,10 @@
         <v>48</v>
       </c>
       <c r="B47" s="3">
-        <v>1367.2</v>
+        <v>1377.9</v>
       </c>
       <c r="C47" s="3">
-        <v>1371.3</v>
+        <v>1383.7</v>
       </c>
     </row>
     <row r="48" spans="1:3">
@@ -4997,10 +4997,10 @@
         <v>49</v>
       </c>
       <c r="B48" s="3">
-        <v>1377.9</v>
+        <v>1382</v>
       </c>
       <c r="C48" s="3">
-        <v>1383.7</v>
+        <v>1389.1</v>
       </c>
     </row>
     <row r="49" spans="1:3">
@@ -5008,10 +5008,10 @@
         <v>50</v>
       </c>
       <c r="B49" s="3">
-        <v>1382</v>
+        <v>1391</v>
       </c>
       <c r="C49" s="3">
-        <v>1389.1</v>
+        <v>1389.7</v>
       </c>
     </row>
     <row r="50" spans="1:3">
@@ -5019,10 +5019,10 @@
         <v>51</v>
       </c>
       <c r="B50" s="3">
-        <v>1391</v>
+        <v>1383.1</v>
       </c>
       <c r="C50" s="3">
-        <v>1389.7</v>
+        <v>1391.8</v>
       </c>
     </row>
     <row r="51" spans="1:3">
@@ -5030,10 +5030,10 @@
         <v>52</v>
       </c>
       <c r="B51" s="3">
-        <v>1383.1</v>
+        <v>1387</v>
       </c>
       <c r="C51" s="3">
-        <v>1391.8</v>
+        <v>1392</v>
       </c>
     </row>
     <row r="52" spans="1:3">
@@ -5041,10 +5041,10 @@
         <v>53</v>
       </c>
       <c r="B52" s="3">
-        <v>1387</v>
+        <v>1401.4</v>
       </c>
       <c r="C52" s="3">
-        <v>1392</v>
+        <v>1388.3</v>
       </c>
     </row>
     <row r="53" spans="1:3">
@@ -5052,10 +5052,10 @@
         <v>54</v>
       </c>
       <c r="B53" s="3">
-        <v>1401.4</v>
+        <v>1385.2</v>
       </c>
       <c r="C53" s="3">
-        <v>1388.3</v>
+        <v>1386.5</v>
       </c>
     </row>
     <row r="54" spans="1:3">
@@ -5063,10 +5063,10 @@
         <v>55</v>
       </c>
       <c r="B54" s="3">
-        <v>1385.2</v>
+        <v>1388.3</v>
       </c>
       <c r="C54" s="3">
-        <v>1386.5</v>
+        <v>1386.3</v>
       </c>
     </row>
     <row r="55" spans="1:3">
@@ -5074,10 +5074,10 @@
         <v>56</v>
       </c>
       <c r="B55" s="3">
-        <v>1388.3</v>
+        <v>1389.5</v>
       </c>
       <c r="C55" s="3">
-        <v>1386.3</v>
+        <v>1386.4</v>
       </c>
     </row>
     <row r="56" spans="1:3">
@@ -5085,10 +5085,10 @@
         <v>57</v>
       </c>
       <c r="B56" s="3">
-        <v>1389.5</v>
+        <v>1381.2</v>
       </c>
       <c r="C56" s="3">
-        <v>1386.4</v>
+        <v>1386</v>
       </c>
     </row>
     <row r="57" spans="1:3">
@@ -5096,10 +5096,10 @@
         <v>58</v>
       </c>
       <c r="B57" s="3">
-        <v>1381.2</v>
+        <v>1389.6</v>
       </c>
       <c r="C57" s="3">
-        <v>1386</v>
+        <v>1387.5</v>
       </c>
     </row>
     <row r="58" spans="1:3">
@@ -5107,10 +5107,10 @@
         <v>59</v>
       </c>
       <c r="B58" s="3">
-        <v>1389.6</v>
+        <v>1388</v>
       </c>
       <c r="C58" s="3">
-        <v>1387.5</v>
+        <v>1390.5</v>
       </c>
     </row>
     <row r="59" spans="1:3">
@@ -5118,10 +5118,10 @@
         <v>60</v>
       </c>
       <c r="B59" s="3">
-        <v>1388</v>
+        <v>1389.9</v>
       </c>
       <c r="C59" s="3">
-        <v>1390.5</v>
+        <v>1384.4</v>
       </c>
     </row>
     <row r="60" spans="1:3">
@@ -5129,10 +5129,10 @@
         <v>61</v>
       </c>
       <c r="B60" s="3">
-        <v>1389.9</v>
+        <v>1381.7</v>
       </c>
       <c r="C60" s="3">
-        <v>1384.4</v>
+        <v>1379.4</v>
       </c>
     </row>
     <row r="61" spans="1:3">
@@ -5140,10 +5140,10 @@
         <v>62</v>
       </c>
       <c r="B61" s="3">
-        <v>1381.7</v>
+        <v>1382</v>
       </c>
       <c r="C61" s="3">
-        <v>1379.4</v>
+        <v>1389.5</v>
       </c>
     </row>
     <row r="62" spans="1:3">
@@ -5151,10 +5151,10 @@
         <v>63</v>
       </c>
       <c r="B62" s="3">
-        <v>1382</v>
+        <v>1385</v>
       </c>
       <c r="C62" s="3">
-        <v>1389.5</v>
+        <v>1388.1</v>
       </c>
     </row>
     <row r="63" spans="1:3">
@@ -5162,10 +5162,10 @@
         <v>64</v>
       </c>
       <c r="B63" s="3">
-        <v>1385</v>
+        <v>1390.9</v>
       </c>
       <c r="C63" s="3">
-        <v>1388.1</v>
+        <v>1392</v>
       </c>
     </row>
     <row r="64" spans="1:3">
@@ -5173,10 +5173,10 @@
         <v>65</v>
       </c>
       <c r="B64" s="3">
-        <v>1390.9</v>
+        <v>1398.4</v>
       </c>
       <c r="C64" s="3">
-        <v>1392</v>
+        <v>1397</v>
       </c>
     </row>
     <row r="65" spans="1:3">
@@ -5187,7 +5187,7 @@
         <v>1398.4</v>
       </c>
       <c r="C65" s="3">
-        <v>1397</v>
+        <v>1398.8</v>
       </c>
     </row>
     <row r="66" spans="1:3">
@@ -5195,10 +5195,10 @@
         <v>67</v>
       </c>
       <c r="B66" s="3">
-        <v>1398.4</v>
+        <v>1393.2</v>
       </c>
       <c r="C66" s="3">
-        <v>1398.8</v>
+        <v>1383.5</v>
       </c>
     </row>
     <row r="67" spans="1:3">
@@ -5206,10 +5206,10 @@
         <v>68</v>
       </c>
       <c r="B67" s="3">
-        <v>1393.2</v>
+        <v>1384.7</v>
       </c>
       <c r="C67" s="3">
-        <v>1383.5</v>
+        <v>1390.3</v>
       </c>
     </row>
     <row r="68" spans="1:3">
@@ -5217,10 +5217,10 @@
         <v>69</v>
       </c>
       <c r="B68" s="3">
-        <v>1384.7</v>
+        <v>1395.8</v>
       </c>
       <c r="C68" s="3">
-        <v>1390.3</v>
+        <v>1393.2</v>
       </c>
     </row>
     <row r="69" spans="1:3">
@@ -5228,10 +5228,10 @@
         <v>70</v>
       </c>
       <c r="B69" s="3">
-        <v>1395.8</v>
+        <v>1396.3</v>
       </c>
       <c r="C69" s="3">
-        <v>1393.2</v>
+        <v>1394.2</v>
       </c>
     </row>
     <row r="70" spans="1:3">
@@ -5239,10 +5239,10 @@
         <v>71</v>
       </c>
       <c r="B70" s="3">
-        <v>1396.3</v>
+        <v>1387.6</v>
       </c>
       <c r="C70" s="3">
-        <v>1394.2</v>
+        <v>1384.8</v>
       </c>
     </row>
     <row r="71" spans="1:3">
@@ -5250,10 +5250,10 @@
         <v>72</v>
       </c>
       <c r="B71" s="3">
-        <v>1387.6</v>
+        <v>1390.1</v>
       </c>
       <c r="C71" s="3">
-        <v>1384.8</v>
+        <v>1389.8</v>
       </c>
     </row>
     <row r="72" spans="1:3">
@@ -5261,10 +5261,10 @@
         <v>73</v>
       </c>
       <c r="B72" s="3">
-        <v>1390.1</v>
+        <v>1393.7</v>
       </c>
       <c r="C72" s="3">
-        <v>1389.8</v>
+        <v>1394</v>
       </c>
     </row>
     <row r="73" spans="1:3">
@@ -5272,10 +5272,10 @@
         <v>74</v>
       </c>
       <c r="B73" s="3">
-        <v>1393.7</v>
+        <v>1391</v>
       </c>
       <c r="C73" s="3">
-        <v>1394</v>
+        <v>1395.9</v>
       </c>
     </row>
     <row r="74" spans="1:3">
@@ -5283,10 +5283,10 @@
         <v>75</v>
       </c>
       <c r="B74" s="3">
-        <v>1391</v>
+        <v>1392.3</v>
       </c>
       <c r="C74" s="3">
-        <v>1395.9</v>
+        <v>1389.7</v>
       </c>
     </row>
     <row r="75" spans="1:3">
@@ -5294,10 +5294,10 @@
         <v>76</v>
       </c>
       <c r="B75" s="3">
-        <v>1392.3</v>
+        <v>1392.5</v>
       </c>
       <c r="C75" s="3">
-        <v>1389.7</v>
+        <v>1395.3</v>
       </c>
     </row>
     <row r="76" spans="1:3">
@@ -5305,10 +5305,10 @@
         <v>77</v>
       </c>
       <c r="B76" s="3">
-        <v>1392.5</v>
+        <v>1391</v>
       </c>
       <c r="C76" s="3">
-        <v>1395.3</v>
+        <v>1388.4</v>
       </c>
     </row>
     <row r="77" spans="1:3">
@@ -5316,10 +5316,10 @@
         <v>78</v>
       </c>
       <c r="B77" s="3">
-        <v>1391</v>
+        <v>1390.6</v>
       </c>
       <c r="C77" s="3">
-        <v>1388.4</v>
+        <v>1387</v>
       </c>
     </row>
     <row r="78" spans="1:3">
@@ -5327,10 +5327,10 @@
         <v>79</v>
       </c>
       <c r="B78" s="3">
-        <v>1390.6</v>
+        <v>1387.9</v>
       </c>
       <c r="C78" s="3">
-        <v>1387</v>
+        <v>1387.8</v>
       </c>
     </row>
     <row r="79" spans="1:3">
@@ -5338,10 +5338,10 @@
         <v>80</v>
       </c>
       <c r="B79" s="3">
-        <v>1387.9</v>
+        <v>1386.6</v>
       </c>
       <c r="C79" s="3">
-        <v>1387.8</v>
+        <v>1388.5</v>
       </c>
     </row>
     <row r="80" spans="1:3">
@@ -5349,10 +5349,10 @@
         <v>81</v>
       </c>
       <c r="B80" s="3">
-        <v>1386.6</v>
+        <v>1391.8</v>
       </c>
       <c r="C80" s="3">
-        <v>1388.5</v>
+        <v>1390.7</v>
       </c>
     </row>
     <row r="81" spans="1:3">
@@ -5360,10 +5360,10 @@
         <v>82</v>
       </c>
       <c r="B81" s="3">
-        <v>1391.8</v>
+        <v>1388.2</v>
       </c>
       <c r="C81" s="3">
-        <v>1390.7</v>
+        <v>1395.4</v>
       </c>
     </row>
     <row r="82" spans="1:3">
@@ -5371,10 +5371,10 @@
         <v>83</v>
       </c>
       <c r="B82" s="3">
-        <v>1388.2</v>
+        <v>1389</v>
       </c>
       <c r="C82" s="3">
-        <v>1395.4</v>
+        <v>1386.6</v>
       </c>
     </row>
     <row r="83" spans="1:3">
@@ -5382,10 +5382,10 @@
         <v>84</v>
       </c>
       <c r="B83" s="3">
-        <v>1389</v>
+        <v>1378.9</v>
       </c>
       <c r="C83" s="3">
-        <v>1386.6</v>
+        <v>1379.5</v>
       </c>
     </row>
     <row r="84" spans="1:3">
@@ -5393,10 +5393,10 @@
         <v>85</v>
       </c>
       <c r="B84" s="3">
-        <v>1378.9</v>
+        <v>1380.1</v>
       </c>
       <c r="C84" s="3">
-        <v>1379.5</v>
+        <v>1376.3</v>
       </c>
     </row>
     <row r="85" spans="1:3">
@@ -5404,10 +5404,10 @@
         <v>86</v>
       </c>
       <c r="B85" s="3">
-        <v>1380.1</v>
+        <v>1387.8</v>
       </c>
       <c r="C85" s="3">
-        <v>1376.3</v>
+        <v>1389</v>
       </c>
     </row>
     <row r="86" spans="1:3">
@@ -5415,10 +5415,10 @@
         <v>87</v>
       </c>
       <c r="B86" s="3">
-        <v>1387.8</v>
+        <v>1393.6</v>
       </c>
       <c r="C86" s="3">
-        <v>1389</v>
+        <v>1397</v>
       </c>
     </row>
     <row r="87" spans="1:3">
@@ -5426,10 +5426,10 @@
         <v>88</v>
       </c>
       <c r="B87" s="3">
-        <v>1393.6</v>
+        <v>1392.6</v>
       </c>
       <c r="C87" s="3">
-        <v>1397</v>
+        <v>1391.5</v>
       </c>
     </row>
     <row r="88" spans="1:3">
@@ -5440,7 +5440,7 @@
         <v>1392.6</v>
       </c>
       <c r="C88" s="3">
-        <v>1391.5</v>
+        <v>1394</v>
       </c>
     </row>
     <row r="89" spans="1:3">
@@ -5448,10 +5448,10 @@
         <v>90</v>
       </c>
       <c r="B89" s="3">
-        <v>1392.6</v>
+        <v>1397.5</v>
       </c>
       <c r="C89" s="3">
-        <v>1394</v>
+        <v>1403.8</v>
       </c>
     </row>
     <row r="90" spans="1:3">
@@ -5459,10 +5459,10 @@
         <v>91</v>
       </c>
       <c r="B90" s="3">
-        <v>1397.5</v>
+        <v>1400.6</v>
       </c>
       <c r="C90" s="3">
-        <v>1403.8</v>
+        <v>1409.3</v>
       </c>
     </row>
     <row r="91" spans="1:3">
@@ -5470,10 +5470,10 @@
         <v>92</v>
       </c>
       <c r="B91" s="3">
-        <v>1400.6</v>
+        <v>1412.4</v>
       </c>
       <c r="C91" s="3">
-        <v>1409.3</v>
+        <v>1409.7</v>
       </c>
     </row>
     <row r="92" spans="1:3">
@@ -5481,10 +5481,10 @@
         <v>93</v>
       </c>
       <c r="B92" s="3">
-        <v>1412.4</v>
+        <v>1398.7</v>
       </c>
       <c r="C92" s="3">
-        <v>1409.7</v>
+        <v>1400.4</v>
       </c>
     </row>
     <row r="93" spans="1:3">
@@ -5492,10 +5492,10 @@
         <v>94</v>
       </c>
       <c r="B93" s="3">
-        <v>1398.7</v>
+        <v>1402.9</v>
       </c>
       <c r="C93" s="3">
-        <v>1400.4</v>
+        <v>1405</v>
       </c>
     </row>
     <row r="94" spans="1:3">
@@ -5503,10 +5503,10 @@
         <v>95</v>
       </c>
       <c r="B94" s="3">
-        <v>1402.9</v>
+        <v>1403.2</v>
       </c>
       <c r="C94" s="3">
-        <v>1405</v>
+        <v>1403</v>
       </c>
     </row>
     <row r="95" spans="1:3">
@@ -5514,10 +5514,10 @@
         <v>96</v>
       </c>
       <c r="B95" s="3">
-        <v>1403.2</v>
+        <v>1400</v>
       </c>
       <c r="C95" s="3">
-        <v>1403</v>
+        <v>1407</v>
       </c>
     </row>
     <row r="96" spans="1:3">
@@ -5525,10 +5525,10 @@
         <v>97</v>
       </c>
       <c r="B96" s="3">
-        <v>1400</v>
+        <v>1421</v>
       </c>
       <c r="C96" s="3">
-        <v>1407</v>
+        <v>1427</v>
       </c>
     </row>
     <row r="97" spans="1:3">
@@ -5536,10 +5536,10 @@
         <v>98</v>
       </c>
       <c r="B97" s="3">
-        <v>1421</v>
+        <v>1425.8</v>
       </c>
       <c r="C97" s="3">
-        <v>1427</v>
+        <v>1424.5</v>
       </c>
     </row>
     <row r="98" spans="1:3">
@@ -5547,10 +5547,10 @@
         <v>99</v>
       </c>
       <c r="B98" s="3">
-        <v>1425.8</v>
+        <v>1431</v>
       </c>
       <c r="C98" s="3">
-        <v>1424.5</v>
+        <v>1428.1</v>
       </c>
     </row>
     <row r="99" spans="1:3">
@@ -5558,10 +5558,10 @@
         <v>100</v>
       </c>
       <c r="B99" s="3">
-        <v>1431</v>
+        <v>1421.3</v>
       </c>
       <c r="C99" s="3">
-        <v>1428.1</v>
+        <v>1422.6</v>
       </c>
     </row>
     <row r="100" spans="1:3">
@@ -5569,10 +5569,10 @@
         <v>101</v>
       </c>
       <c r="B100" s="3">
-        <v>1421.3</v>
+        <v>1417.9</v>
       </c>
       <c r="C100" s="3">
-        <v>1422.6</v>
+        <v>1417.9</v>
       </c>
     </row>
     <row r="101" spans="1:3">
@@ -5580,10 +5580,10 @@
         <v>102</v>
       </c>
       <c r="B101" s="3">
-        <v>1417.9</v>
+        <v>1421.2</v>
       </c>
       <c r="C101" s="3">
-        <v>1417.9</v>
+        <v>1422.2</v>
       </c>
     </row>
     <row r="102" spans="1:3">
@@ -5591,10 +5591,10 @@
         <v>103</v>
       </c>
       <c r="B102" s="3">
-        <v>1421.2</v>
+        <v>1419.2</v>
       </c>
       <c r="C102" s="3">
-        <v>1422.2</v>
+        <v>1420.8</v>
       </c>
     </row>
     <row r="103" spans="1:3">
@@ -5602,10 +5602,10 @@
         <v>104</v>
       </c>
       <c r="B103" s="3">
-        <v>1419.2</v>
+        <v>1427.8</v>
       </c>
       <c r="C103" s="3">
-        <v>1420.8</v>
+        <v>1432</v>
       </c>
     </row>
     <row r="104" spans="1:3">
@@ -5613,10 +5613,10 @@
         <v>105</v>
       </c>
       <c r="B104" s="3">
-        <v>1427.8</v>
+        <v>1429.8</v>
       </c>
       <c r="C104" s="3">
-        <v>1432</v>
+        <v>1431</v>
       </c>
     </row>
     <row r="105" spans="1:3">
@@ -5624,10 +5624,10 @@
         <v>106</v>
       </c>
       <c r="B105" s="3">
-        <v>1429.8</v>
+        <v>1439.6</v>
       </c>
       <c r="C105" s="3">
-        <v>1431</v>
+        <v>1437.4</v>
       </c>
     </row>
     <row r="106" spans="1:3">
@@ -5635,10 +5635,10 @@
         <v>107</v>
       </c>
       <c r="B106" s="3">
-        <v>1439.6</v>
+        <v>1437.1</v>
       </c>
       <c r="C106" s="3">
-        <v>1437.4</v>
+        <v>1439.4</v>
       </c>
     </row>
     <row r="107" spans="1:3">
@@ -5646,10 +5646,10 @@
         <v>108</v>
       </c>
       <c r="B107" s="3">
-        <v>1437.1</v>
+        <v>1431.7</v>
       </c>
       <c r="C107" s="3">
-        <v>1439.4</v>
+        <v>1433.4</v>
       </c>
     </row>
     <row r="108" spans="1:3">
@@ -5657,10 +5657,10 @@
         <v>109</v>
       </c>
       <c r="B108" s="3">
-        <v>1431.7</v>
+        <v>1437.7</v>
       </c>
       <c r="C108" s="3">
-        <v>1433.4</v>
+        <v>1432.7</v>
       </c>
     </row>
     <row r="109" spans="1:3">
@@ -5668,10 +5668,10 @@
         <v>110</v>
       </c>
       <c r="B109" s="3">
-        <v>1437.7</v>
+        <v>1431.7</v>
       </c>
       <c r="C109" s="3">
-        <v>1432.7</v>
+        <v>1421</v>
       </c>
     </row>
     <row r="110" spans="1:3">
@@ -5679,10 +5679,10 @@
         <v>111</v>
       </c>
       <c r="B110" s="3">
-        <v>1431.7</v>
+        <v>1426.5</v>
       </c>
       <c r="C110" s="3">
-        <v>1421</v>
+        <v>1435</v>
       </c>
     </row>
     <row r="111" spans="1:3">
@@ -5690,10 +5690,10 @@
         <v>112</v>
       </c>
       <c r="B111" s="3">
-        <v>1426.5</v>
+        <v>1424.4</v>
       </c>
       <c r="C111" s="3">
-        <v>1435</v>
+        <v>1433</v>
       </c>
     </row>
     <row r="112" spans="1:3">
@@ -5701,10 +5701,10 @@
         <v>113</v>
       </c>
       <c r="B112" s="3">
-        <v>1424.4</v>
+        <v>1428.8</v>
       </c>
       <c r="C112" s="3">
-        <v>1433</v>
+        <v>1431.3</v>
       </c>
     </row>
     <row r="113" spans="1:3">
@@ -5712,10 +5712,10 @@
         <v>114</v>
       </c>
       <c r="B113" s="3">
-        <v>1428.8</v>
+        <v>1437.9</v>
       </c>
       <c r="C113" s="3">
-        <v>1431.3</v>
+        <v>1440.6</v>
       </c>
     </row>
     <row r="114" spans="1:3">
@@ -5723,10 +5723,10 @@
         <v>115</v>
       </c>
       <c r="B114" s="3">
-        <v>1437.9</v>
+        <v>1449.4</v>
       </c>
       <c r="C114" s="3">
-        <v>1440.6</v>
+        <v>1441.8</v>
       </c>
     </row>
     <row r="115" spans="1:3">
@@ -5734,10 +5734,10 @@
         <v>116</v>
       </c>
       <c r="B115" s="3">
-        <v>1449.4</v>
+        <v>1447.7</v>
       </c>
       <c r="C115" s="3">
-        <v>1441.8</v>
+        <v>1449.3</v>
       </c>
     </row>
     <row r="116" spans="1:3">
@@ -5745,10 +5745,10 @@
         <v>117</v>
       </c>
       <c r="B116" s="3">
-        <v>1447.7</v>
+        <v>1456.9</v>
       </c>
       <c r="C116" s="3">
-        <v>1449.3</v>
+        <v>1461.5</v>
       </c>
     </row>
     <row r="117" spans="1:3">
@@ -5756,10 +5756,10 @@
         <v>118</v>
       </c>
       <c r="B117" s="3">
-        <v>1456.9</v>
+        <v>1451.4</v>
       </c>
       <c r="C117" s="3">
-        <v>1461.5</v>
+        <v>1456.8</v>
       </c>
     </row>
     <row r="118" spans="1:3">
@@ -5767,10 +5767,10 @@
         <v>119</v>
       </c>
       <c r="B118" s="3">
-        <v>1451.4</v>
+        <v>1463.3</v>
       </c>
       <c r="C118" s="3">
-        <v>1456.8</v>
+        <v>1463.4</v>
       </c>
     </row>
     <row r="119" spans="1:3">
@@ -5778,10 +5778,10 @@
         <v>120</v>
       </c>
       <c r="B119" s="3">
-        <v>1463.3</v>
+        <v>1465.7</v>
       </c>
       <c r="C119" s="3">
-        <v>1463.4</v>
+        <v>1468.9</v>
       </c>
     </row>
     <row r="120" spans="1:3">
@@ -5789,10 +5789,10 @@
         <v>121</v>
       </c>
       <c r="B120" s="3">
-        <v>1465.7</v>
+        <v>1467.7</v>
       </c>
       <c r="C120" s="3">
-        <v>1468.9</v>
+        <v>1466</v>
       </c>
     </row>
     <row r="121" spans="1:3">
@@ -5800,10 +5800,10 @@
         <v>122</v>
       </c>
       <c r="B121" s="3">
-        <v>1467.7</v>
+        <v>1457</v>
       </c>
       <c r="C121" s="3">
-        <v>1466</v>
+        <v>1453.1</v>
       </c>
     </row>
     <row r="122" spans="1:3">
@@ -5811,10 +5811,10 @@
         <v>123</v>
       </c>
       <c r="B122" s="3">
-        <v>1457</v>
+        <v>1458</v>
       </c>
       <c r="C122" s="3">
-        <v>1453.1</v>
+        <v>1460.4</v>
       </c>
     </row>
     <row r="123" spans="1:3">
@@ -5822,10 +5822,10 @@
         <v>124</v>
       </c>
       <c r="B123" s="3">
-        <v>1458</v>
+        <v>1465.3</v>
       </c>
       <c r="C123" s="3">
-        <v>1460.4</v>
+        <v>1461.9</v>
       </c>
     </row>
     <row r="124" spans="1:3">
@@ -5833,10 +5833,10 @@
         <v>125</v>
       </c>
       <c r="B124" s="3">
-        <v>1465.3</v>
+        <v>1465.6</v>
       </c>
       <c r="C124" s="3">
-        <v>1461.9</v>
+        <v>1468.5</v>
       </c>
     </row>
     <row r="125" spans="1:3">
@@ -5844,10 +5844,10 @@
         <v>126</v>
       </c>
       <c r="B125" s="3">
-        <v>1465.6</v>
+        <v>1467.9</v>
       </c>
       <c r="C125" s="3">
-        <v>1468.5</v>
+        <v>1472.2</v>
       </c>
     </row>
     <row r="126" spans="1:3">
@@ -5855,10 +5855,10 @@
         <v>127</v>
       </c>
       <c r="B126" s="3">
-        <v>1467.9</v>
+        <v>1475.6</v>
       </c>
       <c r="C126" s="3">
-        <v>1472.2</v>
+        <v>1471.5</v>
       </c>
     </row>
     <row r="127" spans="1:3">
@@ -5866,10 +5866,10 @@
         <v>128</v>
       </c>
       <c r="B127" s="3">
-        <v>1475.6</v>
+        <v>1477.1</v>
       </c>
       <c r="C127" s="3">
-        <v>1471.5</v>
+        <v>1476.5</v>
       </c>
     </row>
     <row r="128" spans="1:3">
@@ -5877,10 +5877,10 @@
         <v>129</v>
       </c>
       <c r="B128" s="3">
-        <v>1477.1</v>
+        <v>1472.4</v>
       </c>
       <c r="C128" s="3">
-        <v>1476.5</v>
+        <v>1469.3</v>
       </c>
     </row>
     <row r="129" spans="1:3">
@@ -5888,10 +5888,10 @@
         <v>130</v>
       </c>
       <c r="B129" s="3">
-        <v>1472.4</v>
+        <v>1465.6</v>
       </c>
       <c r="C129" s="3">
-        <v>1469.3</v>
+        <v>1468.3</v>
       </c>
     </row>
     <row r="130" spans="1:3">
@@ -5899,10 +5899,10 @@
         <v>131</v>
       </c>
       <c r="B130" s="3">
-        <v>1465.6</v>
+        <v>1464.9</v>
       </c>
       <c r="C130" s="3">
-        <v>1468.3</v>
+        <v>1462.7</v>
       </c>
     </row>
     <row r="131" spans="1:3">
@@ -5910,10 +5910,10 @@
         <v>132</v>
       </c>
       <c r="B131" s="3">
-        <v>1464.9</v>
+        <v>1470.6</v>
       </c>
       <c r="C131" s="3">
-        <v>1462.7</v>
+        <v>1466.8</v>
       </c>
     </row>
     <row r="132" spans="1:3">
@@ -5921,10 +5921,10 @@
         <v>133</v>
       </c>
       <c r="B132" s="3">
-        <v>1470.6</v>
+        <v>1469.9</v>
       </c>
       <c r="C132" s="3">
-        <v>1466.8</v>
+        <v>1468</v>
       </c>
     </row>
     <row r="133" spans="1:3">
@@ -5932,10 +5932,10 @@
         <v>134</v>
       </c>
       <c r="B133" s="3">
-        <v>1469.9</v>
+        <v>1468.4</v>
       </c>
       <c r="C133" s="3">
-        <v>1468</v>
+        <v>1469.4</v>
       </c>
     </row>
     <row r="134" spans="1:3">
@@ -5943,10 +5943,10 @@
         <v>135</v>
       </c>
       <c r="B134" s="3">
-        <v>1468.4</v>
+        <v>1468</v>
       </c>
       <c r="C134" s="3">
-        <v>1469.4</v>
+        <v>1466.9</v>
       </c>
     </row>
     <row r="135" spans="1:3">
@@ -5954,10 +5954,10 @@
         <v>136</v>
       </c>
       <c r="B135" s="3">
-        <v>1468</v>
+        <v>1473.5</v>
       </c>
       <c r="C135" s="3">
-        <v>1466.9</v>
+        <v>1473.6</v>
       </c>
     </row>
     <row r="136" spans="1:3">
@@ -5965,10 +5965,10 @@
         <v>137</v>
       </c>
       <c r="B136" s="3">
-        <v>1473.5</v>
+        <v>1468.8</v>
       </c>
       <c r="C136" s="3">
-        <v>1473.6</v>
+        <v>1473.3</v>
       </c>
     </row>
     <row r="137" spans="1:3">
@@ -5976,10 +5976,10 @@
         <v>138</v>
       </c>
       <c r="B137" s="3">
-        <v>1468.8</v>
+        <v>1466.9</v>
       </c>
       <c r="C137" s="3">
-        <v>1473.3</v>
+        <v>1469.8</v>
       </c>
     </row>
     <row r="138" spans="1:3">
@@ -5987,10 +5987,10 @@
         <v>139</v>
       </c>
       <c r="B138" s="3">
-        <v>1466.9</v>
+        <v>1472.3</v>
       </c>
       <c r="C138" s="3">
-        <v>1469.8</v>
+        <v>1469.9</v>
       </c>
     </row>
     <row r="139" spans="1:3">
@@ -5998,10 +5998,10 @@
         <v>140</v>
       </c>
       <c r="B139" s="3">
-        <v>1472.3</v>
+        <v>1470.4</v>
       </c>
       <c r="C139" s="3">
-        <v>1469.9</v>
+        <v>1470.8</v>
       </c>
     </row>
     <row r="140" spans="1:3">
@@ -6009,10 +6009,10 @@
         <v>141</v>
       </c>
       <c r="B140" s="3">
-        <v>1470.4</v>
+        <v>1473</v>
       </c>
       <c r="C140" s="3">
-        <v>1470.8</v>
+        <v>1471.9</v>
       </c>
     </row>
     <row r="141" spans="1:3">
@@ -6020,10 +6020,10 @@
         <v>142</v>
       </c>
       <c r="B141" s="3">
-        <v>1473</v>
+        <v>1473.7</v>
       </c>
       <c r="C141" s="3">
-        <v>1471.9</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="142" spans="1:3">
@@ -6031,10 +6031,10 @@
         <v>143</v>
       </c>
       <c r="B142" s="3">
-        <v>1473.7</v>
+        <v>1471</v>
       </c>
       <c r="C142" s="3">
-        <v>1477</v>
+        <v>1468.6</v>
       </c>
     </row>
     <row r="143" spans="1:3">
@@ -6042,10 +6042,10 @@
         <v>144</v>
       </c>
       <c r="B143" s="3">
-        <v>1471</v>
+        <v>1477</v>
       </c>
       <c r="C143" s="3">
-        <v>1468.6</v>
+        <v>1473</v>
       </c>
     </row>
     <row r="144" spans="1:3">
@@ -6053,10 +6053,10 @@
         <v>145</v>
       </c>
       <c r="B144" s="3">
-        <v>1477</v>
+        <v>1479.8</v>
       </c>
       <c r="C144" s="3">
-        <v>1473</v>
+        <v>1474.5</v>
       </c>
     </row>
     <row r="145" spans="1:3">
@@ -6064,10 +6064,10 @@
         <v>146</v>
       </c>
       <c r="B145" s="3">
-        <v>1479.8</v>
+        <v>1478.3</v>
       </c>
       <c r="C145" s="3">
-        <v>1474.5</v>
+        <v>1473.1</v>
       </c>
     </row>
     <row r="146" spans="1:3">
@@ -6075,10 +6075,10 @@
         <v>147</v>
       </c>
       <c r="B146" s="3">
-        <v>1478.3</v>
+        <v>1476.3</v>
       </c>
       <c r="C146" s="3">
-        <v>1473.1</v>
+        <v>1478</v>
       </c>
     </row>
     <row r="147" spans="1:3">
@@ -6086,10 +6086,10 @@
         <v>148</v>
       </c>
       <c r="B147" s="3">
-        <v>1476.3</v>
+        <v>1480.1</v>
       </c>
       <c r="C147" s="3">
-        <v>1478</v>
+        <v>1481</v>
       </c>
     </row>
     <row r="148" spans="1:3">
@@ -6097,7 +6097,7 @@
         <v>149</v>
       </c>
       <c r="B148" s="3">
-        <v>1480.1</v>
+        <v>1483.6</v>
       </c>
       <c r="C148" s="3">
         <v>1481</v>
@@ -6108,10 +6108,10 @@
         <v>150</v>
       </c>
       <c r="B149" s="3">
-        <v>1483.6</v>
+        <v>1449.8</v>
       </c>
       <c r="C149" s="3">
-        <v>1481</v>
+        <v>1445.7</v>
       </c>
     </row>
     <row r="150" spans="1:3">
@@ -6119,10 +6119,10 @@
         <v>151</v>
       </c>
       <c r="B150" s="3">
-        <v>1449.8</v>
+        <v>1440.3</v>
       </c>
       <c r="C150" s="3">
-        <v>1445.7</v>
+        <v>1442.2</v>
       </c>
     </row>
     <row r="151" spans="1:3">
@@ -6130,10 +6130,10 @@
         <v>152</v>
       </c>
       <c r="B151" s="3">
-        <v>1440.3</v>
+        <v>1429.8</v>
       </c>
       <c r="C151" s="3">
-        <v>1442.2</v>
+        <v>1434.1</v>
       </c>
     </row>
     <row r="152" spans="1:3">
@@ -6141,10 +6141,10 @@
         <v>153</v>
       </c>
       <c r="B152" s="3">
-        <v>1429.8</v>
+        <v>1439</v>
       </c>
       <c r="C152" s="3">
-        <v>1434.1</v>
+        <v>1439.5</v>
       </c>
     </row>
     <row r="153" spans="1:3">
@@ -6152,10 +6152,10 @@
         <v>154</v>
       </c>
       <c r="B153" s="3">
-        <v>1439</v>
+        <v>1441.8</v>
       </c>
       <c r="C153" s="3">
-        <v>1439.5</v>
+        <v>1444.7</v>
       </c>
     </row>
     <row r="154" spans="1:3">
@@ -6163,10 +6163,10 @@
         <v>155</v>
       </c>
       <c r="B154" s="3">
-        <v>1441.8</v>
+        <v>1443.8</v>
       </c>
       <c r="C154" s="3">
-        <v>1444.7</v>
+        <v>1445.6</v>
       </c>
     </row>
     <row r="155" spans="1:3">
@@ -6174,10 +6174,10 @@
         <v>156</v>
       </c>
       <c r="B155" s="3">
-        <v>1443.8</v>
+        <v>1445.4</v>
       </c>
       <c r="C155" s="3">
-        <v>1445.6</v>
+        <v>1447.1</v>
       </c>
     </row>
     <row r="156" spans="1:3">
@@ -6185,10 +6185,10 @@
         <v>157</v>
       </c>
       <c r="B156" s="3">
-        <v>1445.4</v>
+        <v>1445.8</v>
       </c>
       <c r="C156" s="3">
-        <v>1447.1</v>
+        <v>1447.6</v>
       </c>
     </row>
     <row r="157" spans="1:3">
@@ -6196,10 +6196,10 @@
         <v>158</v>
       </c>
       <c r="B157" s="3">
-        <v>1445.8</v>
+        <v>1450.6</v>
       </c>
       <c r="C157" s="3">
-        <v>1447.6</v>
+        <v>1451.8</v>
       </c>
     </row>
     <row r="158" spans="1:3">
@@ -6207,10 +6207,10 @@
         <v>159</v>
       </c>
       <c r="B158" s="3">
-        <v>1450.6</v>
+        <v>1457.6</v>
       </c>
       <c r="C158" s="3">
-        <v>1451.8</v>
+        <v>1459</v>
       </c>
     </row>
     <row r="159" spans="1:3">
@@ -6218,10 +6218,10 @@
         <v>160</v>
       </c>
       <c r="B159" s="3">
-        <v>1457.6</v>
+        <v>1468.4</v>
       </c>
       <c r="C159" s="3">
-        <v>1459</v>
+        <v>1468.8</v>
       </c>
     </row>
     <row r="160" spans="1:3">
@@ -6229,10 +6229,10 @@
         <v>161</v>
       </c>
       <c r="B160" s="3">
-        <v>1468.4</v>
+        <v>1473.7</v>
       </c>
       <c r="C160" s="3">
-        <v>1468.8</v>
+        <v>1478.8</v>
       </c>
     </row>
     <row r="161" spans="1:3">
@@ -6240,10 +6240,10 @@
         <v>162</v>
       </c>
       <c r="B161" s="3">
-        <v>1473.7</v>
+        <v>1477.5</v>
       </c>
       <c r="C161" s="3">
-        <v>1478.8</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="162" spans="1:3">
@@ -6251,10 +6251,10 @@
         <v>163</v>
       </c>
       <c r="B162" s="3">
-        <v>1477.5</v>
+        <v>1469.7</v>
       </c>
       <c r="C162" s="3">
-        <v>1464</v>
+        <v>1469.2</v>
       </c>
     </row>
     <row r="163" spans="1:3">
@@ -6262,10 +6262,10 @@
         <v>164</v>
       </c>
       <c r="B163" s="3">
-        <v>1469.7</v>
+        <v>1473.6</v>
       </c>
       <c r="C163" s="3">
-        <v>1469.2</v>
+        <v>1474.5</v>
       </c>
     </row>
     <row r="164" spans="1:3">
@@ -6273,10 +6273,10 @@
         <v>165</v>
       </c>
       <c r="B164" s="3">
-        <v>1473.6</v>
+        <v>1473.7</v>
       </c>
       <c r="C164" s="3">
-        <v>1474.5</v>
+        <v>1473.1</v>
       </c>
     </row>
     <row r="165" spans="1:3">
@@ -6284,10 +6284,10 @@
         <v>166</v>
       </c>
       <c r="B165" s="3">
-        <v>1473.7</v>
+        <v>1478.1</v>
       </c>
       <c r="C165" s="3">
-        <v>1473.1</v>
+        <v>1476.7</v>
       </c>
     </row>
     <row r="166" spans="1:3">
@@ -6295,10 +6295,10 @@
         <v>167</v>
       </c>
       <c r="B166" s="3">
-        <v>1478.1</v>
+        <v>1471.3</v>
       </c>
       <c r="C166" s="3">
-        <v>1476.7</v>
+        <v>1465.9</v>
       </c>
     </row>
     <row r="167" spans="1:3">
@@ -6306,10 +6306,10 @@
         <v>168</v>
       </c>
       <c r="B167" s="3">
-        <v>1471.3</v>
+        <v>1469.9</v>
       </c>
       <c r="C167" s="3">
-        <v>1465.9</v>
+        <v>1464.5</v>
       </c>
     </row>
     <row r="168" spans="1:3">
@@ -6317,10 +6317,10 @@
         <v>169</v>
       </c>
       <c r="B168" s="3">
-        <v>1469.9</v>
+        <v>1465.8</v>
       </c>
       <c r="C168" s="3">
-        <v>1464.5</v>
+        <v>1462.5</v>
       </c>
     </row>
     <row r="169" spans="1:3">
@@ -6328,10 +6328,10 @@
         <v>170</v>
       </c>
       <c r="B169" s="3">
-        <v>1465.8</v>
+        <v>1440.6</v>
       </c>
       <c r="C169" s="3">
-        <v>1462.5</v>
+        <v>1443.9</v>
       </c>
     </row>
     <row r="170" spans="1:3">
@@ -6339,10 +6339,10 @@
         <v>171</v>
       </c>
       <c r="B170" s="3">
-        <v>1440.6</v>
+        <v>1446.2</v>
       </c>
       <c r="C170" s="3">
-        <v>1443.9</v>
+        <v>1437.5</v>
       </c>
     </row>
     <row r="171" spans="1:3">
@@ -6350,10 +6350,10 @@
         <v>172</v>
       </c>
       <c r="B171" s="3">
-        <v>1446.2</v>
+        <v>1422.5</v>
       </c>
       <c r="C171" s="3">
-        <v>1437.5</v>
+        <v>1436.1</v>
       </c>
     </row>
     <row r="172" spans="1:3">
@@ -6361,10 +6361,10 @@
         <v>173</v>
       </c>
       <c r="B172" s="3">
-        <v>1422.5</v>
+        <v>1426.3</v>
       </c>
       <c r="C172" s="3">
-        <v>1436.1</v>
+        <v>1434</v>
       </c>
     </row>
     <row r="173" spans="1:3">
@@ -6372,10 +6372,10 @@
         <v>174</v>
       </c>
       <c r="B173" s="3">
-        <v>1426.3</v>
+        <v>1439.5</v>
       </c>
       <c r="C173" s="3">
-        <v>1434</v>
+        <v>1443.5</v>
       </c>
     </row>
     <row r="174" spans="1:3">
@@ -6383,10 +6383,10 @@
         <v>175</v>
       </c>
       <c r="B174" s="3">
-        <v>1439.5</v>
+        <v>1464.3</v>
       </c>
       <c r="C174" s="3">
-        <v>1443.5</v>
+        <v>1451.5</v>
       </c>
     </row>
     <row r="175" spans="1:3">
@@ -6394,10 +6394,10 @@
         <v>176</v>
       </c>
       <c r="B175" s="3">
-        <v>1464.3</v>
+        <v>1445.4</v>
       </c>
       <c r="C175" s="3">
-        <v>1451.5</v>
+        <v>1446.6</v>
       </c>
     </row>
     <row r="176" spans="1:3">
@@ -6405,10 +6405,10 @@
         <v>177</v>
       </c>
       <c r="B176" s="3">
-        <v>1445.4</v>
+        <v>1450.2</v>
       </c>
       <c r="C176" s="3">
-        <v>1446.6</v>
+        <v>1459.5</v>
       </c>
     </row>
     <row r="177" spans="1:3">
@@ -6416,10 +6416,10 @@
         <v>178</v>
       </c>
       <c r="B177" s="3">
-        <v>1450.2</v>
+        <v>1469</v>
       </c>
       <c r="C177" s="3">
-        <v>1459.5</v>
+        <v>1463.7</v>
       </c>
     </row>
     <row r="178" spans="1:3">
@@ -6427,10 +6427,10 @@
         <v>179</v>
       </c>
       <c r="B178" s="3">
-        <v>1469</v>
+        <v>1469.5</v>
       </c>
       <c r="C178" s="3">
-        <v>1463.7</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="179" spans="1:3">
@@ -6438,10 +6438,10 @@
         <v>180</v>
       </c>
       <c r="B179" s="3">
-        <v>1469.5</v>
+        <v>1460.3</v>
       </c>
       <c r="C179" s="3">
-        <v>1463</v>
+        <v>1457.7</v>
       </c>
     </row>
     <row r="180" spans="1:3">
@@ -6449,10 +6449,10 @@
         <v>181</v>
       </c>
       <c r="B180" s="3">
-        <v>1460.3</v>
+        <v>1459.1</v>
       </c>
       <c r="C180" s="3">
-        <v>1457.7</v>
+        <v>1457.2</v>
       </c>
     </row>
     <row r="181" spans="1:3">
@@ -6460,10 +6460,10 @@
         <v>182</v>
       </c>
       <c r="B181" s="3">
-        <v>1459.1</v>
+        <v>1450.1</v>
       </c>
       <c r="C181" s="3">
-        <v>1457.2</v>
+        <v>1447</v>
       </c>
     </row>
     <row r="182" spans="1:3">
@@ -6471,10 +6471,10 @@
         <v>183</v>
       </c>
       <c r="B182" s="3">
-        <v>1450.1</v>
+        <v>1440.2</v>
       </c>
       <c r="C182" s="3">
-        <v>1447</v>
+        <v>1438.6</v>
       </c>
     </row>
     <row r="183" spans="1:3">
@@ -6482,10 +6482,10 @@
         <v>184</v>
       </c>
       <c r="B183" s="3">
-        <v>1440.2</v>
+        <v>1444.9</v>
       </c>
       <c r="C183" s="3">
-        <v>1438.6</v>
+        <v>1444.6</v>
       </c>
     </row>
     <row r="184" spans="1:3">
@@ -6493,10 +6493,10 @@
         <v>185</v>
       </c>
       <c r="B184" s="3">
-        <v>1444.9</v>
+        <v>1445.5</v>
       </c>
       <c r="C184" s="3">
-        <v>1444.6</v>
+        <v>1448.9</v>
       </c>
     </row>
     <row r="185" spans="1:3">
@@ -6504,10 +6504,10 @@
         <v>186</v>
       </c>
       <c r="B185" s="3">
-        <v>1445.5</v>
+        <v>1446.6</v>
       </c>
       <c r="C185" s="3">
-        <v>1448.9</v>
+        <v>1446.6</v>
       </c>
     </row>
     <row r="186" spans="1:3">
@@ -6515,10 +6515,10 @@
         <v>187</v>
       </c>
       <c r="B186" s="3">
-        <v>1446.6</v>
+        <v>1440</v>
       </c>
       <c r="C186" s="3">
-        <v>1446.6</v>
+        <v>1442.9</v>
       </c>
     </row>
     <row r="187" spans="1:3">
@@ -6526,10 +6526,10 @@
         <v>188</v>
       </c>
       <c r="B187" s="3">
-        <v>1440</v>
+        <v>1442.5</v>
       </c>
       <c r="C187" s="3">
-        <v>1442.9</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="188" spans="1:3">
@@ -6537,10 +6537,10 @@
         <v>189</v>
       </c>
       <c r="B188" s="3">
-        <v>1442.5</v>
+        <v>1429.4</v>
       </c>
       <c r="C188" s="3">
-        <v>1441</v>
+        <v>1427.8</v>
       </c>
     </row>
     <row r="189" spans="1:3">
@@ -6548,10 +6548,10 @@
         <v>190</v>
       </c>
       <c r="B189" s="3">
-        <v>1429.4</v>
+        <v>1425.8</v>
       </c>
       <c r="C189" s="3">
-        <v>1427.8</v>
+        <v>1433.5</v>
       </c>
     </row>
     <row r="190" spans="1:3">
@@ -6559,10 +6559,10 @@
         <v>191</v>
       </c>
       <c r="B190" s="3">
-        <v>1425.8</v>
+        <v>1439.7</v>
       </c>
       <c r="C190" s="3">
-        <v>1433.5</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="191" spans="1:3">
@@ -6570,10 +6570,10 @@
         <v>192</v>
       </c>
       <c r="B191" s="3">
-        <v>1439.7</v>
+        <v>1466.1</v>
       </c>
       <c r="C191" s="3">
-        <v>1440</v>
+        <v>1485.7</v>
       </c>
     </row>
     <row r="192" spans="1:3">
@@ -6581,10 +6581,10 @@
         <v>193</v>
       </c>
       <c r="B192" s="3">
-        <v>1466.1</v>
+        <v>1476.2</v>
       </c>
       <c r="C192" s="3">
-        <v>1485.7</v>
+        <v>1462.9</v>
       </c>
     </row>
     <row r="193" spans="1:3">
@@ -6592,10 +6592,10 @@
         <v>194</v>
       </c>
       <c r="B193" s="3">
-        <v>1476.2</v>
+        <v>1468.1</v>
       </c>
       <c r="C193" s="3">
-        <v>1462.9</v>
+        <v>1482.2</v>
       </c>
     </row>
     <row r="194" spans="1:3">
@@ -6603,10 +6603,10 @@
         <v>195</v>
       </c>
       <c r="B194" s="3">
-        <v>1468.1</v>
+        <v>1476.4</v>
       </c>
       <c r="C194" s="3">
-        <v>1482.2</v>
+        <v>1481.6</v>
       </c>
     </row>
     <row r="195" spans="1:3">
@@ -6614,10 +6614,10 @@
         <v>196</v>
       </c>
       <c r="B195" s="3">
-        <v>1476.4</v>
+        <v>1495.5</v>
       </c>
       <c r="C195" s="3">
-        <v>1481.6</v>
+        <v>1473.7</v>
       </c>
     </row>
     <row r="196" spans="1:3">
@@ -6625,10 +6625,10 @@
         <v>197</v>
       </c>
       <c r="B196" s="3">
-        <v>1495.5</v>
+        <v>1469.2</v>
       </c>
       <c r="C196" s="3">
-        <v>1473.7</v>
+        <v>1465.7</v>
       </c>
     </row>
     <row r="197" spans="1:3">
@@ -6636,10 +6636,10 @@
         <v>198</v>
       </c>
       <c r="B197" s="3">
-        <v>1469.2</v>
+        <v>1466.5</v>
       </c>
       <c r="C197" s="3">
-        <v>1465.7</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="198" spans="1:3">
@@ -6647,10 +6647,10 @@
         <v>199</v>
       </c>
       <c r="B198" s="3">
-        <v>1466.5</v>
+        <v>1481.2</v>
       </c>
       <c r="C198" s="3">
-        <v>1477</v>
+        <v>1488.5</v>
       </c>
     </row>
     <row r="199" spans="1:3">
@@ -6658,10 +6658,10 @@
         <v>200</v>
       </c>
       <c r="B199" s="3">
-        <v>1481.2</v>
+        <v>1493.7</v>
       </c>
       <c r="C199" s="3">
-        <v>1488.5</v>
+        <v>1497.5</v>
       </c>
     </row>
     <row r="200" spans="1:3">
@@ -6669,10 +6669,10 @@
         <v>201</v>
       </c>
       <c r="B200" s="3">
-        <v>1493.7</v>
+        <v>1497.5</v>
       </c>
       <c r="C200" s="3">
-        <v>1497.5</v>
+        <v>1491.9</v>
       </c>
     </row>
     <row r="201" spans="1:3">
@@ -6680,10 +6680,10 @@
         <v>202</v>
       </c>
       <c r="B201" s="3">
-        <v>1497.5</v>
+        <v>1493.6</v>
       </c>
       <c r="C201" s="3">
-        <v>1491.9</v>
+        <v>1488.4</v>
       </c>
     </row>
     <row r="202" spans="1:3">
@@ -6691,10 +6691,10 @@
         <v>203</v>
       </c>
       <c r="B202" s="3">
-        <v>1493.6</v>
+        <v>1483.1</v>
       </c>
       <c r="C202" s="3">
-        <v>1488.4</v>
+        <v>1500.7</v>
       </c>
     </row>
     <row r="203" spans="1:3">
@@ -6702,10 +6702,10 @@
         <v>204</v>
       </c>
       <c r="B203" s="3">
-        <v>1483.1</v>
+        <v>1501</v>
       </c>
       <c r="C203" s="3">
-        <v>1500.7</v>
+        <v>1495</v>
       </c>
     </row>
     <row r="204" spans="1:3">
@@ -6713,10 +6713,10 @@
         <v>205</v>
       </c>
       <c r="B204" s="3">
-        <v>1501</v>
+        <v>1500.6</v>
       </c>
       <c r="C204" s="3">
-        <v>1495</v>
+        <v>1504.7</v>
       </c>
     </row>
     <row r="205" spans="1:3">
@@ -6724,10 +6724,10 @@
         <v>206</v>
       </c>
       <c r="B205" s="3">
-        <v>1500.6</v>
+        <v>1517.3</v>
       </c>
       <c r="C205" s="3">
-        <v>1504.7</v>
+        <v>1486.7</v>
       </c>
     </row>
     <row r="206" spans="1:3">
@@ -6735,10 +6735,10 @@
         <v>207</v>
       </c>
       <c r="B206" s="3">
-        <v>1517.3</v>
+        <v>1495.2</v>
       </c>
       <c r="C206" s="3">
-        <v>1486.7</v>
+        <v>1499.9</v>
       </c>
     </row>
     <row r="207" spans="1:3">
@@ -6746,10 +6746,10 @@
         <v>208</v>
       </c>
       <c r="B207" s="3">
-        <v>1495.2</v>
+        <v>1499.7</v>
       </c>
       <c r="C207" s="3">
-        <v>1499.9</v>
+        <v>1501.7</v>
       </c>
     </row>
     <row r="208" spans="1:3">
@@ -6757,10 +6757,10 @@
         <v>209</v>
       </c>
       <c r="B208" s="3">
-        <v>1499.7</v>
+        <v>1507</v>
       </c>
       <c r="C208" s="3">
-        <v>1501.7</v>
+        <v>1508</v>
       </c>
     </row>
     <row r="209" spans="1:3">
@@ -6768,10 +6768,10 @@
         <v>210</v>
       </c>
       <c r="B209" s="3">
-        <v>1507</v>
+        <v>1508.9</v>
       </c>
       <c r="C209" s="3">
-        <v>1508</v>
+        <v>1511.4</v>
       </c>
     </row>
     <row r="210" spans="1:3">
@@ -6779,10 +6779,10 @@
         <v>211</v>
       </c>
       <c r="B210" s="3">
-        <v>1508.9</v>
+        <v>1515.7</v>
       </c>
       <c r="C210" s="3">
-        <v>1511.4</v>
+        <v>1518.2</v>
       </c>
     </row>
     <row r="211" spans="1:3">
@@ -6790,10 +6790,10 @@
         <v>212</v>
       </c>
       <c r="B211" s="3">
-        <v>1515.7</v>
+        <v>1530.1</v>
       </c>
       <c r="C211" s="3">
-        <v>1518.2</v>
+        <v>1517</v>
       </c>
     </row>
     <row r="212" spans="1:3">
@@ -6801,10 +6801,10 @@
         <v>213</v>
       </c>
       <c r="B212" s="3">
-        <v>1530.1</v>
+        <v>1501.3</v>
       </c>
       <c r="C212" s="3">
-        <v>1517</v>
+        <v>1513.3</v>
       </c>
     </row>
     <row r="213" spans="1:3">
@@ -6812,10 +6812,10 @@
         <v>214</v>
       </c>
       <c r="B213" s="3">
-        <v>1501.3</v>
+        <v>1519.7</v>
       </c>
       <c r="C213" s="3">
-        <v>1513.3</v>
+        <v>1510.6</v>
       </c>
     </row>
     <row r="214" spans="1:3">
@@ -6823,10 +6823,10 @@
         <v>215</v>
       </c>
       <c r="B214" s="3">
-        <v>1519.7</v>
+        <v>1505.2</v>
       </c>
       <c r="C214" s="3">
-        <v>1510.6</v>
+        <v>1511.4</v>
       </c>
     </row>
     <row r="215" spans="1:3">
@@ -6834,10 +6834,10 @@
         <v>216</v>
       </c>
       <c r="B215" s="3">
-        <v>1505.2</v>
+        <v>1506.3</v>
       </c>
       <c r="C215" s="3">
-        <v>1511.4</v>
+        <v>1509.8</v>
       </c>
     </row>
     <row r="216" spans="1:3">
@@ -6845,10 +6845,10 @@
         <v>217</v>
       </c>
       <c r="B216" s="3">
-        <v>1506.3</v>
+        <v>1504.2</v>
       </c>
       <c r="C216" s="3">
-        <v>1509.8</v>
+        <v>1501</v>
       </c>
     </row>
     <row r="217" spans="1:3">
@@ -6856,10 +6856,10 @@
         <v>218</v>
       </c>
       <c r="B217" s="3">
-        <v>1504.2</v>
+        <v>1470.6</v>
       </c>
       <c r="C217" s="3">
-        <v>1501</v>
+        <v>1479.2</v>
       </c>
     </row>
     <row r="218" spans="1:3">
@@ -6867,10 +6867,10 @@
         <v>219</v>
       </c>
       <c r="B218" s="3">
-        <v>1470.6</v>
+        <v>1482.5</v>
       </c>
       <c r="C218" s="3">
-        <v>1479.2</v>
+        <v>1474.7</v>
       </c>
     </row>
     <row r="219" spans="1:3">
@@ -6881,7 +6881,7 @@
         <v>1482.5</v>
       </c>
       <c r="C219" s="3">
-        <v>1474.7</v>
+        <v>1483.5</v>
       </c>
     </row>
     <row r="220" spans="1:3">
@@ -6889,10 +6889,10 @@
         <v>221</v>
       </c>
       <c r="B220" s="3">
-        <v>1482.5</v>
+        <v>1489.3</v>
       </c>
       <c r="C220" s="3">
-        <v>1483.5</v>
+        <v>1482.7</v>
       </c>
     </row>
     <row r="221" spans="1:3">
@@ -6900,10 +6900,10 @@
         <v>222</v>
       </c>
       <c r="B221" s="3">
-        <v>1489.3</v>
+        <v>1481.2</v>
       </c>
       <c r="C221" s="3">
-        <v>1482.7</v>
+        <v>1472.7</v>
       </c>
     </row>
     <row r="222" spans="1:3">
@@ -6911,10 +6911,10 @@
         <v>223</v>
       </c>
       <c r="B222" s="3">
-        <v>1481.2</v>
+        <v>1474.2</v>
       </c>
       <c r="C222" s="3">
-        <v>1472.7</v>
+        <v>1475.5</v>
       </c>
     </row>
     <row r="223" spans="1:3">
@@ -6922,10 +6922,10 @@
         <v>224</v>
       </c>
       <c r="B223" s="3">
-        <v>1474.2</v>
+        <v>1474.6</v>
       </c>
       <c r="C223" s="3">
-        <v>1475.5</v>
+        <v>1479.2</v>
       </c>
     </row>
     <row r="224" spans="1:3">
@@ -6933,10 +6933,10 @@
         <v>225</v>
       </c>
       <c r="B224" s="3">
-        <v>1474.6</v>
+        <v>1483.5</v>
       </c>
       <c r="C224" s="3">
-        <v>1479.2</v>
+        <v>1460</v>
       </c>
     </row>
     <row r="225" spans="1:3">
@@ -6944,10 +6944,10 @@
         <v>226</v>
       </c>
       <c r="B225" s="3">
-        <v>1483.5</v>
+        <v>1477.2</v>
       </c>
       <c r="C225" s="3">
-        <v>1460</v>
+        <v>1472.8</v>
       </c>
     </row>
     <row r="226" spans="1:3">
@@ -6955,10 +6955,10 @@
         <v>227</v>
       </c>
       <c r="B226" s="3">
-        <v>1477.2</v>
+        <v>1468.5</v>
       </c>
       <c r="C226" s="3">
-        <v>1472.8</v>
+        <v>1480.8</v>
       </c>
     </row>
     <row r="227" spans="1:3">
@@ -6966,10 +6966,10 @@
         <v>228</v>
       </c>
       <c r="B227" s="3">
-        <v>1468.5</v>
+        <v>1476</v>
       </c>
       <c r="C227" s="3">
-        <v>1480.8</v>
+        <v>1480.3</v>
       </c>
     </row>
     <row r="228" spans="1:3">
@@ -6977,10 +6977,10 @@
         <v>229</v>
       </c>
       <c r="B228" s="3">
-        <v>1476</v>
+        <v>1481</v>
       </c>
       <c r="C228" s="3">
-        <v>1480.3</v>
+        <v>1479.2</v>
       </c>
     </row>
     <row r="229" spans="1:3">
@@ -6988,10 +6988,10 @@
         <v>230</v>
       </c>
       <c r="B229" s="3">
-        <v>1481</v>
+        <v>1484.5</v>
       </c>
       <c r="C229" s="3">
-        <v>1479.2</v>
+        <v>1476.8</v>
       </c>
     </row>
     <row r="230" spans="1:3">
@@ -6999,10 +6999,10 @@
         <v>231</v>
       </c>
       <c r="B230" s="3">
-        <v>1484.5</v>
+        <v>1472.5</v>
       </c>
       <c r="C230" s="3">
-        <v>1476.8</v>
+        <v>1473.6</v>
       </c>
     </row>
     <row r="231" spans="1:3">
@@ -7010,10 +7010,10 @@
         <v>232</v>
       </c>
       <c r="B231" s="3">
-        <v>1472.5</v>
+        <v>1473.6</v>
       </c>
       <c r="C231" s="3">
-        <v>1473.6</v>
+        <v>1473.2</v>
       </c>
     </row>
     <row r="232" spans="1:3">
@@ -7021,10 +7021,10 @@
         <v>233</v>
       </c>
       <c r="B232" s="3">
-        <v>1473.6</v>
+        <v>1479</v>
       </c>
       <c r="C232" s="3">
-        <v>1473.2</v>
+        <v>1488.5</v>
       </c>
     </row>
     <row r="233" spans="1:3">
@@ -7032,10 +7032,10 @@
         <v>234</v>
       </c>
       <c r="B233" s="3">
-        <v>1479</v>
+        <v>1483.3</v>
       </c>
       <c r="C233" s="3">
-        <v>1488.5</v>
+        <v>1477.5</v>
       </c>
     </row>
     <row r="234" spans="1:3">
@@ -7043,10 +7043,10 @@
         <v>235</v>
       </c>
       <c r="B234" s="3">
-        <v>1483.3</v>
+        <v>1462.8</v>
       </c>
       <c r="C234" s="3">
-        <v>1477.5</v>
+        <v>1478.4</v>
       </c>
     </row>
     <row r="235" spans="1:3">
@@ -7054,10 +7054,10 @@
         <v>236</v>
       </c>
       <c r="B235" s="3">
-        <v>1462.8</v>
+        <v>1455.1</v>
       </c>
       <c r="C235" s="3">
-        <v>1478.4</v>
+        <v>1449.4</v>
       </c>
     </row>
     <row r="236" spans="1:3">
@@ -7065,10 +7065,10 @@
         <v>237</v>
       </c>
       <c r="B236" s="3">
-        <v>1455.1</v>
+        <v>1454</v>
       </c>
       <c r="C236" s="3">
-        <v>1449.4</v>
+        <v>1456</v>
       </c>
     </row>
     <row r="237" spans="1:3">
@@ -7076,10 +7076,10 @@
         <v>238</v>
       </c>
       <c r="B237" s="3">
-        <v>1454</v>
+        <v>1471.7</v>
       </c>
       <c r="C237" s="3">
-        <v>1456</v>
+        <v>1462.3</v>
       </c>
     </row>
     <row r="238" spans="1:3">
@@ -7087,10 +7087,10 @@
         <v>239</v>
       </c>
       <c r="B238" s="3">
-        <v>1471.7</v>
+        <v>1472.4</v>
       </c>
       <c r="C238" s="3">
-        <v>1462.3</v>
+        <v>1472.7</v>
       </c>
     </row>
     <row r="239" spans="1:3">
@@ -7098,10 +7098,10 @@
         <v>240</v>
       </c>
       <c r="B239" s="3">
-        <v>1472.4</v>
+        <v>1489.9</v>
       </c>
       <c r="C239" s="3">
-        <v>1472.7</v>
+        <v>1490.9</v>
       </c>
     </row>
     <row r="240" spans="1:3">
@@ -7109,10 +7109,10 @@
         <v>241</v>
       </c>
       <c r="B240" s="3">
-        <v>1489.9</v>
+        <v>1490.6</v>
       </c>
       <c r="C240" s="3">
-        <v>1490.9</v>
+        <v>1489.3</v>
       </c>
     </row>
     <row r="241" spans="1:3">
@@ -7120,10 +7120,10 @@
         <v>242</v>
       </c>
       <c r="B241" s="3">
-        <v>1490.6</v>
+        <v>1491</v>
       </c>
       <c r="C241" s="3">
-        <v>1489.3</v>
+        <v>1493.4</v>
       </c>
     </row>
     <row r="242" spans="1:3">
@@ -7131,10 +7131,10 @@
         <v>243</v>
       </c>
       <c r="B242" s="3">
-        <v>1491</v>
+        <v>1500.8</v>
       </c>
       <c r="C242" s="3">
-        <v>1493.4</v>
+        <v>1497.5</v>
       </c>
     </row>
     <row r="243" spans="1:3">
@@ -7142,10 +7142,10 @@
         <v>244</v>
       </c>
       <c r="B243" s="3">
-        <v>1500.8</v>
+        <v>1500.3</v>
       </c>
       <c r="C243" s="3">
-        <v>1497.5</v>
+        <v>1492.9</v>
       </c>
     </row>
     <row r="244" spans="1:3">
@@ -7153,10 +7153,10 @@
         <v>245</v>
       </c>
       <c r="B244" s="3">
-        <v>1500.3</v>
+        <v>1507.8</v>
       </c>
       <c r="C244" s="3">
-        <v>1492.9</v>
+        <v>1508.7</v>
       </c>
     </row>
     <row r="245" spans="1:3">
@@ -7164,10 +7164,10 @@
         <v>246</v>
       </c>
       <c r="B245" s="3">
-        <v>1507.8</v>
+        <v>1506.8</v>
       </c>
       <c r="C245" s="3">
-        <v>1508.7</v>
+        <v>1496.7</v>
       </c>
     </row>
     <row r="246" spans="1:3">
@@ -7175,10 +7175,10 @@
         <v>247</v>
       </c>
       <c r="B246" s="3">
-        <v>1506.8</v>
+        <v>1506.1</v>
       </c>
       <c r="C246" s="4">
-        <v>1508.7</v>
+        <v>1496.7</v>
       </c>
     </row>
   </sheetData>
